--- a/research/traditional_assets/database/data/japan/japan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ35"/>
+  <dimension ref="A1:AQ33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03560000000000001</v>
+        <v>0.00945</v>
       </c>
       <c r="E2">
-        <v>0.0625</v>
+        <v>-0.0151</v>
       </c>
       <c r="F2">
-        <v>0.089</v>
+        <v>0.0572</v>
       </c>
       <c r="G2">
-        <v>0.06098184110056006</v>
+        <v>0.07688054969002951</v>
       </c>
       <c r="H2">
-        <v>0.05964017963275303</v>
+        <v>0.07622253918622594</v>
       </c>
       <c r="I2">
-        <v>0.0676229358826369</v>
+        <v>0.04734817516681705</v>
       </c>
       <c r="J2">
-        <v>0.05023696208296012</v>
+        <v>0.03381106672108938</v>
       </c>
       <c r="K2">
-        <v>3128.069</v>
+        <v>3756.926</v>
       </c>
       <c r="L2">
-        <v>0.1112592361268697</v>
+        <v>0.1589159661874983</v>
       </c>
       <c r="M2">
-        <v>1858.19904</v>
+        <v>1907.74436</v>
       </c>
       <c r="N2">
-        <v>0.04749803280029446</v>
+        <v>0.06048727187408844</v>
       </c>
       <c r="O2">
-        <v>0.5940402977044303</v>
+        <v>0.5077939677278711</v>
       </c>
       <c r="P2">
-        <v>1754.37504</v>
+        <v>1182.56336</v>
       </c>
       <c r="Q2">
-        <v>0.04484415361334915</v>
+        <v>0.0374945579525422</v>
       </c>
       <c r="R2">
-        <v>0.560849214003911</v>
+        <v>0.3147688722109512</v>
       </c>
       <c r="S2">
-        <v>103.8239999999999</v>
+        <v>725.181</v>
       </c>
       <c r="T2">
-        <v>0.05587345476187521</v>
+        <v>0.3801248297229929</v>
       </c>
       <c r="U2">
-        <v>94841.69</v>
+        <v>93627.88</v>
       </c>
       <c r="V2">
-        <v>2.424279426199337</v>
+        <v>2.96858171948915</v>
       </c>
       <c r="W2">
-        <v>0.07741312741312742</v>
+        <v>0.032897384305835</v>
       </c>
       <c r="X2">
-        <v>0.04193104446424555</v>
+        <v>0.08075198581698241</v>
       </c>
       <c r="Y2">
-        <v>0.03548208294888187</v>
+        <v>-0.04785460151114741</v>
       </c>
       <c r="Z2">
-        <v>0.07315664590424363</v>
+        <v>0.07040544243343699</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03633670577324147</v>
+        <v>0.07128010423427249</v>
       </c>
       <c r="AC2">
-        <v>-0.03595978989239257</v>
+        <v>-0.06976518271013085</v>
       </c>
       <c r="AD2">
-        <v>377346.979</v>
+        <v>355929.865</v>
       </c>
       <c r="AE2">
-        <v>2293.1734522432</v>
+        <v>1769.753424041424</v>
       </c>
       <c r="AF2">
-        <v>379640.1524522432</v>
+        <v>357699.6184240414</v>
       </c>
       <c r="AG2">
-        <v>284798.4624522432</v>
+        <v>264071.7384240414</v>
       </c>
       <c r="AH2">
-        <v>0.9065779055252627</v>
+        <v>0.9189711660410324</v>
       </c>
       <c r="AI2">
-        <v>0.8692530904348981</v>
+        <v>0.8691727633814276</v>
       </c>
       <c r="AJ2">
-        <v>0.8792245231621989</v>
+        <v>0.8933072047637164</v>
       </c>
       <c r="AK2">
-        <v>0.83298455448631</v>
+        <v>0.8306430422979399</v>
       </c>
       <c r="AL2">
-        <v>41.443</v>
+        <v>94.983</v>
       </c>
       <c r="AM2">
-        <v>-80.631</v>
+        <v>-5.403999999999996</v>
       </c>
       <c r="AN2">
-        <v>145.3031787514878</v>
+        <v>197.0054065393222</v>
       </c>
       <c r="AO2">
-        <v>44.16427382187583</v>
+        <v>10.19032879567923</v>
       </c>
       <c r="AP2">
-        <v>109.6659684609458</v>
+        <v>146.1623912446174</v>
       </c>
       <c r="AQ2">
-        <v>-22.69970606838561</v>
+        <v>-179.1095484826056</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nexus Bank Co., Ltd. (JASDAQ:4764)</t>
+          <t>M&amp;A Research Institute Inc. (TSE:9552)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.02838600451467269</v>
+        <v>0.5425185185185185</v>
       </c>
       <c r="H3">
-        <v>0.02838600451467269</v>
+        <v>0.5407407407407407</v>
       </c>
       <c r="I3">
-        <v>0.20372460496614</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="J3">
-        <v>0.1403328632783387</v>
+        <v>0.3423611111111111</v>
       </c>
       <c r="K3">
-        <v>29</v>
+        <v>9.16</v>
       </c>
       <c r="L3">
-        <v>0.1636568848758465</v>
+        <v>0.3392592592592593</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +764,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>202.9</v>
+        <v>27.5</v>
       </c>
       <c r="V3">
-        <v>3.241214057507987</v>
-      </c>
-      <c r="W3">
-        <v>1.666666666666667</v>
+        <v>0.03014359311629946</v>
       </c>
       <c r="X3">
-        <v>0.04193104446424555</v>
-      </c>
-      <c r="Y3">
-        <v>1.624735622202421</v>
-      </c>
-      <c r="Z3">
-        <v>85.56253017865775</v>
-      </c>
-      <c r="AA3">
-        <v>12.00723484931031</v>
+        <v>0.07137160704491299</v>
       </c>
       <c r="AB3">
-        <v>0.03694673846708921</v>
-      </c>
-      <c r="AC3">
-        <v>11.97028811084322</v>
+        <v>0.07135174650760384</v>
       </c>
       <c r="AD3">
-        <v>23.3</v>
+        <v>0.926</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>23.3</v>
+        <v>0.926</v>
       </c>
       <c r="AG3">
-        <v>-179.6</v>
+        <v>-26.574</v>
       </c>
       <c r="AH3">
-        <v>0.2712456344586729</v>
+        <v>0.001013987775205699</v>
       </c>
       <c r="AI3">
-        <v>0.08537925980212532</v>
+        <v>0.04383224462747326</v>
       </c>
       <c r="AJ3">
-        <v>1.535042735042735</v>
+        <v>-0.0300025064184635</v>
       </c>
       <c r="AK3">
-        <v>-2.565714285714286</v>
+        <v>4.169124568559773</v>
       </c>
       <c r="AL3">
-        <v>0.511</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.6083550913838121</v>
-      </c>
-      <c r="AO3">
-        <v>70.64579256360078</v>
+        <v>0.06342465753424659</v>
       </c>
       <c r="AP3">
-        <v>-4.689295039164491</v>
-      </c>
-      <c r="AQ3">
-        <v>85.14150943396226</v>
+        <v>-1.82013698630137</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Strike Company,Limited (TSE:6196)</t>
+          <t>M&amp;A Capital Partners Co.,Ltd. (TSE:6080)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,26 +828,32 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.2</v>
+      </c>
+      <c r="E4">
+        <v>0.212</v>
+      </c>
       <c r="F4">
-        <v>0.29</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="G4">
-        <v>0.3890374331550803</v>
+        <v>0.4870719776380154</v>
       </c>
       <c r="H4">
-        <v>0.3890374331550803</v>
+        <v>0.4870719776380154</v>
       </c>
       <c r="I4">
-        <v>0.3823529411764706</v>
+        <v>0.471145134035268</v>
       </c>
       <c r="J4">
-        <v>0.2685961618690029</v>
+        <v>0.3280566118467792</v>
       </c>
       <c r="K4">
-        <v>19.8</v>
+        <v>47</v>
       </c>
       <c r="L4">
-        <v>0.2647058823529412</v>
+        <v>0.3284416491963662</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,70 +877,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>68.3</v>
+        <v>246.5</v>
       </c>
       <c r="V4">
-        <v>0.08032459132071033</v>
+        <v>0.2219920749279539</v>
       </c>
       <c r="W4">
-        <v>0.330550918196995</v>
+        <v>0.2028485110056107</v>
       </c>
       <c r="X4">
-        <v>0.03642434289743676</v>
+        <v>0.07183461332887973</v>
       </c>
       <c r="Y4">
-        <v>0.2941265752995582</v>
+        <v>0.131013897676731</v>
       </c>
       <c r="Z4">
-        <v>35.61904761904759</v>
+        <v>439.4199318600593</v>
       </c>
       <c r="AA4">
-        <v>9.56713947990543</v>
+        <v>144.1546140239536</v>
       </c>
       <c r="AB4">
-        <v>0.03642434289743676</v>
+        <v>0.07139445157097908</v>
       </c>
       <c r="AC4">
-        <v>9.530715137007993</v>
+        <v>144.0832195723827</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>21.69565659776576</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>21.69565659776576</v>
       </c>
       <c r="AG4">
-        <v>-68.3</v>
+        <v>-224.8043434022343</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.01916415496457844</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.08783821098966649</v>
       </c>
       <c r="AJ4">
-        <v>-0.08734015345268542</v>
+        <v>-0.2538453545107432</v>
       </c>
       <c r="AK4">
-        <v>-13.13461538461538</v>
+        <v>-453.5485745888809</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.025</v>
+        <v>-0.007</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-2.347079037800687</v>
+        <v>-3.023189125904172</v>
       </c>
       <c r="AQ4">
-        <v>-1144</v>
+        <v>-9585.714285714284</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hirose Tusyo Inc. (JASDAQ:7185)</t>
+          <t>meinan M&amp;A co.,ltd. (NSE:7076)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,121 +960,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0741</v>
+        <v>0.249</v>
       </c>
       <c r="E5">
-        <v>0.245</v>
+        <v>0.484</v>
       </c>
       <c r="G5">
-        <v>0.3511749347258486</v>
+        <v>0.2617801047120419</v>
       </c>
       <c r="H5">
-        <v>0.3511749347258486</v>
+        <v>0.2617801047120419</v>
       </c>
       <c r="I5">
-        <v>0.3185378590078329</v>
+        <v>0.2577791862330918</v>
       </c>
       <c r="J5">
-        <v>0.2169537266603769</v>
+        <v>0.174000950707337</v>
       </c>
       <c r="K5">
-        <v>16.3</v>
+        <v>1.59</v>
       </c>
       <c r="L5">
-        <v>0.2127937336814622</v>
+        <v>0.1664921465968586</v>
       </c>
       <c r="M5">
-        <v>1.76808</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.01461223140495868</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1084711656441718</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>1.76808</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.01461223140495868</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1084711656441718</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>101.3</v>
+        <v>10.6</v>
       </c>
       <c r="V5">
-        <v>0.8371900826446281</v>
+        <v>0.397003745318352</v>
       </c>
       <c r="W5">
-        <v>0.1546489563567362</v>
+        <v>0.1445454545454546</v>
       </c>
       <c r="X5">
-        <v>0.04300253963876403</v>
+        <v>0.07165146585224924</v>
       </c>
       <c r="Y5">
-        <v>0.1116464167179722</v>
+        <v>0.07289398869320532</v>
       </c>
       <c r="Z5">
-        <v>1.467432950191571</v>
+        <v>75.76727814649468</v>
       </c>
       <c r="AA5">
-        <v>0.3183650471682926</v>
+        <v>13.18357842999731</v>
       </c>
       <c r="AB5">
-        <v>0.0360310204560771</v>
+        <v>0.07137658833663212</v>
       </c>
       <c r="AC5">
-        <v>0.2823340267122155</v>
+        <v>13.11220184166067</v>
       </c>
       <c r="AD5">
-        <v>53.8</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.3260438573698687</v>
       </c>
       <c r="AF5">
-        <v>53.8</v>
+        <v>0.3260438573698687</v>
       </c>
       <c r="AG5">
-        <v>-47.5</v>
+        <v>-10.27395614263013</v>
       </c>
       <c r="AH5">
-        <v>0.3077803203661327</v>
+        <v>0.0120640615803988</v>
       </c>
       <c r="AI5">
-        <v>0.3196672608437314</v>
+        <v>0.03160551291539346</v>
       </c>
       <c r="AJ5">
-        <v>-0.6462585034013606</v>
+        <v>-0.6254674729862307</v>
       </c>
       <c r="AK5">
-        <v>-0.7089552238805971</v>
+        <v>36.1814893224993</v>
       </c>
       <c r="AL5">
-        <v>0.511</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.511</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>2.160642570281125</v>
-      </c>
-      <c r="AO5">
-        <v>47.74951076320939</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-1.907630522088354</v>
-      </c>
-      <c r="AQ5">
-        <v>47.74951076320939</v>
+        <v>-3.956086308290385</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SBI Holdings, Inc. (TSE:8473)</t>
+          <t>Strike Company,Limited (TSE:6196)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1108,125 +1084,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.193</v>
-      </c>
-      <c r="E6">
-        <v>0.288</v>
-      </c>
       <c r="F6">
-        <v>0.018</v>
+        <v>0.158</v>
       </c>
       <c r="G6">
-        <v>0.2710415661404839</v>
+        <v>0.3994601889338732</v>
       </c>
       <c r="H6">
-        <v>0.2646136347969946</v>
+        <v>0.3994601889338732</v>
       </c>
       <c r="I6">
-        <v>0.2885331219411318</v>
+        <v>0.3940620782726046</v>
       </c>
       <c r="J6">
-        <v>0.2192488895733299</v>
+        <v>0.2761133603238866</v>
       </c>
       <c r="K6">
-        <v>1118.5</v>
+        <v>20.5</v>
       </c>
       <c r="L6">
-        <v>0.1927517750051699</v>
+        <v>0.2766531713900135</v>
       </c>
       <c r="M6">
-        <v>286.55</v>
+        <v>3.46</v>
       </c>
       <c r="N6">
-        <v>0.04303327926953805</v>
+        <v>0.005309191345711216</v>
       </c>
       <c r="O6">
-        <v>0.2561913276709879</v>
+        <v>0.1687804878048781</v>
       </c>
       <c r="P6">
-        <v>286.182</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.04297801405658676</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.2558623156012517</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0.367999999999995</v>
+        <v>3.46</v>
       </c>
       <c r="T6">
-        <v>0.001284243587506526</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>7664.4</v>
+        <v>59</v>
       </c>
       <c r="V6">
-        <v>1.151018201477744</v>
+        <v>0.09053245358293693</v>
       </c>
       <c r="W6">
-        <v>0.2406773825662212</v>
+        <v>0.2789115646258503</v>
       </c>
       <c r="X6">
-        <v>0.06429207034048592</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="Y6">
-        <v>0.1763853122257353</v>
+        <v>0.2075653284476373</v>
       </c>
       <c r="Z6">
-        <v>0.3893660421922809</v>
+        <v>14.24999999999999</v>
       </c>
       <c r="AA6">
-        <v>0.0853680723882199</v>
+        <v>3.934615384615382</v>
       </c>
       <c r="AB6">
-        <v>0.03558958111788407</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="AC6">
-        <v>0.04977849127033583</v>
+        <v>3.863269148437169</v>
       </c>
       <c r="AD6">
-        <v>12542.6</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12542.6</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>4878.200000000001</v>
+        <v>-59</v>
       </c>
       <c r="AH6">
-        <v>0.653212786567646</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.639220862616389</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.4228308919129757</v>
+        <v>-0.09954445756706597</v>
       </c>
       <c r="AK6">
-        <v>0.407968354059863</v>
+        <v>-3.155080213903743</v>
       </c>
       <c r="AL6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>6.621931260229133</v>
-      </c>
-      <c r="AO6">
-        <v>46.50833333333333</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.575471200042237</v>
-      </c>
-      <c r="AQ6">
-        <v>1116.2</v>
+        <v>-1.993243243243243</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Akatsuki Corp. (TSE:8737)</t>
+          <t>ONDECK Co., Ltd. (TSE:7360)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1245,122 +1209,107 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.519</v>
-      </c>
-      <c r="E7">
-        <v>-0.0293</v>
-      </c>
       <c r="G7">
-        <v>0.07825086306098963</v>
+        <v>0.04509018036072144</v>
       </c>
       <c r="H7">
-        <v>0.07825086306098963</v>
+        <v>0.04509018036072144</v>
       </c>
       <c r="I7">
-        <v>0.06875719217491369</v>
+        <v>0.2995991983967936</v>
       </c>
       <c r="J7">
-        <v>0.04831503145205818</v>
+        <v>0.2039501299897092</v>
       </c>
       <c r="K7">
-        <v>15.6</v>
+        <v>2.02</v>
       </c>
       <c r="L7">
-        <v>0.04487917146144994</v>
+        <v>0.2024048096192385</v>
       </c>
       <c r="M7">
-        <v>5.341000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.05563541666666668</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.3423717948717949</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>5.287000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05507291666666667</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.3389102564102565</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>0.05400000000000027</v>
-      </c>
-      <c r="T7">
-        <v>0.0101104662048306</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>144.7</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="V7">
-        <v>1.507291666666666</v>
+        <v>0.2816326530612245</v>
       </c>
       <c r="W7">
-        <v>0.1260096930533118</v>
+        <v>0.2407628128724672</v>
       </c>
       <c r="X7">
-        <v>0.07727964701206441</v>
+        <v>0.07148141597386588</v>
       </c>
       <c r="Y7">
-        <v>0.04873004604124739</v>
+        <v>0.1692813968986013</v>
       </c>
       <c r="Z7">
-        <v>1.679227053140097</v>
+        <v>5.516860143725812</v>
       </c>
       <c r="AA7">
-        <v>0.08113190788761075</v>
+        <v>1.125164343447925</v>
       </c>
       <c r="AB7">
-        <v>0.03548615436956309</v>
+        <v>0.07135976946925636</v>
       </c>
       <c r="AC7">
-        <v>0.04564575351804766</v>
+        <v>1.053804573978669</v>
       </c>
       <c r="AD7">
-        <v>265.1</v>
+        <v>0.159</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>265.1</v>
+        <v>0.159</v>
       </c>
       <c r="AG7">
-        <v>120.4</v>
+        <v>-8.120999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.7341456660204929</v>
+        <v>0.005379072363747082</v>
       </c>
       <c r="AI7">
-        <v>0.6634134134134134</v>
+        <v>0.01796813199231552</v>
       </c>
       <c r="AJ7">
-        <v>0.55637707948244</v>
+        <v>-0.3816438742422106</v>
       </c>
       <c r="AK7">
-        <v>0.4723420949391919</v>
+        <v>-14.27240773286465</v>
       </c>
       <c r="AL7">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>2.989</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="AO7">
-        <v>7.587301587301587</v>
+        <v>0.05179153094462541</v>
       </c>
       <c r="AP7">
-        <v>4.37818181818182</v>
-      </c>
-      <c r="AQ7">
-        <v>7.995985279357645</v>
+        <v>-2.645276872964169</v>
       </c>
     </row>
     <row r="8">
@@ -1371,7 +1320,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FinTech Global Incorporated (TSE:8789)</t>
+          <t>SBI Holdings, Inc. (TSE:8473)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1380,115 +1329,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0161</v>
+        <v>0.261</v>
+      </c>
+      <c r="E8">
+        <v>0.505</v>
       </c>
       <c r="G8">
-        <v>0.100687757909216</v>
+        <v>0.271741752850916</v>
       </c>
       <c r="H8">
-        <v>0.100687757909216</v>
+        <v>0.2693130458559182</v>
       </c>
       <c r="I8">
-        <v>0.04058273847206845</v>
+        <v>0.1367152944204076</v>
       </c>
       <c r="J8">
-        <v>0.02029136923603423</v>
+        <v>0.1170028307859708</v>
       </c>
       <c r="K8">
-        <v>1.17</v>
+        <v>2059.9</v>
       </c>
       <c r="L8">
-        <v>0.01609353507565337</v>
+        <v>0.3313174529136442</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>282.893</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.05451152304609218</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.137333365697364</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>282.776</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.05448897795591182</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.1372765668236322</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.1170000000000186</v>
+      </c>
+      <c r="T8">
+        <v>0.0004135839345618966</v>
       </c>
       <c r="U8">
-        <v>21.3</v>
+        <v>26440.7</v>
       </c>
       <c r="V8">
-        <v>0.2652552926525529</v>
+        <v>5.094939879759519</v>
       </c>
       <c r="W8">
-        <v>0.01953255425709516</v>
+        <v>0.3778870319751977</v>
       </c>
       <c r="X8">
-        <v>0.04865783785878103</v>
+        <v>0.1867886339717466</v>
       </c>
       <c r="Y8">
-        <v>-0.02912528360168588</v>
+        <v>0.191098398003451</v>
       </c>
       <c r="Z8">
-        <v>0.6479606311029718</v>
+        <v>0.6019091322742102</v>
       </c>
       <c r="AA8">
-        <v>0.01314800841612416</v>
+        <v>0.07042507235200994</v>
       </c>
       <c r="AB8">
-        <v>0.03729604512937093</v>
+        <v>0.06855328045798961</v>
       </c>
       <c r="AC8">
-        <v>-0.02414803671324676</v>
+        <v>0.001871791894020328</v>
       </c>
       <c r="AD8">
-        <v>64.5</v>
+        <v>23968.3</v>
       </c>
       <c r="AE8">
-        <v>1.898174565403117</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>66.39817456540311</v>
+        <v>23968.3</v>
       </c>
       <c r="AG8">
-        <v>45.09817456540311</v>
+        <v>-2472.400000000001</v>
       </c>
       <c r="AH8">
-        <v>0.4526175922918557</v>
+        <v>0.8220173606466857</v>
       </c>
       <c r="AI8">
-        <v>0.4988661548680798</v>
+        <v>0.6676071951824142</v>
       </c>
       <c r="AJ8">
-        <v>0.3596398011510251</v>
+        <v>-0.9099072574709268</v>
       </c>
       <c r="AK8">
-        <v>0.4033891853844197</v>
+        <v>-0.2613226791810679</v>
       </c>
       <c r="AL8">
-        <v>1.11</v>
+        <v>91.3</v>
       </c>
       <c r="AM8">
-        <v>0.8950000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="AN8">
-        <v>7.127071823204419</v>
+        <v>20.43856058668031</v>
       </c>
       <c r="AO8">
-        <v>1.441441441441441</v>
+        <v>9.309967141292443</v>
       </c>
       <c r="AP8">
-        <v>4.983223708884322</v>
+        <v>-2.10829709218044</v>
       </c>
       <c r="AQ8">
-        <v>1.787709497206704</v>
+        <v>12.40875912408759</v>
       </c>
     </row>
     <row r="9">
@@ -1499,7 +1454,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mito Securities Co., Ltd. (TSE:8622)</t>
+          <t>FinTech Global Incorporated (TSE:8789)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1508,37 +1463,34 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0423</v>
-      </c>
-      <c r="E9">
-        <v>0.08119999999999999</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.1222395023328149</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.1222395023328149</v>
       </c>
       <c r="I9">
-        <v>0.01606921122086476</v>
+        <v>0.06731758871213177</v>
       </c>
       <c r="J9">
-        <v>0.01076774495483588</v>
+        <v>0.05180298818863265</v>
       </c>
       <c r="K9">
-        <v>15.7</v>
+        <v>1.22</v>
       </c>
       <c r="L9">
-        <v>0.1168154761904762</v>
+        <v>0.01897356143079316</v>
       </c>
       <c r="M9">
-        <v>1.24</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.007903123008285532</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.07898089171974522</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1550,76 +1502,76 @@
         <v>-0</v>
       </c>
       <c r="S9">
-        <v>1.24</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>266.4</v>
+        <v>16.4</v>
       </c>
       <c r="V9">
-        <v>1.697896749521988</v>
+        <v>0.191812865497076</v>
       </c>
       <c r="W9">
-        <v>0.04231805929919137</v>
+        <v>0.02125435540069686</v>
       </c>
       <c r="X9">
-        <v>0.04074789267127105</v>
+        <v>0.08916683435978956</v>
       </c>
       <c r="Y9">
-        <v>0.001570166627920318</v>
+        <v>-0.06791247895909269</v>
       </c>
       <c r="Z9">
-        <v>0.7456249041579436</v>
+        <v>0.6170979596817553</v>
       </c>
       <c r="AA9">
-        <v>0.008028698799946681</v>
+        <v>0.03196751831662328</v>
       </c>
       <c r="AB9">
-        <v>0.03613534327330292</v>
+        <v>0.07239339156205893</v>
       </c>
       <c r="AC9">
-        <v>-0.02810664447335624</v>
+        <v>-0.04042587324543565</v>
       </c>
       <c r="AD9">
-        <v>39.9</v>
+        <v>56.2</v>
       </c>
       <c r="AE9">
-        <v>5.95149005957888</v>
+        <v>4.757395229049637</v>
       </c>
       <c r="AF9">
-        <v>45.85149005957888</v>
+        <v>60.95739522904964</v>
       </c>
       <c r="AG9">
-        <v>-220.5485099404211</v>
+        <v>44.55739522904964</v>
       </c>
       <c r="AH9">
-        <v>0.2261462544423488</v>
+        <v>0.416212476903036</v>
       </c>
       <c r="AI9">
-        <v>0.1133951306889531</v>
+        <v>0.5293398231855153</v>
       </c>
       <c r="AJ9">
-        <v>3.465100913546413</v>
+        <v>0.3425979364770277</v>
       </c>
       <c r="AK9">
-        <v>-1.598739599298057</v>
+        <v>0.4511803407299974</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.822</v>
       </c>
       <c r="AM9">
-        <v>-2.45</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AN9">
-        <v>11.91044776119403</v>
+        <v>6.115342763873775</v>
+      </c>
+      <c r="AO9">
+        <v>4.805352798053528</v>
       </c>
       <c r="AP9">
-        <v>-65.83537610161824</v>
+        <v>4.848465204466772</v>
       </c>
       <c r="AQ9">
-        <v>-0</v>
+        <v>4.846625766871166</v>
       </c>
     </row>
     <row r="10">
@@ -1630,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Okasan Securities Group Inc. (TSE:8609)</t>
+          <t>Akatsuki Corp. (TSE:8737)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1639,118 +1591,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0124</v>
+        <v>0.242</v>
       </c>
       <c r="E10">
-        <v>-0.0617</v>
+        <v>-0.224</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.06952789699570815</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.06952789699570815</v>
       </c>
       <c r="I10">
-        <v>0.008727878192232624</v>
+        <v>0.02793991416309013</v>
       </c>
       <c r="J10">
-        <v>0.006484410066157045</v>
+        <v>0.01485921512985697</v>
       </c>
       <c r="K10">
-        <v>62.3</v>
+        <v>2.87</v>
       </c>
       <c r="L10">
-        <v>0.09769484083424806</v>
+        <v>0.01231759656652361</v>
       </c>
       <c r="M10">
-        <v>26.532</v>
+        <v>4.8268</v>
       </c>
       <c r="N10">
-        <v>0.04049450549450549</v>
+        <v>0.06722562674094708</v>
       </c>
       <c r="O10">
-        <v>0.4258747993579454</v>
+        <v>1.681811846689895</v>
       </c>
       <c r="P10">
-        <v>26.532</v>
+        <v>3.8068</v>
       </c>
       <c r="Q10">
-        <v>0.04049450549450549</v>
+        <v>0.05301949860724234</v>
       </c>
       <c r="R10">
-        <v>0.4258747993579454</v>
+        <v>1.326411149825784</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.2113201292781968</v>
       </c>
       <c r="U10">
-        <v>707</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V10">
-        <v>1.079059829059829</v>
+        <v>1.077994428969359</v>
       </c>
       <c r="W10">
-        <v>0.04052296084298165</v>
+        <v>0.02238689547581903</v>
       </c>
       <c r="X10">
-        <v>0.06583947903037486</v>
+        <v>0.1485955889985768</v>
       </c>
       <c r="Y10">
-        <v>-0.02531651818739321</v>
+        <v>-0.1262086935227578</v>
       </c>
       <c r="Z10">
-        <v>0.3783736277145501</v>
+        <v>0.9889643463497453</v>
       </c>
       <c r="AA10">
-        <v>0.002453529760320587</v>
+        <v>0.01469523397816924</v>
       </c>
       <c r="AB10">
-        <v>0.03557406954589156</v>
+        <v>0.06877917383277143</v>
       </c>
       <c r="AC10">
-        <v>-0.03312053978557097</v>
+        <v>-0.05408393985460219</v>
       </c>
       <c r="AD10">
-        <v>1245.5</v>
+        <v>221.9</v>
       </c>
       <c r="AE10">
-        <v>57.17116038406628</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1302.671160384066</v>
+        <v>221.9</v>
       </c>
       <c r="AG10">
-        <v>595.6711603840663</v>
+        <v>144.5</v>
       </c>
       <c r="AH10">
-        <v>0.6653508089513548</v>
+        <v>0.7555328566564522</v>
       </c>
       <c r="AI10">
-        <v>0.4301983313426629</v>
+        <v>0.6865717821782179</v>
       </c>
       <c r="AJ10">
-        <v>0.4762050475295729</v>
+        <v>0.6680536292186777</v>
       </c>
       <c r="AK10">
-        <v>0.2566363197091729</v>
+        <v>0.5878763222131814</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AM10">
-        <v>-12.3</v>
+        <v>1.49</v>
       </c>
       <c r="AN10">
-        <v>73.26470588235294</v>
+        <v>23.78349410503751</v>
+      </c>
+      <c r="AO10">
+        <v>2.384615384615385</v>
       </c>
       <c r="AP10">
-        <v>35.03948002259214</v>
+        <v>15.48767416934619</v>
       </c>
       <c r="AQ10">
-        <v>-0</v>
+        <v>4.369127516778524</v>
       </c>
     </row>
     <row r="11">
@@ -1761,7 +1716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tokai Tokyo Financial Holdings, Inc. (TSE:8616)</t>
+          <t>Mito Securities Co., Ltd. (TSE:8622)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1770,10 +1725,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0536</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="E11">
-        <v>0.126</v>
+        <v>-0.19</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1782,103 +1737,103 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.01274445624929131</v>
+        <v>0.01995891706814959</v>
       </c>
       <c r="J11">
-        <v>0.01012465303266729</v>
+        <v>0.01449204999437766</v>
       </c>
       <c r="K11">
-        <v>146.2</v>
+        <v>4.47</v>
       </c>
       <c r="L11">
-        <v>0.2160484705186936</v>
+        <v>0.05289940828402367</v>
       </c>
       <c r="M11">
-        <v>48.9348</v>
+        <v>0.477</v>
       </c>
       <c r="N11">
-        <v>0.05743521126760564</v>
+        <v>0.004462114125350795</v>
       </c>
       <c r="O11">
-        <v>0.3347113543091656</v>
+        <v>0.1067114093959732</v>
       </c>
       <c r="P11">
-        <v>48.9348</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.05743521126760564</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.3347113543091656</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>740</v>
+        <v>160.4</v>
       </c>
       <c r="V11">
-        <v>0.8685446009389671</v>
+        <v>1.500467726847521</v>
       </c>
       <c r="W11">
-        <v>0.09712349697734671</v>
+        <v>0.01246861924686192</v>
       </c>
       <c r="X11">
-        <v>0.1639651316953251</v>
+        <v>0.08022381748483012</v>
       </c>
       <c r="Y11">
-        <v>-0.06684163471797838</v>
+        <v>-0.0677551982379682</v>
       </c>
       <c r="Z11">
-        <v>0.1034855193385615</v>
+        <v>0.5973109378033021</v>
       </c>
       <c r="AA11">
-        <v>0.001047754977208316</v>
+        <v>0.008656259972834061</v>
       </c>
       <c r="AB11">
-        <v>0.03527924297197178</v>
+        <v>0.07045575879337379</v>
       </c>
       <c r="AC11">
-        <v>-0.03423148799476346</v>
+        <v>-0.06179949882053973</v>
       </c>
       <c r="AD11">
-        <v>7309.4</v>
+        <v>28.5</v>
       </c>
       <c r="AE11">
-        <v>35.37913228052284</v>
+        <v>9.467357538706796</v>
       </c>
       <c r="AF11">
-        <v>7344.779132280522</v>
+        <v>37.96735753870679</v>
       </c>
       <c r="AG11">
-        <v>6604.779132280522</v>
+        <v>-122.4326424612932</v>
       </c>
       <c r="AH11">
-        <v>0.8960567332301712</v>
+        <v>0.2620835927690776</v>
       </c>
       <c r="AI11">
-        <v>0.816070327526854</v>
+        <v>0.1238871175176023</v>
       </c>
       <c r="AJ11">
-        <v>0.8857415534393828</v>
+        <v>7.88228035032616</v>
       </c>
       <c r="AK11">
-        <v>0.7995927238998065</v>
+        <v>-0.8381930400079254</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-6.63</v>
+        <v>-1.98</v>
       </c>
       <c r="AN11">
-        <v>465.5668789808917</v>
+        <v>7.960893854748603</v>
       </c>
       <c r="AP11">
-        <v>420.6865689350652</v>
+        <v>-34.19906214002604</v>
       </c>
       <c r="AQ11">
         <v>-0</v>
@@ -1892,7 +1847,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GMO Financial Holdings, Inc. (JASDAQ:7177)</t>
+          <t>Okasan Securities Group Inc. (TSE:8609)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1900,104 +1855,119 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D12">
+        <v>-0.0295</v>
+      </c>
+      <c r="E12">
+        <v>0.0152</v>
+      </c>
       <c r="G12">
-        <v>0.0004541607898448519</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.01683895030475693</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.01275479504277308</v>
       </c>
       <c r="K12">
-        <v>79.7</v>
+        <v>52.6</v>
       </c>
       <c r="L12">
-        <v>0.2248236953455571</v>
+        <v>0.1102263202011735</v>
       </c>
       <c r="M12">
-        <v>48.0105</v>
+        <v>22.6582</v>
       </c>
       <c r="N12">
-        <v>0.05764257413855205</v>
+        <v>0.03581757824849826</v>
       </c>
       <c r="O12">
-        <v>0.6023902132998745</v>
+        <v>0.4307642585551331</v>
       </c>
       <c r="P12">
-        <v>48.0105</v>
+        <v>22.6512</v>
       </c>
       <c r="Q12">
-        <v>0.05764257413855205</v>
+        <v>0.03580651280429972</v>
       </c>
       <c r="R12">
-        <v>0.6023902132998745</v>
+        <v>0.4306311787072243</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>0.00700000000000145</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.0003089389271875722</v>
       </c>
       <c r="U12">
-        <v>681.7</v>
+        <v>566.4</v>
       </c>
       <c r="V12">
-        <v>0.8184656021130989</v>
+        <v>0.8953525134366107</v>
       </c>
       <c r="W12">
-        <v>0.220104943385805</v>
+        <v>0.0345370978332239</v>
       </c>
       <c r="X12">
-        <v>0.06617209208404265</v>
+        <v>0.1276877684991462</v>
       </c>
       <c r="Y12">
-        <v>0.1539328513017624</v>
+        <v>-0.09315067066592231</v>
       </c>
       <c r="Z12">
-        <v>0.3944147752558967</v>
+        <v>0.2265560251753657</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.002889675666817129</v>
       </c>
       <c r="AB12">
-        <v>0.03557087608504555</v>
+        <v>0.06899268664881975</v>
       </c>
       <c r="AC12">
-        <v>-0.03557087608504555</v>
+        <v>-0.06610301098200262</v>
       </c>
       <c r="AD12">
-        <v>1674.7</v>
+        <v>1381.1</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>44.82226457284996</v>
       </c>
       <c r="AF12">
-        <v>1674.7</v>
+        <v>1425.92226457285</v>
       </c>
       <c r="AG12">
-        <v>993</v>
+        <v>859.5222645728498</v>
       </c>
       <c r="AH12">
-        <v>0.6678497368001276</v>
+        <v>0.6926921749222534</v>
       </c>
       <c r="AI12">
-        <v>0.8180841189976065</v>
+        <v>0.5271388273759799</v>
       </c>
       <c r="AJ12">
-        <v>0.543841393285503</v>
+        <v>0.5760401040721053</v>
       </c>
       <c r="AK12">
-        <v>0.7272594111615643</v>
+        <v>0.4019046648915925</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>-10.6</v>
+      </c>
+      <c r="AN12">
+        <v>81.24117647058823</v>
+      </c>
+      <c r="AP12">
+        <v>50.56013321016763</v>
+      </c>
+      <c r="AQ12">
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -2008,7 +1978,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toyo Securities Co., Ltd. (TSE:8614)</t>
+          <t>Tokai Tokyo Financial Holdings, Inc. (TSE:8616)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2017,10 +1987,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0379</v>
+        <v>0.00229</v>
       </c>
       <c r="E13">
-        <v>-0.117</v>
+        <v>-0.303</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2029,34 +1999,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.02084632254999479</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.01333445804491046</v>
       </c>
       <c r="K13">
-        <v>11.1</v>
+        <v>28</v>
       </c>
       <c r="L13">
-        <v>0.1000901713255185</v>
+        <v>0.05372217958557175</v>
       </c>
       <c r="M13">
-        <v>4.2606</v>
+        <v>37.7872</v>
       </c>
       <c r="N13">
-        <v>0.04197635467980296</v>
+        <v>0.0567801652892562</v>
       </c>
       <c r="O13">
-        <v>0.3838378378378379</v>
+        <v>1.349542857142857</v>
       </c>
       <c r="P13">
-        <v>4.2606</v>
+        <v>37.7872</v>
       </c>
       <c r="Q13">
-        <v>0.04197635467980296</v>
+        <v>0.0567801652892562</v>
       </c>
       <c r="R13">
-        <v>0.3838378378378379</v>
+        <v>1.349542857142857</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2065,61 +2035,67 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>338.5</v>
+        <v>554.3</v>
       </c>
       <c r="V13">
-        <v>3.334975369458128</v>
+        <v>0.8329075882794891</v>
       </c>
       <c r="W13">
-        <v>0.03162393162393162</v>
+        <v>0.01811711420252346</v>
       </c>
       <c r="X13">
-        <v>0.056903884659653</v>
+        <v>0.2612923696305705</v>
       </c>
       <c r="Y13">
-        <v>-0.02527995303572138</v>
+        <v>-0.243175255428047</v>
       </c>
       <c r="Z13">
-        <v>0.6717141126589945</v>
+        <v>0.06406825174880808</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.0008543154149552424</v>
       </c>
       <c r="AB13">
-        <v>0.03568240280969764</v>
+        <v>0.06834366747012501</v>
       </c>
       <c r="AC13">
-        <v>-0.03568240280969764</v>
+        <v>-0.06748935205516976</v>
       </c>
       <c r="AD13">
-        <v>140.5</v>
+        <v>5037.1</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>20.17448343471359</v>
       </c>
       <c r="AF13">
-        <v>140.5</v>
+        <v>5057.274483434714</v>
       </c>
       <c r="AG13">
-        <v>-198</v>
+        <v>4502.974483434714</v>
       </c>
       <c r="AH13">
-        <v>0.5805785123966942</v>
+        <v>0.8837102524437451</v>
       </c>
       <c r="AI13">
-        <v>0.287262318544265</v>
+        <v>0.799130105789718</v>
       </c>
       <c r="AJ13">
-        <v>2.051813471502591</v>
+        <v>0.8712386020027826</v>
       </c>
       <c r="AK13">
-        <v>-1.314741035856573</v>
+        <v>0.7798473178032822</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-2.89</v>
+        <v>-5.07</v>
+      </c>
+      <c r="AN13">
+        <v>338.0604026845638</v>
+      </c>
+      <c r="AP13">
+        <v>302.213052579511</v>
       </c>
       <c r="AQ13">
         <v>-0</v>
@@ -2133,7 +2109,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kyokuto Securities Co., Ltd. (TSE:8706)</t>
+          <t>GMO Financial Holdings, Inc. (TSE:7177)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2141,12 +2117,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.0552</v>
-      </c>
-      <c r="E14">
-        <v>-0.0459</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2154,34 +2124,34 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.001996228418276866</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0.001378217976454165</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>25.2</v>
+        <v>31.8</v>
       </c>
       <c r="L14">
-        <v>0.3529411764705882</v>
+        <v>0.103515625</v>
       </c>
       <c r="M14">
-        <v>14.2912</v>
+        <v>25.014</v>
       </c>
       <c r="N14">
-        <v>0.06897297297297297</v>
+        <v>0.05675970047651464</v>
       </c>
       <c r="O14">
-        <v>0.5671111111111111</v>
+        <v>0.7866037735849056</v>
       </c>
       <c r="P14">
-        <v>14.2912</v>
+        <v>25.014</v>
       </c>
       <c r="Q14">
-        <v>0.06897297297297297</v>
+        <v>0.05675970047651464</v>
       </c>
       <c r="R14">
-        <v>0.5671111111111111</v>
+        <v>0.7866037735849056</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2190,70 +2160,61 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>193.5</v>
+        <v>417.4</v>
       </c>
       <c r="V14">
-        <v>0.9338803088803089</v>
+        <v>0.9471295665985932</v>
       </c>
       <c r="W14">
-        <v>0.06022944550669216</v>
+        <v>0.09031525134904857</v>
       </c>
       <c r="X14">
-        <v>0.04362342294320855</v>
+        <v>0.1507057023259479</v>
       </c>
       <c r="Y14">
-        <v>0.01660602256348361</v>
+        <v>-0.06039045097689931</v>
       </c>
       <c r="Z14">
-        <v>0.2289765336313969</v>
+        <v>0.2571356825981418</v>
       </c>
       <c r="AA14">
-        <v>0.0003155795748369529</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.03600604810821957</v>
+        <v>0.06876237820743114</v>
       </c>
       <c r="AC14">
-        <v>-0.03569046853338262</v>
+        <v>-0.06876237820743114</v>
       </c>
       <c r="AD14">
-        <v>100</v>
+        <v>1399.2</v>
       </c>
       <c r="AE14">
-        <v>0.8223464546751589</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>100.8223464546752</v>
+        <v>1399.2</v>
       </c>
       <c r="AG14">
-        <v>-92.67765354532484</v>
+        <v>981.8000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.3273215323989844</v>
+        <v>0.7604761128322192</v>
       </c>
       <c r="AI14">
-        <v>0.194516688590218</v>
+        <v>0.8252919664975816</v>
       </c>
       <c r="AJ14">
-        <v>-0.8092538828830595</v>
+        <v>0.6901933216168717</v>
       </c>
       <c r="AK14">
-        <v>-0.2853179732148042</v>
+        <v>0.7682316118935838</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-3.98</v>
-      </c>
-      <c r="AN14">
-        <v>325.7328990228013</v>
-      </c>
-      <c r="AP14">
-        <v>-301.8816076394946</v>
-      </c>
-      <c r="AQ14">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2264,7 +2225,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Matsui Securities Co., Ltd. (TSE:8628)</t>
+          <t>HS Holdings Co., Ltd. (TSE:8699)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2273,10 +2234,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0133</v>
+        <v>0.0775</v>
       </c>
       <c r="E15">
-        <v>-0.00091</v>
+        <v>0.165</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2291,94 +2252,91 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>100.3</v>
+        <v>80.7</v>
       </c>
       <c r="L15">
-        <v>0.3732787495347972</v>
+        <v>0.1840784671532847</v>
       </c>
       <c r="M15">
-        <v>92.2989</v>
+        <v>68.6528</v>
       </c>
       <c r="N15">
-        <v>0.05226734243162127</v>
+        <v>0.2400447552447552</v>
       </c>
       <c r="O15">
-        <v>0.9202283150548356</v>
+        <v>0.850716232961586</v>
       </c>
       <c r="P15">
-        <v>92.2989</v>
+        <v>2.1528</v>
       </c>
       <c r="Q15">
-        <v>0.05226734243162127</v>
+        <v>0.007527272727272727</v>
       </c>
       <c r="R15">
-        <v>0.9202283150548356</v>
+        <v>0.02667657992565056</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>0.9686422112426587</v>
       </c>
       <c r="U15">
-        <v>458.2</v>
+        <v>706.4</v>
       </c>
       <c r="V15">
-        <v>0.2594710912282688</v>
+        <v>2.46993006993007</v>
       </c>
       <c r="W15">
-        <v>0.1327070653612067</v>
+        <v>0.1511802173098539</v>
       </c>
       <c r="X15">
-        <v>0.05315618116692356</v>
+        <v>0.1195193997199579</v>
       </c>
       <c r="Y15">
-        <v>0.07955088419428311</v>
+        <v>0.03166081758989603</v>
       </c>
       <c r="Z15">
-        <v>0.1456842333550206</v>
+        <v>1.588981515041682</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03574611840041498</v>
+        <v>0.06910925129187688</v>
       </c>
       <c r="AC15">
-        <v>-0.03574611840041498</v>
+        <v>-0.06910925129187688</v>
       </c>
       <c r="AD15">
-        <v>1997.1</v>
+        <v>551.2</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>1997.1</v>
+        <v>551.2</v>
       </c>
       <c r="AG15">
-        <v>1538.9</v>
+        <v>-155.1999999999999</v>
       </c>
       <c r="AH15">
-        <v>0.5307201700770662</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="AI15">
-        <v>0.7385998002884723</v>
+        <v>0.4746404891070352</v>
       </c>
       <c r="AJ15">
-        <v>0.4656560154926168</v>
+        <v>-1.186544342507644</v>
       </c>
       <c r="AK15">
-        <v>0.6852651734425792</v>
+        <v>-0.341173884370191</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1.04</v>
-      </c>
-      <c r="AQ15">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2389,7 +2347,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HS Holdings Co.,Ltd. (JASDAQ:8699)</t>
+          <t>Matsui Securities Co., Ltd. (TSE:8628)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2398,10 +2356,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0333</v>
+        <v>0.00945</v>
       </c>
       <c r="E16">
-        <v>-0.483</v>
+        <v>-0.0443</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2410,34 +2368,34 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>1.435615841958822e-05</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>7.178079209794111e-06</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>-4.67</v>
+        <v>61.5</v>
       </c>
       <c r="L16">
-        <v>-0.009245693921995644</v>
+        <v>0.3101361573373676</v>
       </c>
       <c r="M16">
-        <v>4.2768</v>
+        <v>71</v>
       </c>
       <c r="N16">
-        <v>0.01015625742104013</v>
+        <v>0.04638400731691383</v>
       </c>
       <c r="O16">
-        <v>-0.9158029978586724</v>
+        <v>1.154471544715447</v>
       </c>
       <c r="P16">
-        <v>4.2768</v>
+        <v>71</v>
       </c>
       <c r="Q16">
-        <v>0.01015625742104013</v>
+        <v>0.04638400731691383</v>
       </c>
       <c r="R16">
-        <v>-0.9158029978586724</v>
+        <v>1.154471544715447</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2446,67 +2404,64 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>747</v>
+        <v>429.4</v>
       </c>
       <c r="V16">
-        <v>1.773925433388744</v>
+        <v>0.2805252498856732</v>
       </c>
       <c r="W16">
-        <v>-0.008366176997491937</v>
+        <v>0.08701188455008489</v>
       </c>
       <c r="X16">
-        <v>0.05360857531923398</v>
+        <v>0.1004535044074719</v>
       </c>
       <c r="Y16">
-        <v>-0.06197475231672592</v>
+        <v>-0.01344161985738697</v>
       </c>
       <c r="Z16">
-        <v>-7.715896566582099</v>
+        <v>0.08830208843567708</v>
       </c>
       <c r="AA16">
-        <v>-5.538531672950474e-05</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03573763458843433</v>
+        <v>0.06951828350877937</v>
       </c>
       <c r="AC16">
-        <v>-0.03579301990516384</v>
+        <v>-0.06951828350877937</v>
       </c>
       <c r="AD16">
-        <v>489.1</v>
+        <v>1782.5</v>
       </c>
       <c r="AE16">
-        <v>0.008743521911329936</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>489.1087435219114</v>
+        <v>1782.5</v>
       </c>
       <c r="AG16">
-        <v>-257.8912564780886</v>
+        <v>1353.1</v>
       </c>
       <c r="AH16">
-        <v>0.537358871800529</v>
+        <v>0.5379995170831825</v>
       </c>
       <c r="AI16">
-        <v>0.41625966293313</v>
+        <v>0.7689155379173497</v>
       </c>
       <c r="AJ16">
-        <v>-1.580131376009679</v>
+        <v>0.4692072959289825</v>
       </c>
       <c r="AK16">
-        <v>-0.6025373555596212</v>
+        <v>0.7163807708598051</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>54344.44444444445</v>
-      </c>
-      <c r="AP16">
-        <v>-28654.58405312096</v>
+        <v>-0.131</v>
+      </c>
+      <c r="AQ16">
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -2517,7 +2472,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INV Inc. (JASDAQ:7338)</t>
+          <t>INV Inc. (TSE:7338)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2526,7 +2481,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0228</v>
+        <v>0.0767</v>
+      </c>
+      <c r="E17">
+        <v>0.291</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2541,28 +2499,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>1.96</v>
+        <v>3.27</v>
       </c>
       <c r="L17">
-        <v>0.05226666666666666</v>
+        <v>0.08605263157894737</v>
       </c>
       <c r="M17">
-        <v>1.00548</v>
+        <v>1.74636</v>
       </c>
       <c r="N17">
-        <v>0.0216698275862069</v>
+        <v>0.05151504424778761</v>
       </c>
       <c r="O17">
-        <v>0.5130000000000001</v>
+        <v>0.5340550458715596</v>
       </c>
       <c r="P17">
-        <v>1.00548</v>
+        <v>1.74636</v>
       </c>
       <c r="Q17">
-        <v>0.0216698275862069</v>
+        <v>0.05151504424778761</v>
       </c>
       <c r="R17">
-        <v>0.5130000000000001</v>
+        <v>0.5340550458715596</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2571,55 +2529,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>77.8</v>
+        <v>57.5</v>
       </c>
       <c r="V17">
-        <v>1.676724137931034</v>
+        <v>1.696165191740413</v>
       </c>
       <c r="W17">
-        <v>0.01946375372393247</v>
+        <v>0.032897384305835</v>
       </c>
       <c r="X17">
-        <v>0.04787120420714525</v>
+        <v>0.09508828344053563</v>
       </c>
       <c r="Y17">
-        <v>-0.02840745048321278</v>
+        <v>-0.06219089913470063</v>
       </c>
       <c r="Z17">
-        <v>0.6432246998284733</v>
+        <v>0.6608695652173912</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.03586689729703722</v>
+        <v>0.06969108574180394</v>
       </c>
       <c r="AC17">
-        <v>-0.03586689729703722</v>
+        <v>-0.06969108574180394</v>
       </c>
       <c r="AD17">
-        <v>35.9</v>
+        <v>32.2</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>35.9</v>
+        <v>32.2</v>
       </c>
       <c r="AG17">
-        <v>-41.9</v>
+        <v>-25.3</v>
       </c>
       <c r="AH17">
-        <v>0.4362089914945322</v>
+        <v>0.48714069591528</v>
       </c>
       <c r="AI17">
-        <v>0.2653362897265336</v>
+        <v>0.2809773123909249</v>
       </c>
       <c r="AJ17">
-        <v>-9.31111111111111</v>
+        <v>-2.941860465116278</v>
       </c>
       <c r="AK17">
-        <v>-0.728695652173913</v>
+        <v>-0.4430823117338002</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2636,7 +2594,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maruhachi Securities Co., Ltd. (JASDAQ:8700)</t>
+          <t>Kyokuto Securities Co., Ltd. (TSE:8706)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2645,7 +2603,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.06809999999999999</v>
+        <v>-0.08119999999999999</v>
+      </c>
+      <c r="E18">
+        <v>-0.163</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2654,100 +2615,103 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0.0008240108656515923</v>
+        <v>0.005265779741080137</v>
       </c>
       <c r="J18">
-        <v>0.0005694830649281005</v>
+        <v>0.003508879397560876</v>
       </c>
       <c r="K18">
-        <v>3.11</v>
+        <v>7.1</v>
       </c>
       <c r="L18">
-        <v>0.1178030303030303</v>
+        <v>0.2005649717514124</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>7.719799999999999</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.05549820273184759</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>1.087295774647887</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>7.719799999999999</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.05549820273184759</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>1.087295774647887</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>41</v>
+        <v>153.7</v>
       </c>
       <c r="V18">
-        <v>0.8488612836438924</v>
+        <v>1.104960460100647</v>
       </c>
       <c r="W18">
-        <v>0.04769938650306748</v>
+        <v>0.01701006229036895</v>
       </c>
       <c r="X18">
-        <v>0.03643237761249451</v>
+        <v>0.08496132374048139</v>
       </c>
       <c r="Y18">
-        <v>0.01126700889057297</v>
+        <v>-0.06795126145011243</v>
       </c>
       <c r="Z18">
-        <v>0.8508929224923863</v>
+        <v>0.109135317584858</v>
       </c>
       <c r="AA18">
-        <v>0.0004845691094265928</v>
+        <v>0.0003829426674197716</v>
       </c>
       <c r="AB18">
-        <v>0.03642364925985631</v>
+        <v>0.07014812537755062</v>
       </c>
       <c r="AC18">
-        <v>-0.03593908015042972</v>
+        <v>-0.06976518271013085</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>75.3</v>
       </c>
       <c r="AE18">
-        <v>0.02623056573398981</v>
+        <v>0.4679569858288159</v>
       </c>
       <c r="AF18">
-        <v>0.02623056573398981</v>
+        <v>75.76795698582882</v>
       </c>
       <c r="AG18">
-        <v>-40.97376943426601</v>
+        <v>-77.93204301417117</v>
       </c>
       <c r="AH18">
-        <v>0.000542781123769019</v>
+        <v>0.3526256685673516</v>
       </c>
       <c r="AI18">
-        <v>0.0004009181868980799</v>
+        <v>0.1932028245453178</v>
       </c>
       <c r="AJ18">
-        <v>-5.59274910428116</v>
+        <v>-1.274066469675065</v>
       </c>
       <c r="AK18">
-        <v>-1.67744954850895</v>
+        <v>-0.3268029969276013</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-0.242</v>
+        <v>-3.54</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>268.9285714285714</v>
       </c>
       <c r="AP18">
-        <v>-1517.547016083926</v>
+        <v>-278.3287250506113</v>
       </c>
       <c r="AQ18">
         <v>-0</v>
@@ -2761,7 +2725,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aizawa Securities Group Co.,Ltd. (TSE:8708)</t>
+          <t>Aizawa Securities Group Co., Ltd. (TSE:8708)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2770,10 +2734,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0989</v>
+        <v>-0.0124</v>
       </c>
       <c r="E19">
-        <v>0.322</v>
+        <v>0.199</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2788,91 +2752,91 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>51.6</v>
+        <v>-5.77</v>
       </c>
       <c r="L19">
-        <v>0.3491204330175913</v>
+        <v>-0.06347634763476347</v>
       </c>
       <c r="M19">
-        <v>24.095</v>
+        <v>13.1502</v>
       </c>
       <c r="N19">
-        <v>0.06967900520532098</v>
+        <v>0.06601506024096385</v>
       </c>
       <c r="O19">
-        <v>0.4669573643410853</v>
+        <v>-2.279064124783362</v>
       </c>
       <c r="P19">
-        <v>11.895</v>
+        <v>7.430199999999999</v>
       </c>
       <c r="Q19">
-        <v>0.0343984962406015</v>
+        <v>0.03730020080321285</v>
       </c>
       <c r="R19">
-        <v>0.2305232558139535</v>
+        <v>-1.287729636048527</v>
       </c>
       <c r="S19">
-        <v>12.2</v>
+        <v>5.719999999999999</v>
       </c>
       <c r="T19">
-        <v>0.5063291139240507</v>
+        <v>0.4349743730133382</v>
       </c>
       <c r="U19">
-        <v>372.8</v>
+        <v>146.8</v>
       </c>
       <c r="V19">
-        <v>1.07807981492192</v>
+        <v>0.7369477911646587</v>
       </c>
       <c r="W19">
-        <v>0.1048354327509143</v>
+        <v>-0.01110469591993841</v>
       </c>
       <c r="X19">
-        <v>0.0448742525206083</v>
+        <v>0.08157281255806598</v>
       </c>
       <c r="Y19">
-        <v>0.05996118023030596</v>
+        <v>-0.09267750847800439</v>
       </c>
       <c r="Z19">
-        <v>0.3865709742216271</v>
+        <v>0.2656574217494228</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03595978989239257</v>
+        <v>0.07035973352695506</v>
       </c>
       <c r="AC19">
-        <v>-0.03595978989239257</v>
+        <v>-0.07035973352695506</v>
       </c>
       <c r="AD19">
-        <v>197.5</v>
+        <v>81.5</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>197.5</v>
+        <v>81.5</v>
       </c>
       <c r="AG19">
-        <v>-175.3</v>
+        <v>-65.30000000000001</v>
       </c>
       <c r="AH19">
-        <v>0.3635192343088534</v>
+        <v>0.2903455646597791</v>
       </c>
       <c r="AI19">
-        <v>0.2691835900231702</v>
+        <v>0.1748176748176748</v>
       </c>
       <c r="AJ19">
-        <v>-1.028152492668622</v>
+        <v>-0.487677371172517</v>
       </c>
       <c r="AK19">
-        <v>-0.485730119146578</v>
+        <v>-0.204445835942392</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-13.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AQ19">
         <v>-0</v>
@@ -2895,10 +2859,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0736</v>
+        <v>0.0179</v>
       </c>
       <c r="E20">
-        <v>0.188</v>
+        <v>-0.0471</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2913,28 +2877,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>40.1</v>
+        <v>26</v>
       </c>
       <c r="L20">
-        <v>0.2030379746835443</v>
+        <v>0.1893663510560815</v>
       </c>
       <c r="M20">
-        <v>24.675</v>
+        <v>9.7525</v>
       </c>
       <c r="N20">
-        <v>0.0892727930535456</v>
+        <v>0.04218209342560553</v>
       </c>
       <c r="O20">
-        <v>0.6153366583541147</v>
+        <v>0.3750961538461538</v>
       </c>
       <c r="P20">
-        <v>24.675</v>
+        <v>9.7525</v>
       </c>
       <c r="Q20">
-        <v>0.0892727930535456</v>
+        <v>0.04218209342560553</v>
       </c>
       <c r="R20">
-        <v>0.6153366583541147</v>
+        <v>0.3750961538461538</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2943,55 +2907,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>132.6</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="V20">
-        <v>0.4797395079594791</v>
+        <v>0.365916955017301</v>
       </c>
       <c r="W20">
-        <v>0.07741312741312742</v>
+        <v>0.05165905026822968</v>
       </c>
       <c r="X20">
-        <v>0.04112400279315605</v>
+        <v>0.08075198581698241</v>
       </c>
       <c r="Y20">
-        <v>0.03628912461997136</v>
+        <v>-0.02909293554875273</v>
       </c>
       <c r="Z20">
-        <v>0.3679895658654742</v>
+        <v>0.2994547437295529</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.03611626364396167</v>
+        <v>0.07041726521824627</v>
       </c>
       <c r="AC20">
-        <v>-0.03611626364396167</v>
+        <v>-0.07041726521824627</v>
       </c>
       <c r="AD20">
-        <v>87.8</v>
+        <v>87</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>87.8</v>
+        <v>87</v>
       </c>
       <c r="AG20">
-        <v>-44.8</v>
+        <v>2.400000000000006</v>
       </c>
       <c r="AH20">
-        <v>0.2410763316858869</v>
+        <v>0.2734129478315525</v>
       </c>
       <c r="AI20">
-        <v>0.1485366266283201</v>
+        <v>0.1834668916069169</v>
       </c>
       <c r="AJ20">
-        <v>-0.1934369602763385</v>
+        <v>0.01027397260273975</v>
       </c>
       <c r="AK20">
-        <v>-0.09770992366412214</v>
+        <v>0.006160164271047242</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3008,7 +2972,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Traders Holdings Co.,Ltd. (JASDAQ:8704)</t>
+          <t>Traders Holdings Co.,Ltd. (TSE:8704)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3017,10 +2981,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.171</v>
+        <v>0.374</v>
       </c>
       <c r="G21">
-        <v>0.004593639575971731</v>
+        <v>0.007527675276752767</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3032,85 +2996,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="L21">
-        <v>0.3215547703180212</v>
+        <v>0.3468634686346864</v>
       </c>
       <c r="M21">
-        <v>2.637</v>
+        <v>4.261200000000001</v>
       </c>
       <c r="N21">
-        <v>0.02749739311783107</v>
+        <v>0.0517764277035237</v>
       </c>
       <c r="O21">
-        <v>0.1448901098901099</v>
+        <v>0.2266595744680851</v>
       </c>
       <c r="P21">
-        <v>2.619</v>
+        <v>2.1812</v>
       </c>
       <c r="Q21">
-        <v>0.02730969760166841</v>
+        <v>0.02650303766707169</v>
       </c>
       <c r="R21">
-        <v>0.1439010989010989</v>
+        <v>0.1160212765957447</v>
       </c>
       <c r="S21">
-        <v>0.01799999999999979</v>
+        <v>2.080000000000001</v>
       </c>
       <c r="T21">
-        <v>0.006825938566552823</v>
+        <v>0.4881254106824369</v>
       </c>
       <c r="U21">
-        <v>42.2</v>
+        <v>25.3</v>
       </c>
       <c r="V21">
-        <v>0.4400417101147028</v>
+        <v>0.307411907654921</v>
       </c>
       <c r="W21">
-        <v>0.3074324324324324</v>
+        <v>0.2625698324022347</v>
       </c>
       <c r="X21">
-        <v>0.03904699247760472</v>
+        <v>0.07581080468316508</v>
       </c>
       <c r="Y21">
-        <v>0.2683854399548277</v>
+        <v>0.1867590277190696</v>
       </c>
       <c r="Z21">
-        <v>1.322429906542056</v>
+        <v>1.168103448275862</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.03623191729351311</v>
+        <v>0.07083132933805628</v>
       </c>
       <c r="AC21">
-        <v>-0.03623191729351311</v>
+        <v>-0.07083132933805628</v>
       </c>
       <c r="AD21">
-        <v>17</v>
+        <v>14.7</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>17</v>
+        <v>14.7</v>
       </c>
       <c r="AG21">
-        <v>-25.2</v>
+        <v>-10.6</v>
       </c>
       <c r="AH21">
-        <v>0.1505757307351639</v>
+        <v>0.1515463917525773</v>
       </c>
       <c r="AI21">
-        <v>0.1918735891647856</v>
+        <v>0.1715285880980163</v>
       </c>
       <c r="AJ21">
-        <v>-0.3564356435643565</v>
+        <v>-0.1478382147838215</v>
       </c>
       <c r="AK21">
-        <v>-0.5431034482758622</v>
+        <v>-0.1754966887417219</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3127,7 +3091,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Marusan Securities Co., Ltd. (TSE:8613)</t>
+          <t>Kobayashi Yoko Co., Ltd. (TSE:8742)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3136,46 +3100,43 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0441</v>
-      </c>
-      <c r="E22">
-        <v>0.186</v>
+        <v>0.0512</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>-0.03330882352941177</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>-0.03330882352941177</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>0.001029411764705882</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>0.0005494995200877555</v>
       </c>
       <c r="K22">
-        <v>32.8</v>
+        <v>0.166</v>
       </c>
       <c r="L22">
-        <v>0.18458075407991</v>
+        <v>0.006102941176470589</v>
       </c>
       <c r="M22">
-        <v>18.487</v>
+        <v>0.2125</v>
       </c>
       <c r="N22">
-        <v>0.06166444296197465</v>
+        <v>0.01011904761904762</v>
       </c>
       <c r="O22">
-        <v>0.5636280487804879</v>
+        <v>1.280120481927711</v>
       </c>
       <c r="P22">
-        <v>18.487</v>
+        <v>0.2125</v>
       </c>
       <c r="Q22">
-        <v>0.06166444296197465</v>
+        <v>0.01011904761904762</v>
       </c>
       <c r="R22">
-        <v>0.5636280487804879</v>
+        <v>1.280120481927711</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3184,61 +3145,73 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>364.8</v>
+        <v>18.9</v>
       </c>
       <c r="V22">
-        <v>1.216811207471648</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="W22">
-        <v>0.07656395891690009</v>
+        <v>0.002381635581061693</v>
       </c>
       <c r="X22">
-        <v>0.03776663559784027</v>
+        <v>0.0715842886485451</v>
       </c>
       <c r="Y22">
-        <v>0.03879732331905981</v>
+        <v>-0.06920265306748341</v>
       </c>
       <c r="Z22">
-        <v>1.273835125448029</v>
+        <v>0.6188850967007963</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>0.0003400770636265517</v>
       </c>
       <c r="AB22">
-        <v>0.03631804393385031</v>
+        <v>0.07131418254999124</v>
       </c>
       <c r="AC22">
-        <v>-0.03631804393385031</v>
+        <v>-0.07097410548636468</v>
       </c>
       <c r="AD22">
-        <v>27.2</v>
+        <v>0.2</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>27.2</v>
+        <v>0.2</v>
       </c>
       <c r="AG22">
-        <v>-337.6</v>
+        <v>-18.7</v>
       </c>
       <c r="AH22">
-        <v>0.08318042813455657</v>
+        <v>0.009433962264150945</v>
       </c>
       <c r="AI22">
-        <v>0.06047132058692752</v>
+        <v>0.003316749585406302</v>
       </c>
       <c r="AJ22">
-        <v>8.931216931216929</v>
+        <v>-8.130434782608694</v>
       </c>
       <c r="AK22">
-        <v>-3.971764705882353</v>
+        <v>-0.4516908212560385</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>-0.256</v>
+      </c>
+      <c r="AN22">
+        <v>0.8264462809917356</v>
+      </c>
+      <c r="AO22">
+        <v>4</v>
+      </c>
+      <c r="AP22">
+        <v>-77.27272727272727</v>
+      </c>
+      <c r="AQ22">
+        <v>-0.109375</v>
       </c>
     </row>
     <row r="23">
@@ -3249,7 +3222,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ichiyoshi Securities Co., Ltd. (TSE:8624)</t>
+          <t>Marusan Securities Co., Ltd. (TSE:8613)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3258,10 +3231,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0187</v>
+        <v>-0.00291</v>
       </c>
       <c r="E23">
-        <v>0.0625</v>
+        <v>0.0611</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3276,94 +3249,91 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>25.6</v>
+        <v>12.4</v>
       </c>
       <c r="L23">
-        <v>0.1357370095440085</v>
+        <v>0.1083916083916084</v>
       </c>
       <c r="M23">
-        <v>12.3101</v>
+        <v>10.7505</v>
       </c>
       <c r="N23">
-        <v>0.05958422071636012</v>
+        <v>0.05410417715148465</v>
       </c>
       <c r="O23">
-        <v>0.4808632812500001</v>
+        <v>0.8669758064516129</v>
       </c>
       <c r="P23">
-        <v>12.3101</v>
+        <v>7.2705</v>
       </c>
       <c r="Q23">
-        <v>0.05958422071636012</v>
+        <v>0.03659033719174636</v>
       </c>
       <c r="R23">
-        <v>0.4808632812500001</v>
+        <v>0.5863306451612903</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>0.3237058741453886</v>
       </c>
       <c r="U23">
-        <v>177.8</v>
+        <v>241</v>
       </c>
       <c r="V23">
-        <v>0.8606001936108423</v>
+        <v>1.212883744338198</v>
       </c>
       <c r="W23">
-        <v>0.09667673716012085</v>
+        <v>0.02934216753431141</v>
       </c>
       <c r="X23">
-        <v>0.03692776810841816</v>
+        <v>0.07386214049475731</v>
       </c>
       <c r="Y23">
-        <v>0.05974896905170268</v>
+        <v>-0.04451997296044591</v>
       </c>
       <c r="Z23">
-        <v>1.645580664863449</v>
+        <v>1.345882352941177</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.03638228951203391</v>
+        <v>0.07103551970893907</v>
       </c>
       <c r="AC23">
-        <v>-0.03638228951203391</v>
+        <v>-0.07103551970893907</v>
       </c>
       <c r="AD23">
-        <v>7.03</v>
+        <v>20</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>7.03</v>
+        <v>20</v>
       </c>
       <c r="AG23">
-        <v>-170.77</v>
+        <v>-221</v>
       </c>
       <c r="AH23">
-        <v>0.03290736319805271</v>
+        <v>0.09144947416552356</v>
       </c>
       <c r="AI23">
-        <v>0.02563541552711228</v>
+        <v>0.05986231667165519</v>
       </c>
       <c r="AJ23">
-        <v>-4.766117778397993</v>
+        <v>9.910313901345287</v>
       </c>
       <c r="AK23">
-        <v>-1.770921912267967</v>
+        <v>-2.373791621911922</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-0.161</v>
-      </c>
-      <c r="AQ23">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3374,7 +3344,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Imamura Securities Co., Ltd. (JASDAQ:7175)</t>
+          <t>Ichiyoshi Securities Co., Ltd. (TSE:8624)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3383,7 +3353,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.175</v>
+        <v>-0.0369</v>
+      </c>
+      <c r="E24">
+        <v>-0.138</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3398,88 +3371,94 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>12.3</v>
+        <v>10.5</v>
       </c>
       <c r="L24">
-        <v>0.2589473684210526</v>
+        <v>0.08454106280193237</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>13.2133</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.08248002496878902</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>1.258409523809524</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>4.4933</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.02804806491885144</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0.4279333333333333</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>8.720000000000001</v>
+      </c>
+      <c r="T24">
+        <v>0.6599411199321896</v>
       </c>
       <c r="U24">
-        <v>73.5</v>
+        <v>126.4</v>
       </c>
       <c r="V24">
-        <v>1.622516556291391</v>
+        <v>0.7890137328339576</v>
       </c>
       <c r="W24">
-        <v>0.143859649122807</v>
+        <v>0.03929640718562875</v>
       </c>
       <c r="X24">
-        <v>0.03642434289743676</v>
+        <v>0.07184240172030965</v>
       </c>
       <c r="Y24">
-        <v>0.1074353062253703</v>
+        <v>-0.0325459945346809</v>
       </c>
       <c r="Z24">
-        <v>1.892430278884462</v>
+        <v>1.287980918801204</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.03642434289743676</v>
+        <v>0.07128010423427249</v>
       </c>
       <c r="AC24">
-        <v>-0.03642434289743676</v>
+        <v>-0.07128010423427249</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AG24">
-        <v>-73.5</v>
+        <v>-123.22</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>0.01946382666177011</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>0.01578320428826683</v>
       </c>
       <c r="AJ24">
-        <v>2.606382978723404</v>
+        <v>-3.332071389940509</v>
       </c>
       <c r="AK24">
-        <v>-3.909574468085107</v>
+        <v>-1.64118273841236</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>-0.104</v>
+      </c>
+      <c r="AQ24">
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -3490,7 +3469,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Kosei Securities Co., Ltd. (TSE:8617)</t>
+          <t>The Imamura Securities Co., Ltd. (TSE:7175)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3499,7 +3478,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.009979999999999999</v>
+        <v>0.04</v>
+      </c>
+      <c r="E25">
+        <v>0.0761</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3514,19 +3496,19 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>-0.977</v>
+        <v>4.73</v>
       </c>
       <c r="L25">
-        <v>-0.2074309978768578</v>
+        <v>0.1701438848920863</v>
       </c>
       <c r="M25">
-        <v>0.018</v>
+        <v>-0</v>
       </c>
       <c r="N25">
-        <v>0.0004400977995110024</v>
+        <v>-0</v>
       </c>
       <c r="O25">
-        <v>-0.01842374616171955</v>
+        <v>-0</v>
       </c>
       <c r="P25">
         <v>-0</v>
@@ -3535,40 +3517,37 @@
         <v>-0</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S25">
-        <v>0.018</v>
-      </c>
-      <c r="T25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>66.40000000000001</v>
+        <v>54.2</v>
       </c>
       <c r="V25">
-        <v>1.623471882640587</v>
+        <v>1.812709030100335</v>
       </c>
       <c r="W25">
-        <v>-0.006091022443890274</v>
+        <v>0.05124593716143012</v>
       </c>
       <c r="X25">
-        <v>0.03642434289743676</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="Y25">
-        <v>-0.04251536534132704</v>
+        <v>-0.0201002990167829</v>
       </c>
       <c r="Z25">
-        <v>0.05316027088036117</v>
+        <v>1.478723404255319</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.03642434289743676</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="AC25">
-        <v>-0.03642434289743676</v>
+        <v>-0.07134623617821302</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -3580,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>-66.40000000000001</v>
+        <v>-54.2</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -3589,10 +3568,10 @@
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>2.603921568627451</v>
+        <v>2.230452674897119</v>
       </c>
       <c r="AK25">
-        <v>-0.8147239263803682</v>
+        <v>-2.683168316831683</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3609,7 +3588,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monex Group, Inc. (TSE:8698)</t>
+          <t>Maruhachi Securities Co., Ltd. (TSE:8700)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3618,10 +3597,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.172</v>
+        <v>0.00422</v>
       </c>
       <c r="E26">
-        <v>-0.0429</v>
+        <v>-0.149</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3636,91 +3615,88 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>210.3</v>
+        <v>1.35</v>
       </c>
       <c r="L26">
-        <v>0.24442119944212</v>
+        <v>0.07031250000000001</v>
       </c>
       <c r="M26">
-        <v>35.95050000000001</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.02217524056254627</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>0.1709486447931527</v>
+        <v>-0</v>
       </c>
       <c r="P26">
-        <v>35.95050000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.02217524056254627</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>0.1709486447931527</v>
+        <v>-0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
-        <v>1404</v>
+        <v>29.3</v>
       </c>
       <c r="V26">
-        <v>0.8660251665433012</v>
+        <v>0.6894117647058824</v>
       </c>
       <c r="W26">
-        <v>0.2847664184157075</v>
+        <v>0.02064220183486239</v>
       </c>
       <c r="X26">
-        <v>0.06545641162613233</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="Y26">
-        <v>0.2193100067895752</v>
+        <v>-0.05070403434335063</v>
       </c>
       <c r="Z26">
-        <v>0.422282208588957</v>
+        <v>0.7868852459016391</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.0377001175812291</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="AC26">
-        <v>-0.0377001175812291</v>
+        <v>-0.07134623617821302</v>
       </c>
       <c r="AD26">
-        <v>3181.3</v>
+        <v>0</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>3181.3</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1777.3</v>
+        <v>-29.3</v>
       </c>
       <c r="AH26">
-        <v>0.6624258198854763</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>0.7783758655281251</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>0.5229660144181257</v>
+        <v>-2.21969696969697</v>
       </c>
       <c r="AK26">
-        <v>0.6624054265588312</v>
+        <v>-1.362790697674419</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-3.85</v>
+        <v>-0.062</v>
       </c>
       <c r="AQ26">
         <v>-0</v>
@@ -3734,7 +3710,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Daiwa Securities Group Inc. (TSE:8601)</t>
+          <t>The Kosei Securities Co., Ltd. (TSE:8617)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3743,13 +3719,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.00745</v>
-      </c>
-      <c r="E27">
-        <v>0.0415</v>
-      </c>
-      <c r="F27">
-        <v>-0.0315</v>
+        <v>-0.268</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3758,106 +3728,94 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0.001652551319664945</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>0.001254790033431298</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>1127.8</v>
+        <v>-3.32</v>
       </c>
       <c r="L27">
-        <v>0.2017928393780529</v>
+        <v>-1.55868544600939</v>
       </c>
       <c r="M27">
-        <v>656.8833999999999</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.07751202416633232</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>0.582446710409647</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>567.0834</v>
+        <v>-0</v>
       </c>
       <c r="Q27">
-        <v>0.06691565383616925</v>
+        <v>-0</v>
       </c>
       <c r="R27">
-        <v>0.5028226635928356</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>89.79999999999995</v>
-      </c>
-      <c r="T27">
-        <v>0.1367061490669424</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>41964.9</v>
+        <v>40</v>
       </c>
       <c r="V27">
-        <v>4.951844334835863</v>
+        <v>1.556420233463035</v>
       </c>
       <c r="W27">
-        <v>0.09561516549104719</v>
+        <v>-0.02244759972954699</v>
       </c>
       <c r="X27">
-        <v>0.2493724327422425</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="Y27">
-        <v>-0.1537572672511953</v>
+        <v>-0.09379383590776001</v>
       </c>
       <c r="Z27">
-        <v>0.05496399970250115</v>
+        <v>0.02613496932515337</v>
       </c>
       <c r="AA27">
-        <v>6.896827902421929e-05</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.03896214089482873</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="AC27">
-        <v>-0.03889317261580452</v>
+        <v>-0.07134623617821302</v>
       </c>
       <c r="AD27">
-        <v>121510.1</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>468.320279647623</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>121978.4202796476</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>80013.52027964764</v>
+        <v>-40</v>
       </c>
       <c r="AH27">
-        <v>0.9350371499116441</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>0.8940489200882962</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>0.9042289521664845</v>
+        <v>2.797202797202797</v>
       </c>
       <c r="AK27">
-        <v>0.8469833754967061</v>
+        <v>-0.5997001499250375</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-39.3</v>
-      </c>
-      <c r="AN27">
-        <v>1180.856171039844</v>
-      </c>
-      <c r="AP27">
-        <v>777.5852310947291</v>
-      </c>
-      <c r="AQ27">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3868,7 +3826,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nomura Holdings, Inc. (TSE:8604)</t>
+          <t>Toyo Securities Co., Ltd. (TSE:8614)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3877,10 +3835,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.00966</v>
-      </c>
-      <c r="F28">
-        <v>0.16</v>
+        <v>-0.104</v>
+      </c>
+      <c r="E28">
+        <v>0.0282</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3889,103 +3847,100 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0.003555547183442045</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>0.001777773591721022</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>-47.9</v>
+        <v>-5.52</v>
       </c>
       <c r="L28">
-        <v>-0.004269999465135767</v>
+        <v>-0.08917609046849757</v>
       </c>
       <c r="M28">
-        <v>548.4259999999999</v>
+        <v>3.2677</v>
       </c>
       <c r="N28">
-        <v>0.04173269210282009</v>
+        <v>0.01851388101983003</v>
       </c>
       <c r="O28">
-        <v>-11.44939457202505</v>
+        <v>-0.5919746376811594</v>
       </c>
       <c r="P28">
-        <v>548.3</v>
+        <v>3.2677</v>
       </c>
       <c r="Q28">
-        <v>0.0417231040832788</v>
+        <v>0.01851388101983003</v>
       </c>
       <c r="R28">
-        <v>-11.44676409185804</v>
+        <v>-0.5919746376811594</v>
       </c>
       <c r="S28">
-        <v>0.1259999999999764</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>0.0002297484072600066</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>37464.2</v>
+        <v>210.5</v>
       </c>
       <c r="V28">
-        <v>2.850853029357602</v>
+        <v>1.192634560906516</v>
       </c>
       <c r="W28">
-        <v>-0.001849642235171005</v>
+        <v>-0.01583476764199656</v>
       </c>
       <c r="X28">
-        <v>0.2931563764459547</v>
+        <v>0.08659845351957417</v>
       </c>
       <c r="Y28">
-        <v>-0.2950060186811256</v>
+        <v>-0.1024332211615707</v>
       </c>
       <c r="Z28">
-        <v>0.04447466867267297</v>
+        <v>0.4110225763612217</v>
       </c>
       <c r="AA28">
-        <v>7.906589146682026e-05</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.03899057210394059</v>
+        <v>0.07229966365708113</v>
       </c>
       <c r="AC28">
-        <v>-0.03891150621247377</v>
+        <v>-0.07229966365708113</v>
       </c>
       <c r="AD28">
-        <v>226322.3</v>
+        <v>107.7</v>
       </c>
       <c r="AE28">
-        <v>1718.072914027919</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>228040.3729140279</v>
+        <v>107.7</v>
       </c>
       <c r="AG28">
-        <v>190576.1729140279</v>
+        <v>-102.8</v>
       </c>
       <c r="AH28">
-        <v>0.9455124662149141</v>
+        <v>0.3789584799437016</v>
       </c>
       <c r="AI28">
-        <v>0.9007846787579138</v>
+        <v>0.2983379501385042</v>
       </c>
       <c r="AJ28">
-        <v>0.9354920647638686</v>
+        <v>-1.394843962008141</v>
       </c>
       <c r="AK28">
-        <v>0.8835517693219329</v>
+        <v>-0.6830564784053156</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>590.1494132985658</v>
-      </c>
-      <c r="AP28">
-        <v>496.9391731786909</v>
+        <v>-2.22</v>
+      </c>
+      <c r="AQ28">
+        <v>-0</v>
       </c>
     </row>
     <row r="29">
@@ -3996,7 +3951,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kobayashi Yoko Co., Ltd. (TSE:8742)</t>
+          <t>Monex Group, Inc. (TSE:8698)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4005,43 +3960,46 @@
         </is>
       </c>
       <c r="D29">
-        <v>-0.011</v>
+        <v>0.105</v>
+      </c>
+      <c r="E29">
+        <v>-0.0151</v>
       </c>
       <c r="G29">
-        <v>-0.04276315789473684</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>-0.04276315789473684</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>-0.04506578947368422</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>-0.04506578947368422</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>-0.502</v>
+        <v>15.5</v>
       </c>
       <c r="L29">
-        <v>-0.01651315789473684</v>
+        <v>0.0293282876064333</v>
       </c>
       <c r="M29">
-        <v>0.20768</v>
+        <v>28.3657</v>
       </c>
       <c r="N29">
-        <v>0.01141098901098901</v>
+        <v>0.03383313454198474</v>
       </c>
       <c r="O29">
-        <v>-0.4137051792828685</v>
+        <v>1.830045161290323</v>
       </c>
       <c r="P29">
-        <v>0.20768</v>
+        <v>28.3657</v>
       </c>
       <c r="Q29">
-        <v>0.01141098901098901</v>
+        <v>0.03383313454198474</v>
       </c>
       <c r="R29">
-        <v>-0.4137051792828685</v>
+        <v>1.830045161290323</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4050,73 +4008,64 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>27</v>
+        <v>7485.5</v>
       </c>
       <c r="V29">
-        <v>1.483516483516484</v>
+        <v>8.928315839694656</v>
       </c>
       <c r="W29">
-        <v>-0.006924137931034482</v>
+        <v>0.0173203709911722</v>
       </c>
       <c r="X29">
-        <v>0.03751363251265675</v>
+        <v>0.1458080494411488</v>
       </c>
       <c r="Y29">
-        <v>-0.04443777044369123</v>
+        <v>-0.1284876784499766</v>
       </c>
       <c r="Z29">
-        <v>0.7002994701681641</v>
+        <v>0.1977771124915799</v>
       </c>
       <c r="AA29">
-        <v>-0.03155954849113108</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.03633670577324147</v>
+        <v>0.07322985438092383</v>
       </c>
       <c r="AC29">
-        <v>-0.06789625426437254</v>
+        <v>-0.07322985438092383</v>
       </c>
       <c r="AD29">
-        <v>1.34</v>
+        <v>2497.6</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.34</v>
+        <v>2497.6</v>
       </c>
       <c r="AG29">
-        <v>-25.66</v>
+        <v>-4987.9</v>
       </c>
       <c r="AH29">
-        <v>0.06857727737973389</v>
+        <v>0.7486810551558752</v>
       </c>
       <c r="AI29">
-        <v>0.01697491765898151</v>
+        <v>0.7705312519281793</v>
       </c>
       <c r="AJ29">
-        <v>3.439678284182305</v>
+        <v>1.202048439571032</v>
       </c>
       <c r="AK29">
-        <v>-0.4940315748941086</v>
+        <v>1.175255059965599</v>
       </c>
       <c r="AL29">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>-0.305</v>
-      </c>
-      <c r="AN29">
-        <v>-1.240740740740741</v>
-      </c>
-      <c r="AO29">
-        <v>-152.2222222222223</v>
-      </c>
-      <c r="AP29">
-        <v>23.75925925925926</v>
+        <v>-16.6</v>
       </c>
       <c r="AQ29">
-        <v>4.491803278688525</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -4127,7 +4076,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fujitomi Co.,Ltd. (JASDAQ:8740)</t>
+          <t>Nomura Holdings, Inc. (TSE:8604)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4136,112 +4085,118 @@
         </is>
       </c>
       <c r="D30">
-        <v>-0.0236</v>
+        <v>-0.0178</v>
+      </c>
+      <c r="E30">
+        <v>-0.145</v>
+      </c>
+      <c r="F30">
+        <v>0.04</v>
       </c>
       <c r="G30">
-        <v>-0.04576470588235294</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>-0.04576470588235294</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>-0.06235294117647059</v>
+        <v>0.01083112369246625</v>
       </c>
       <c r="J30">
-        <v>-0.06235294117647059</v>
+        <v>0.006780105723444051</v>
       </c>
       <c r="K30">
-        <v>-0.789</v>
+        <v>758.6</v>
       </c>
       <c r="L30">
-        <v>-0.04641176470588235</v>
+        <v>0.08431793173204104</v>
       </c>
       <c r="M30">
-        <v>-0</v>
+        <v>827.662</v>
       </c>
       <c r="N30">
-        <v>-0</v>
+        <v>0.07441196831704532</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.091038755602425</v>
       </c>
       <c r="P30">
-        <v>-0</v>
+        <v>393.262</v>
       </c>
       <c r="Q30">
-        <v>-0</v>
+        <v>0.03535670295881396</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>0.5184049564988136</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>434.4</v>
+      </c>
+      <c r="T30">
+        <v>0.5248519323105326</v>
       </c>
       <c r="U30">
-        <v>7.6</v>
+        <v>27799.4</v>
       </c>
       <c r="V30">
-        <v>0.6229508196721312</v>
+        <v>2.499339189225638</v>
       </c>
       <c r="W30">
-        <v>-0.04152631578947369</v>
+        <v>0.03094873834730637</v>
       </c>
       <c r="X30">
-        <v>0.03642434289743676</v>
+        <v>0.5286010362330021</v>
       </c>
       <c r="Y30">
-        <v>-0.07795065868691045</v>
+        <v>-0.4976522978856958</v>
       </c>
       <c r="Z30">
-        <v>2.207792207792208</v>
+        <v>0.04190171394887759</v>
       </c>
       <c r="AA30">
-        <v>-0.1376623376623377</v>
+        <v>0.0002840980505669003</v>
       </c>
       <c r="AB30">
-        <v>0.03642434289743676</v>
+        <v>0.07511531743274975</v>
       </c>
       <c r="AC30">
-        <v>-0.1740866805597744</v>
+        <v>-0.07483121938218286</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>202128.1</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1344.767316256252</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>203472.8673162562</v>
       </c>
       <c r="AG30">
-        <v>-7.6</v>
+        <v>175673.4673162563</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>0.9481690132787872</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>0.9012066118447265</v>
       </c>
       <c r="AJ30">
-        <v>-1.652173913043478</v>
+        <v>0.940455416404938</v>
       </c>
       <c r="AK30">
-        <v>-0.7916666666666666</v>
+        <v>0.8873344397694285</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-0.045</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>-0</v>
+        <v>551.6596615720524</v>
       </c>
       <c r="AP30">
-        <v>7.524752475247524</v>
-      </c>
-      <c r="AQ30">
-        <v>23.55555555555556</v>
+        <v>479.4581531557212</v>
       </c>
     </row>
     <row r="31">
@@ -4252,7 +4207,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oak Capital Corporation (TSE:3113)</t>
+          <t>Daiwa Securities Group Inc. (TSE:8601)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4261,115 +4216,121 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.214</v>
+        <v>-0.00049</v>
+      </c>
+      <c r="E31">
+        <v>-0.0537</v>
+      </c>
+      <c r="F31">
+        <v>-0.05860000000000001</v>
       </c>
       <c r="G31">
-        <v>-0.1476683937823834</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>-0.1476683937823834</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>-0.1955958549222798</v>
+        <v>0.00708934583830262</v>
       </c>
       <c r="J31">
-        <v>-0.1955958549222798</v>
+        <v>0.005471828860854173</v>
       </c>
       <c r="K31">
-        <v>-11.7</v>
+        <v>526.3</v>
       </c>
       <c r="L31">
-        <v>-0.3031088082901554</v>
+        <v>0.1164200234476961</v>
       </c>
       <c r="M31">
-        <v>-0</v>
+        <v>470.8736</v>
       </c>
       <c r="N31">
-        <v>-0</v>
+        <v>0.0733151060318251</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>0.894686680600418</v>
       </c>
       <c r="P31">
-        <v>-0</v>
+        <v>271.6736</v>
       </c>
       <c r="Q31">
-        <v>-0</v>
+        <v>0.04229962943356273</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>0.5161953258597758</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>199.2</v>
+      </c>
+      <c r="T31">
+        <v>0.4230434664419496</v>
       </c>
       <c r="U31">
-        <v>13</v>
+        <v>27401.5</v>
       </c>
       <c r="V31">
-        <v>0.3448275862068965</v>
+        <v>4.26641858437393</v>
       </c>
       <c r="W31">
-        <v>-0.2373225152129818</v>
+        <v>0.04336326934168246</v>
       </c>
       <c r="X31">
-        <v>0.04172222599770896</v>
+        <v>0.5257801172035315</v>
       </c>
       <c r="Y31">
-        <v>-0.2790447412106907</v>
+        <v>-0.482416847861849</v>
       </c>
       <c r="Z31">
-        <v>0.9460784313725491</v>
+        <v>0.04923144624961927</v>
       </c>
       <c r="AA31">
-        <v>-0.1850490196078431</v>
+        <v>0.0002693860484502577</v>
       </c>
       <c r="AB31">
-        <v>0.03693215206316525</v>
+        <v>0.07511410514648356</v>
       </c>
       <c r="AC31">
-        <v>-0.2219811716710084</v>
+        <v>-0.07484471909803331</v>
       </c>
       <c r="AD31">
-        <v>13.5</v>
+        <v>116444.1</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>322.7559713439267</v>
       </c>
       <c r="AF31">
-        <v>13.5</v>
+        <v>116766.8559713439</v>
       </c>
       <c r="AG31">
-        <v>0.5</v>
+        <v>89365.35597134393</v>
       </c>
       <c r="AH31">
-        <v>0.263671875</v>
+        <v>0.9478640444560936</v>
       </c>
       <c r="AI31">
-        <v>0.2705410821643287</v>
+        <v>0.908701697763699</v>
       </c>
       <c r="AJ31">
-        <v>0.01308900523560209</v>
+        <v>0.9329498167606646</v>
       </c>
       <c r="AK31">
-        <v>0.01355013550135501</v>
+        <v>0.8839560668974835</v>
       </c>
       <c r="AL31">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>-0.144</v>
+        <v>-32.4</v>
       </c>
       <c r="AN31">
-        <v>-1.962209302325581</v>
-      </c>
-      <c r="AO31">
-        <v>-49.67105263157895</v>
+        <v>1205.425465838509</v>
       </c>
       <c r="AP31">
-        <v>-0.07267441860465117</v>
+        <v>925.1072046722975</v>
       </c>
       <c r="AQ31">
-        <v>52.43055555555556</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4380,7 +4341,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Daiichi Commodities Co.,Ltd. (JASDAQ:8746)</t>
+          <t>Daiichi Commodities Co.,Ltd. (TSE:8746)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4389,25 +4350,25 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.354</v>
+        <v>0.0344</v>
       </c>
       <c r="G32">
-        <v>-0.9531249999999999</v>
+        <v>-0.1112412177985948</v>
       </c>
       <c r="H32">
-        <v>-0.9531249999999999</v>
+        <v>-0.1112412177985948</v>
       </c>
       <c r="I32">
-        <v>-0.5739318730142687</v>
+        <v>-0.0611661743557906</v>
       </c>
       <c r="J32">
-        <v>-0.5739318730142687</v>
+        <v>-0.0611661743557906</v>
       </c>
       <c r="K32">
-        <v>-9.49</v>
+        <v>-12</v>
       </c>
       <c r="L32">
-        <v>-0.7414062499999999</v>
+        <v>-0.2810304449648712</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4431,70 +4392,70 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>14.2</v>
+        <v>20.5</v>
       </c>
       <c r="V32">
-        <v>0.6311111111111111</v>
+        <v>0.7945736434108527</v>
       </c>
       <c r="W32">
-        <v>-0.1777153558052434</v>
+        <v>-0.25</v>
       </c>
       <c r="X32">
-        <v>0.0382862819196076</v>
+        <v>0.07184903172443635</v>
       </c>
       <c r="Y32">
-        <v>-0.216001637724851</v>
+        <v>-0.3218490317244364</v>
       </c>
       <c r="Z32">
-        <v>0.3983612430186091</v>
+        <v>1.244209536778776</v>
       </c>
       <c r="AA32">
-        <v>-0.2286322143419626</v>
+        <v>-0.07610353746174808</v>
       </c>
       <c r="AB32">
-        <v>0.03663962674261584</v>
+        <v>0.07139584696863543</v>
       </c>
       <c r="AC32">
-        <v>-0.2652718410845785</v>
+        <v>-0.1474993844303835</v>
       </c>
       <c r="AD32">
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>2.831639872913195</v>
+        <v>0.5189782249612932</v>
       </c>
       <c r="AF32">
-        <v>2.831639872913195</v>
+        <v>0.5189782249612932</v>
       </c>
       <c r="AG32">
-        <v>-11.3683601270868</v>
+        <v>-19.98102177503871</v>
       </c>
       <c r="AH32">
-        <v>0.1117827304951162</v>
+        <v>0.01971878317331813</v>
       </c>
       <c r="AI32">
-        <v>0.0557062467390925</v>
+        <v>0.01595924144267638</v>
       </c>
       <c r="AJ32">
-        <v>-1.021265532920232</v>
+        <v>-3.433768095114604</v>
       </c>
       <c r="AK32">
-        <v>-0.3103426482277959</v>
+        <v>-1.662455942680856</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-0.161</v>
+        <v>-0.007</v>
       </c>
       <c r="AN32">
         <v>-0</v>
       </c>
       <c r="AP32">
-        <v>1.704401818153944</v>
+        <v>8.063366333752505</v>
       </c>
       <c r="AQ32">
-        <v>57.26708074534162</v>
+        <v>437.1428571428572</v>
       </c>
     </row>
     <row r="33">
@@ -4505,7 +4466,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>meinan M&amp;A co.,ltd. (NSE:7076)</t>
+          <t>Oak Capital Corporation (TSE:3113)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4513,23 +4474,26 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D33">
+        <v>-0.257</v>
+      </c>
       <c r="G33">
-        <v>0.1934426229508197</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="H33">
-        <v>0.1934426229508197</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="I33">
-        <v>0.1885245901639344</v>
+        <v>-0.3986111111111111</v>
       </c>
       <c r="J33">
-        <v>0.1232265275707899</v>
+        <v>-0.3986111111111111</v>
       </c>
       <c r="K33">
-        <v>1.43</v>
+        <v>-4.51</v>
       </c>
       <c r="L33">
-        <v>0.1172131147540984</v>
+        <v>-0.3131944444444444</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4538,7 +4502,7 @@
         <v>-0</v>
       </c>
       <c r="O33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P33">
         <v>-0</v>
@@ -4547,299 +4511,79 @@
         <v>-0</v>
       </c>
       <c r="R33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="U33">
+        <v>12.1</v>
+      </c>
+      <c r="V33">
+        <v>0.2415169660678643</v>
+      </c>
+      <c r="W33">
+        <v>-0.1288571428571429</v>
+      </c>
+      <c r="X33">
+        <v>0.0769340546434928</v>
+      </c>
+      <c r="Y33">
+        <v>-0.2057911975006357</v>
+      </c>
+      <c r="Z33">
+        <v>0.4578696343402226</v>
+      </c>
+      <c r="AA33">
+        <v>-0.1825119236883943</v>
+      </c>
+      <c r="AB33">
+        <v>0.07072545204403818</v>
+      </c>
+      <c r="AC33">
+        <v>-0.2532373757324324</v>
+      </c>
+      <c r="AD33">
         <v>11.2</v>
       </c>
-      <c r="V33">
-        <v>0.3343283582089552</v>
-      </c>
-      <c r="W33">
-        <v>0.1505263157894737</v>
-      </c>
-      <c r="X33">
-        <v>0.03642434289743676</v>
-      </c>
-      <c r="Y33">
-        <v>0.1141019728920369</v>
-      </c>
-      <c r="Z33">
-        <v>-11.09090909090909</v>
-      </c>
-      <c r="AA33">
-        <v>-1.366694214876033</v>
-      </c>
-      <c r="AB33">
-        <v>0.03642434289743676</v>
-      </c>
-      <c r="AC33">
-        <v>-1.40311855777347</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="AG33">
-        <v>-11.2</v>
+        <v>-0.9000000000000004</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>0.1827079934747145</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>0.2338204592901879</v>
       </c>
       <c r="AJ33">
-        <v>-0.5022421524663677</v>
+        <v>-0.01829268292682927</v>
       </c>
       <c r="AK33">
-        <v>56.0000000000002</v>
+        <v>-0.02513966480446928</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>-0.132</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>-2.125237191650854</v>
+      </c>
+      <c r="AO33">
+        <v>-46.29032258064516</v>
       </c>
       <c r="AP33">
-        <v>-4.745762711864407</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>M&amp;A Capital Partners Co.,Ltd. (TSE:6080)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>0.322</v>
-      </c>
-      <c r="E34">
-        <v>0.319</v>
-      </c>
-      <c r="G34">
-        <v>0.4554819720382634</v>
-      </c>
-      <c r="H34">
-        <v>0.4554819720382634</v>
-      </c>
-      <c r="I34">
-        <v>0.4485778648081632</v>
-      </c>
-      <c r="J34">
-        <v>0.293738804874381</v>
-      </c>
-      <c r="K34">
-        <v>38.6</v>
-      </c>
-      <c r="L34">
-        <v>0.2840323767476086</v>
-      </c>
-      <c r="M34">
-        <v>-0</v>
-      </c>
-      <c r="N34">
-        <v>-0</v>
-      </c>
-      <c r="O34">
-        <v>-0</v>
-      </c>
-      <c r="P34">
-        <v>-0</v>
-      </c>
-      <c r="Q34">
-        <v>-0</v>
-      </c>
-      <c r="R34">
-        <v>-0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>244.4</v>
-      </c>
-      <c r="V34">
-        <v>0.1683543431838534</v>
-      </c>
-      <c r="W34">
-        <v>0.1973415132924335</v>
-      </c>
-      <c r="X34">
-        <v>0.03645177137998949</v>
-      </c>
-      <c r="Y34">
-        <v>0.1608897419124441</v>
-      </c>
-      <c r="Z34">
-        <v>-8.935698984012758</v>
-      </c>
-      <c r="AA34">
-        <v>-2.624761540281128</v>
-      </c>
-      <c r="AB34">
-        <v>0.03642790678630504</v>
-      </c>
-      <c r="AC34">
-        <v>-2.661189447067433</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>2.691340862853095</v>
-      </c>
-      <c r="AF34">
-        <v>2.691340862853095</v>
-      </c>
-      <c r="AG34">
-        <v>-241.7086591371469</v>
-      </c>
-      <c r="AH34">
-        <v>0.001850492908776802</v>
-      </c>
-      <c r="AI34">
-        <v>0.01148225379378605</v>
-      </c>
-      <c r="AJ34">
-        <v>-0.1997606519768834</v>
-      </c>
-      <c r="AK34">
-        <v>24.14995413721806</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-0.027</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>-3.747421071893751</v>
-      </c>
-      <c r="AQ34">
-        <v>-2181.481481481481</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ONDECK Co., Ltd. (TSE:7360)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>0.2547993019197207</v>
-      </c>
-      <c r="H35">
-        <v>0.2547993019197207</v>
-      </c>
-      <c r="I35">
-        <v>-0.1047120418848167</v>
-      </c>
-      <c r="J35">
-        <v>-0.1047120418848167</v>
-      </c>
-      <c r="K35">
-        <v>-0.573</v>
-      </c>
-      <c r="L35">
-        <v>-0.09999999999999998</v>
-      </c>
-      <c r="M35">
-        <v>-0</v>
-      </c>
-      <c r="N35">
-        <v>-0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>-0</v>
-      </c>
-      <c r="Q35">
-        <v>-0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>7.09</v>
-      </c>
-      <c r="V35">
-        <v>0.1708433734939759</v>
-      </c>
-      <c r="X35">
-        <v>0.03660580236763052</v>
-      </c>
-      <c r="AB35">
-        <v>0.03647329007891822</v>
-      </c>
-      <c r="AD35">
-        <v>0.509</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0.509</v>
-      </c>
-      <c r="AG35">
-        <v>-6.581</v>
-      </c>
-      <c r="AH35">
-        <v>0.01211645123663977</v>
-      </c>
-      <c r="AI35">
-        <v>0.05719743791437239</v>
-      </c>
-      <c r="AJ35">
-        <v>-0.1884647326670294</v>
-      </c>
-      <c r="AK35">
-        <v>-3.637921503593143</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>0</v>
+        <v>0.1707779886148008</v>
+      </c>
+      <c r="AQ33">
+        <v>43.48484848484848</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ33"/>
+  <dimension ref="A1:AQ36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00945</v>
+        <v>0.03445</v>
       </c>
       <c r="E2">
-        <v>-0.0151</v>
+        <v>-0.006015</v>
       </c>
       <c r="F2">
-        <v>0.0572</v>
+        <v>0.07325000000000001</v>
       </c>
       <c r="G2">
-        <v>0.07688054969002951</v>
+        <v>0.05110022574237218</v>
       </c>
       <c r="H2">
-        <v>0.07622253918622594</v>
+        <v>0.05073073316125536</v>
       </c>
       <c r="I2">
-        <v>0.04734817516681705</v>
+        <v>0.04263997306138397</v>
       </c>
       <c r="J2">
-        <v>0.03381106672108938</v>
+        <v>0.03142034644777512</v>
       </c>
       <c r="K2">
-        <v>3756.926</v>
+        <v>2364.971</v>
       </c>
       <c r="L2">
-        <v>0.1589159661874983</v>
+        <v>0.08322278467204015</v>
       </c>
       <c r="M2">
-        <v>1907.74436</v>
+        <v>1446.12516</v>
       </c>
       <c r="N2">
-        <v>0.06048727187408844</v>
+        <v>0.03590636252355685</v>
       </c>
       <c r="O2">
-        <v>0.5077939677278711</v>
+        <v>0.6114769102876949</v>
       </c>
       <c r="P2">
-        <v>1182.56336</v>
+        <v>1057.21316</v>
       </c>
       <c r="Q2">
-        <v>0.0374945579525422</v>
+        <v>0.02624992638094694</v>
       </c>
       <c r="R2">
-        <v>0.3147688722109512</v>
+        <v>0.4470300735188719</v>
       </c>
       <c r="S2">
-        <v>725.181</v>
+        <v>388.912</v>
       </c>
       <c r="T2">
-        <v>0.3801248297229929</v>
+        <v>0.2689338452558283</v>
       </c>
       <c r="U2">
-        <v>93627.88</v>
+        <v>85375.96000000001</v>
       </c>
       <c r="V2">
-        <v>2.96858171948915</v>
+        <v>2.119830465128405</v>
       </c>
       <c r="W2">
-        <v>0.032897384305835</v>
+        <v>0.05812974103698459</v>
       </c>
       <c r="X2">
-        <v>0.08075198581698241</v>
+        <v>0.06309207931767974</v>
       </c>
       <c r="Y2">
-        <v>-0.04785460151114741</v>
+        <v>-0.004962338280695144</v>
       </c>
       <c r="Z2">
-        <v>0.07040544243343699</v>
+        <v>0.09055167075842084</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07128010423427249</v>
+        <v>0.05964069736236868</v>
       </c>
       <c r="AC2">
-        <v>-0.06976518271013085</v>
+        <v>-0.05663633480888276</v>
       </c>
       <c r="AD2">
-        <v>355929.865</v>
+        <v>387708.038</v>
       </c>
       <c r="AE2">
-        <v>1769.753424041424</v>
+        <v>1657.739807620402</v>
       </c>
       <c r="AF2">
-        <v>357699.6184240414</v>
+        <v>389365.7778076204</v>
       </c>
       <c r="AG2">
-        <v>264071.7384240414</v>
+        <v>303989.8178076204</v>
       </c>
       <c r="AH2">
-        <v>0.9189711660410324</v>
+        <v>0.9062591088778753</v>
       </c>
       <c r="AI2">
-        <v>0.8691727633814276</v>
+        <v>0.877843357680679</v>
       </c>
       <c r="AJ2">
-        <v>0.8933072047637164</v>
+        <v>0.8830118280592838</v>
       </c>
       <c r="AK2">
-        <v>0.8306430422979399</v>
+        <v>0.8487254039540501</v>
       </c>
       <c r="AL2">
-        <v>94.983</v>
+        <v>211.688</v>
       </c>
       <c r="AM2">
-        <v>-5.403999999999996</v>
+        <v>117.144</v>
       </c>
       <c r="AN2">
-        <v>197.0054065393222</v>
+        <v>199.5507950984712</v>
       </c>
       <c r="AO2">
-        <v>10.19032879567923</v>
+        <v>5.073126488039001</v>
       </c>
       <c r="AP2">
-        <v>146.1623912446174</v>
+        <v>156.4615739159631</v>
       </c>
       <c r="AQ2">
-        <v>-179.1095484826056</v>
+        <v>9.167520316874956</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M&amp;A Research Institute Inc. (TSE:9552)</t>
+          <t>M&amp;A Research Institute Holdings Inc. (TSE:9552)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5425185185185185</v>
+        <v>0.5336787564766839</v>
       </c>
       <c r="H3">
-        <v>0.5407407407407407</v>
+        <v>0.531951640759931</v>
       </c>
       <c r="I3">
-        <v>0.5370370370370371</v>
+        <v>0.5302245250431779</v>
       </c>
       <c r="J3">
-        <v>0.3423611111111111</v>
+        <v>0.3128324697754749</v>
       </c>
       <c r="K3">
-        <v>9.16</v>
+        <v>17.7</v>
       </c>
       <c r="L3">
-        <v>0.3392592592592593</v>
+        <v>0.3056994818652849</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,40 +764,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>27.5</v>
+        <v>49.7</v>
       </c>
       <c r="V3">
-        <v>0.03014359311629946</v>
+        <v>0.02673192771084337</v>
+      </c>
+      <c r="W3">
+        <v>1.351145038167939</v>
       </c>
       <c r="X3">
-        <v>0.07137160704491299</v>
+        <v>0.06060653245775174</v>
+      </c>
+      <c r="Y3">
+        <v>1.290538505710187</v>
       </c>
       <c r="AB3">
-        <v>0.07135174650760384</v>
+        <v>0.06059999721808682</v>
       </c>
       <c r="AD3">
-        <v>0.926</v>
+        <v>0.67</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.926</v>
+        <v>0.67</v>
       </c>
       <c r="AG3">
-        <v>-26.574</v>
+        <v>-49.03</v>
       </c>
       <c r="AH3">
-        <v>0.001013987775205699</v>
+        <v>0.0003602402318441612</v>
       </c>
       <c r="AI3">
-        <v>0.04383224462747326</v>
+        <v>0.0175530521351847</v>
       </c>
       <c r="AJ3">
-        <v>-0.0300025064184635</v>
+        <v>-0.02708585381483507</v>
       </c>
       <c r="AK3">
-        <v>4.169124568559773</v>
+        <v>4.252385082393755</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -806,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.06342465753424659</v>
+        <v>0.02175324675324675</v>
       </c>
       <c r="AP3">
-        <v>-1.82013698630137</v>
+        <v>-1.591883116883117</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M&amp;A Capital Partners Co.,Ltd. (TSE:6080)</t>
+          <t>Japan M&amp;A Solution Incorporated (TSE:9236)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -828,32 +834,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.2</v>
-      </c>
-      <c r="E4">
-        <v>0.212</v>
-      </c>
-      <c r="F4">
-        <v>0.07440000000000001</v>
-      </c>
       <c r="G4">
-        <v>0.4870719776380154</v>
+        <v>0.2358870967741935</v>
       </c>
       <c r="H4">
-        <v>0.4870719776380154</v>
+        <v>0.2358870967741935</v>
       </c>
       <c r="I4">
-        <v>0.471145134035268</v>
+        <v>0.2338709677419355</v>
       </c>
       <c r="J4">
-        <v>0.3280566118467792</v>
+        <v>0.1740337111304853</v>
       </c>
       <c r="K4">
-        <v>47</v>
+        <v>0.825</v>
       </c>
       <c r="L4">
-        <v>0.3284416491963662</v>
+        <v>0.1663306451612903</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,70 +874,52 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>246.5</v>
+        <v>4.33</v>
       </c>
       <c r="V4">
-        <v>0.2219920749279539</v>
-      </c>
-      <c r="W4">
-        <v>0.2028485110056107</v>
+        <v>0.1467796610169491</v>
       </c>
       <c r="X4">
-        <v>0.07183461332887973</v>
-      </c>
-      <c r="Y4">
-        <v>0.131013897676731</v>
-      </c>
-      <c r="Z4">
-        <v>439.4199318600593</v>
-      </c>
-      <c r="AA4">
-        <v>144.1546140239536</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="AB4">
-        <v>0.07139445157097908</v>
-      </c>
-      <c r="AC4">
-        <v>144.0832195723827</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>21.69565659776576</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>21.69565659776576</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-224.8043434022343</v>
+        <v>-4.33</v>
       </c>
       <c r="AH4">
-        <v>0.01916415496457844</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.08783821098966649</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.2538453545107432</v>
+        <v>-0.1720301946762018</v>
       </c>
       <c r="AK4">
-        <v>-453.5485745888809</v>
+        <v>11.1025641025641</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-3.023189125904172</v>
-      </c>
-      <c r="AQ4">
-        <v>-9585.714285714284</v>
+        <v>-3.700854700854701</v>
       </c>
     </row>
     <row r="5">
@@ -960,28 +939,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.249</v>
+        <v>0.254</v>
       </c>
       <c r="E5">
-        <v>0.484</v>
+        <v>0.375</v>
       </c>
       <c r="G5">
-        <v>0.2617801047120419</v>
+        <v>0.1356628982528263</v>
       </c>
       <c r="H5">
-        <v>0.2617801047120419</v>
+        <v>0.1356628982528263</v>
       </c>
       <c r="I5">
-        <v>0.2577791862330918</v>
+        <v>0.132644935088361</v>
       </c>
       <c r="J5">
-        <v>0.174000950707337</v>
+        <v>0.08174102410146007</v>
       </c>
       <c r="K5">
-        <v>1.59</v>
+        <v>0.723</v>
       </c>
       <c r="L5">
-        <v>0.1664921465968586</v>
+        <v>0.07430626927029804</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1005,55 +984,46 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>10.6</v>
+        <v>9.06</v>
       </c>
       <c r="V5">
-        <v>0.397003745318352</v>
+        <v>0.5005524861878453</v>
       </c>
       <c r="W5">
-        <v>0.1445454545454546</v>
+        <v>0.07237237237237237</v>
       </c>
       <c r="X5">
-        <v>0.07165146585224924</v>
+        <v>0.06082405784425225</v>
       </c>
       <c r="Y5">
-        <v>0.07289398869320532</v>
-      </c>
-      <c r="Z5">
-        <v>75.76727814649468</v>
-      </c>
-      <c r="AA5">
-        <v>13.18357842999731</v>
+        <v>0.01154831452812013</v>
       </c>
       <c r="AB5">
-        <v>0.07137658833663212</v>
-      </c>
-      <c r="AC5">
-        <v>13.11220184166067</v>
+        <v>0.06047186810760012</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.3260438573698687</v>
+        <v>0.2668239079512364</v>
       </c>
       <c r="AF5">
-        <v>0.3260438573698687</v>
+        <v>0.2668239079512364</v>
       </c>
       <c r="AG5">
-        <v>-10.27395614263013</v>
+        <v>-8.793176092048764</v>
       </c>
       <c r="AH5">
-        <v>0.0120640615803988</v>
+        <v>0.01452749311957659</v>
       </c>
       <c r="AI5">
-        <v>0.03160551291539346</v>
+        <v>0.02525109818007462</v>
       </c>
       <c r="AJ5">
-        <v>-0.6254674729862307</v>
+        <v>-0.9448095482430219</v>
       </c>
       <c r="AK5">
-        <v>36.1814893224993</v>
+        <v>-5.83556980059101</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1065,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>-3.956086308290385</v>
+        <v>-6.21865353044467</v>
       </c>
     </row>
     <row r="6">
@@ -1076,7 +1046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strike Company,Limited (TSE:6196)</t>
+          <t>M&amp;A Capital Partners Co.,Ltd. (TSE:6080)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1084,35 +1054,41 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.211</v>
+      </c>
+      <c r="E6">
+        <v>0.151</v>
+      </c>
       <c r="F6">
-        <v>0.158</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="G6">
-        <v>0.3994601889338732</v>
+        <v>0.3832378223495702</v>
       </c>
       <c r="H6">
-        <v>0.3994601889338732</v>
+        <v>0.3832378223495702</v>
       </c>
       <c r="I6">
-        <v>0.3940620782726046</v>
+        <v>0.3706360514372952</v>
       </c>
       <c r="J6">
-        <v>0.2761133603238866</v>
+        <v>0.2097800051135091</v>
       </c>
       <c r="K6">
-        <v>20.5</v>
+        <v>28.3</v>
       </c>
       <c r="L6">
-        <v>0.2766531713900135</v>
+        <v>0.2027220630372493</v>
       </c>
       <c r="M6">
-        <v>3.46</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.005309191345711216</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1687804878048781</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1124,73 +1100,64 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>3.46</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>59</v>
+        <v>262.8</v>
       </c>
       <c r="V6">
-        <v>0.09053245358293693</v>
+        <v>0.4796495710896149</v>
       </c>
       <c r="W6">
-        <v>0.2789115646258503</v>
+        <v>0.1256102973812694</v>
       </c>
       <c r="X6">
-        <v>0.07134623617821302</v>
+        <v>0.06128009162901029</v>
       </c>
       <c r="Y6">
-        <v>0.2075653284476373</v>
-      </c>
-      <c r="Z6">
-        <v>14.24999999999999</v>
-      </c>
-      <c r="AA6">
-        <v>3.934615384615382</v>
+        <v>0.06433020575225912</v>
       </c>
       <c r="AB6">
-        <v>0.07134623617821302</v>
-      </c>
-      <c r="AC6">
-        <v>3.863269148437169</v>
+        <v>0.06039219439972221</v>
       </c>
       <c r="AD6">
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>24.59603609676796</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>24.59603609676796</v>
       </c>
       <c r="AG6">
-        <v>-59</v>
+        <v>-238.2039639032321</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.04296280593392708</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.08996485994428333</v>
       </c>
       <c r="AJ6">
-        <v>-0.09954445756706597</v>
+        <v>-0.7691540612060098</v>
       </c>
       <c r="AK6">
-        <v>-3.155080213903743</v>
+        <v>-22.48047871183544</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="AN6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>-1.993243243243243</v>
+        <v>-3.952936672805046</v>
+      </c>
+      <c r="AQ6">
+        <v>-7128.571428571428</v>
       </c>
     </row>
     <row r="7">
@@ -1201,7 +1168,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ONDECK Co., Ltd. (TSE:7360)</t>
+          <t>Bridge Consulting Group Inc. (TSE:9225)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,22 +1177,22 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.04509018036072144</v>
+        <v>0.09639639639639641</v>
       </c>
       <c r="H7">
-        <v>0.04509018036072144</v>
+        <v>0.09639639639639641</v>
       </c>
       <c r="I7">
-        <v>0.2995991983967936</v>
+        <v>0.09369369369369369</v>
       </c>
       <c r="J7">
-        <v>0.2039501299897092</v>
+        <v>0.06925626925626925</v>
       </c>
       <c r="K7">
-        <v>2.02</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L7">
-        <v>0.2024048096192385</v>
+        <v>0.06153153153153154</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1249,55 +1216,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>8.279999999999999</v>
+        <v>6.56</v>
       </c>
       <c r="V7">
-        <v>0.2816326530612245</v>
+        <v>0.2172185430463576</v>
       </c>
       <c r="W7">
-        <v>0.2407628128724672</v>
+        <v>0.1592074592074592</v>
       </c>
       <c r="X7">
-        <v>0.07148141597386588</v>
+        <v>0.06072829687885595</v>
       </c>
       <c r="Y7">
-        <v>0.1692813968986013</v>
+        <v>0.09847916232860326</v>
       </c>
       <c r="Z7">
-        <v>5.516860143725812</v>
+        <v>54.95049504950496</v>
       </c>
       <c r="AA7">
-        <v>1.125164343447925</v>
+        <v>3.805666280913806</v>
       </c>
       <c r="AB7">
-        <v>0.07135976946925636</v>
+        <v>0.0605759744281195</v>
       </c>
       <c r="AC7">
-        <v>1.053804573978669</v>
+        <v>3.745090306485687</v>
       </c>
       <c r="AD7">
-        <v>0.159</v>
+        <v>0.254</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.159</v>
+        <v>0.254</v>
       </c>
       <c r="AG7">
-        <v>-8.120999999999999</v>
+        <v>-6.305999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.005379072363747082</v>
+        <v>0.0083404478886189</v>
       </c>
       <c r="AI7">
-        <v>0.01796813199231552</v>
+        <v>0.04107373868046572</v>
       </c>
       <c r="AJ7">
-        <v>-0.3816438742422106</v>
+        <v>-0.2639156273541475</v>
       </c>
       <c r="AK7">
-        <v>-14.27240773286465</v>
+        <v>16.7712765957447</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1306,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>0.05179153094462541</v>
+        <v>0.2373831775700934</v>
       </c>
       <c r="AP7">
-        <v>-2.645276872964169</v>
+        <v>-5.893457943925233</v>
       </c>
     </row>
     <row r="8">
@@ -1320,7 +1287,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SBI Holdings, Inc. (TSE:8473)</t>
+          <t>Strike Company,Limited (TSE:6196)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1328,122 +1295,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.261</v>
-      </c>
-      <c r="E8">
-        <v>0.505</v>
-      </c>
       <c r="G8">
-        <v>0.271741752850916</v>
+        <v>0.3833693304535638</v>
       </c>
       <c r="H8">
-        <v>0.2693130458559182</v>
+        <v>0.3833693304535638</v>
       </c>
       <c r="I8">
-        <v>0.1367152944204076</v>
+        <v>0.3758099352051836</v>
       </c>
       <c r="J8">
-        <v>0.1170028307859708</v>
+        <v>0.2796976241900648</v>
       </c>
       <c r="K8">
-        <v>2059.9</v>
+        <v>25.9</v>
       </c>
       <c r="L8">
-        <v>0.3313174529136442</v>
+        <v>0.2796976241900648</v>
       </c>
       <c r="M8">
-        <v>282.893</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.05451152304609218</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.137333365697364</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>282.776</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.05448897795591182</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.1372765668236322</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>0.1170000000000186</v>
-      </c>
-      <c r="T8">
-        <v>0.0004135839345618966</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>26440.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="V8">
-        <v>5.094939879759519</v>
+        <v>0.1437709412123058</v>
       </c>
       <c r="W8">
-        <v>0.3778870319751977</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="X8">
-        <v>0.1867886339717466</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="Y8">
-        <v>0.191098398003451</v>
+        <v>0.2727322516853921</v>
       </c>
       <c r="Z8">
-        <v>0.6019091322742102</v>
+        <v>4.95187165775401</v>
       </c>
       <c r="AA8">
-        <v>0.07042507235200994</v>
+        <v>1.385026737967914</v>
       </c>
       <c r="AB8">
-        <v>0.06855328045798961</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="AC8">
-        <v>0.001871791894020328</v>
+        <v>1.324425656319973</v>
       </c>
       <c r="AD8">
-        <v>23968.3</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>23968.3</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>-2472.400000000001</v>
+        <v>-94.40000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.8220173606466857</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.6676071951824142</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.9099072574709268</v>
+        <v>-0.167911775168979</v>
       </c>
       <c r="AK8">
-        <v>-0.2613226791810679</v>
+        <v>-34.96296296296311</v>
       </c>
       <c r="AL8">
-        <v>91.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>68.5</v>
+        <v>-0.013</v>
       </c>
       <c r="AN8">
-        <v>20.43856058668031</v>
-      </c>
-      <c r="AO8">
-        <v>9.309967141292443</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>-2.10829709218044</v>
+        <v>-2.659154929577465</v>
       </c>
       <c r="AQ8">
-        <v>12.40875912408759</v>
+        <v>-2676.923076923077</v>
       </c>
     </row>
     <row r="9">
@@ -1454,7 +1409,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FinTech Global Incorporated (TSE:8789)</t>
+          <t>SBI Holdings, Inc. (TSE:8473)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1463,115 +1418,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.05309999999999999</v>
+        <v>0.243</v>
+      </c>
+      <c r="E9">
+        <v>0.0138</v>
       </c>
       <c r="G9">
-        <v>0.1222395023328149</v>
+        <v>0.1763949253286757</v>
       </c>
       <c r="H9">
-        <v>0.1222395023328149</v>
+        <v>0.1750003384919507</v>
       </c>
       <c r="I9">
-        <v>0.06731758871213177</v>
+        <v>0.1263522753428924</v>
       </c>
       <c r="J9">
-        <v>0.05180298818863265</v>
+        <v>0.08677646482329687</v>
       </c>
       <c r="K9">
-        <v>1.22</v>
+        <v>429.4</v>
       </c>
       <c r="L9">
-        <v>0.01897356143079316</v>
+        <v>0.05813937744560434</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>221.3135</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.03570206004291084</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.5154017233348859</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>221.2265</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.03568802529481038</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.5151991150442479</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.08699999999998909</v>
+      </c>
+      <c r="T9">
+        <v>0.0003931075149052773</v>
       </c>
       <c r="U9">
-        <v>16.4</v>
+        <v>23178.1</v>
       </c>
       <c r="V9">
-        <v>0.191812865497076</v>
+        <v>3.739066608591847</v>
       </c>
       <c r="W9">
-        <v>0.02125435540069686</v>
+        <v>0.06165996553704767</v>
       </c>
       <c r="X9">
-        <v>0.08916683435978956</v>
+        <v>0.1236564617607285</v>
       </c>
       <c r="Y9">
-        <v>-0.06791247895909269</v>
+        <v>-0.06199649622368086</v>
       </c>
       <c r="Z9">
-        <v>0.6170979596817553</v>
+        <v>1.644336094042213</v>
       </c>
       <c r="AA9">
-        <v>0.03196751831662328</v>
+        <v>0.1426896732223314</v>
       </c>
       <c r="AB9">
-        <v>0.07239339156205893</v>
+        <v>0.05817318417967055</v>
       </c>
       <c r="AC9">
-        <v>-0.04042587324543565</v>
+        <v>0.08451648904266088</v>
       </c>
       <c r="AD9">
-        <v>56.2</v>
+        <v>25841.9</v>
       </c>
       <c r="AE9">
-        <v>4.757395229049637</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>60.95739522904964</v>
+        <v>25841.9</v>
       </c>
       <c r="AG9">
-        <v>44.55739522904964</v>
+        <v>2663.800000000003</v>
       </c>
       <c r="AH9">
-        <v>0.416212476903036</v>
+        <v>0.8065310479139097</v>
       </c>
       <c r="AI9">
-        <v>0.5293398231855153</v>
+        <v>0.6840987846491471</v>
       </c>
       <c r="AJ9">
-        <v>0.3425979364770277</v>
+        <v>0.3005630338384468</v>
       </c>
       <c r="AK9">
-        <v>0.4511803407299974</v>
+        <v>0.1824895526478045</v>
       </c>
       <c r="AL9">
-        <v>0.822</v>
+        <v>207.8</v>
       </c>
       <c r="AM9">
-        <v>0.8149999999999999</v>
+        <v>174.7</v>
       </c>
       <c r="AN9">
-        <v>6.115342763873775</v>
+        <v>19.57719696969697</v>
       </c>
       <c r="AO9">
-        <v>4.805352798053528</v>
+        <v>4.490856592877767</v>
       </c>
       <c r="AP9">
-        <v>4.848465204466772</v>
+        <v>2.018030303030305</v>
       </c>
       <c r="AQ9">
-        <v>4.846625766871166</v>
+        <v>5.341728677733257</v>
       </c>
     </row>
     <row r="10">
@@ -1582,7 +1543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Akatsuki Corp. (TSE:8737)</t>
+          <t>FinTech Global Incorporated (TSE:8789)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1591,121 +1552,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.242</v>
+        <v>0.203</v>
       </c>
       <c r="E10">
-        <v>-0.224</v>
+        <v>0.74</v>
       </c>
       <c r="G10">
-        <v>0.06952789699570815</v>
+        <v>0.1942215088282504</v>
       </c>
       <c r="H10">
-        <v>0.06952789699570815</v>
+        <v>0.1942215088282504</v>
       </c>
       <c r="I10">
-        <v>0.02793991416309013</v>
+        <v>0.1526656039140839</v>
       </c>
       <c r="J10">
-        <v>0.01485921512985697</v>
+        <v>0.1375241792635887</v>
       </c>
       <c r="K10">
-        <v>2.87</v>
+        <v>10.7</v>
       </c>
       <c r="L10">
-        <v>0.01231759656652361</v>
+        <v>0.1717495987158908</v>
       </c>
       <c r="M10">
-        <v>4.8268</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.06722562674094708</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>1.681811846689895</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>3.8068</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.05301949860724234</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>1.326411149825784</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>1.02</v>
-      </c>
-      <c r="T10">
-        <v>0.2113201292781968</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>77.40000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="V10">
-        <v>1.077994428969359</v>
+        <v>0.2275379229871645</v>
       </c>
       <c r="W10">
-        <v>0.02238689547581903</v>
+        <v>0.2331154684095861</v>
       </c>
       <c r="X10">
-        <v>0.1485955889985768</v>
+        <v>0.07032499447474588</v>
       </c>
       <c r="Y10">
-        <v>-0.1262086935227578</v>
+        <v>0.1627904739348402</v>
       </c>
       <c r="Z10">
-        <v>0.9889643463497453</v>
+        <v>0.7016898553895204</v>
       </c>
       <c r="AA10">
-        <v>0.01469523397816924</v>
+        <v>0.09649932146003004</v>
       </c>
       <c r="AB10">
-        <v>0.06877917383277143</v>
+        <v>0.05869850292348498</v>
       </c>
       <c r="AC10">
-        <v>-0.05408393985460219</v>
+        <v>0.03780081853654507</v>
       </c>
       <c r="AD10">
-        <v>221.9</v>
+        <v>51.2</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>3.894664380762871</v>
       </c>
       <c r="AF10">
-        <v>221.9</v>
+        <v>55.09466438076287</v>
       </c>
       <c r="AG10">
-        <v>144.5</v>
+        <v>35.59466438076287</v>
       </c>
       <c r="AH10">
-        <v>0.7555328566564522</v>
+        <v>0.3913121610330753</v>
       </c>
       <c r="AI10">
-        <v>0.6865717821782179</v>
+        <v>0.466925048432488</v>
       </c>
       <c r="AJ10">
-        <v>0.6680536292186777</v>
+        <v>0.2934561430420853</v>
       </c>
       <c r="AK10">
-        <v>0.5878763222131814</v>
+        <v>0.3613867269313211</v>
       </c>
       <c r="AL10">
-        <v>2.73</v>
+        <v>0.864</v>
       </c>
       <c r="AM10">
-        <v>1.49</v>
+        <v>0.764</v>
       </c>
       <c r="AN10">
-        <v>23.78349410503751</v>
+        <v>3.823749066467513</v>
       </c>
       <c r="AO10">
-        <v>2.384615384615385</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="AP10">
-        <v>15.48767416934619</v>
+        <v>2.658302044866533</v>
       </c>
       <c r="AQ10">
-        <v>4.369127516778524</v>
+        <v>11.78010471204188</v>
       </c>
     </row>
     <row r="11">
@@ -1716,7 +1674,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mito Securities Co., Ltd. (TSE:8622)</t>
+          <t>Akatsuki Corp. (TSE:8737)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1725,37 +1683,37 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.04099999999999999</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="E11">
-        <v>-0.19</v>
+        <v>0.205</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.05614973262032086</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.05614973262032086</v>
       </c>
       <c r="I11">
-        <v>0.01995891706814959</v>
+        <v>0.06651069518716578</v>
       </c>
       <c r="J11">
-        <v>0.01449204999437766</v>
+        <v>0.04465718105423988</v>
       </c>
       <c r="K11">
-        <v>4.47</v>
+        <v>12.5</v>
       </c>
       <c r="L11">
-        <v>0.05289940828402367</v>
+        <v>0.04177807486631016</v>
       </c>
       <c r="M11">
-        <v>0.477</v>
+        <v>1.34</v>
       </c>
       <c r="N11">
-        <v>0.004462114125350795</v>
+        <v>0.01397288842544317</v>
       </c>
       <c r="O11">
-        <v>0.1067114093959732</v>
+        <v>0.1072</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1767,76 +1725,79 @@
         <v>-0</v>
       </c>
       <c r="S11">
-        <v>0.477</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
         <v>1</v>
       </c>
       <c r="U11">
-        <v>160.4</v>
+        <v>126.3</v>
       </c>
       <c r="V11">
-        <v>1.500467726847521</v>
+        <v>1.316996871741397</v>
       </c>
       <c r="W11">
-        <v>0.01246861924686192</v>
+        <v>0.1292657704239917</v>
       </c>
       <c r="X11">
-        <v>0.08022381748483012</v>
+        <v>0.09881725021301811</v>
       </c>
       <c r="Y11">
-        <v>-0.0677551982379682</v>
+        <v>0.03044852021097362</v>
       </c>
       <c r="Z11">
-        <v>0.5973109378033021</v>
+        <v>1.286052009456265</v>
       </c>
       <c r="AA11">
-        <v>0.008656259972834061</v>
+        <v>0.05743145743145743</v>
       </c>
       <c r="AB11">
-        <v>0.07045575879337379</v>
+        <v>0.05422876778597634</v>
       </c>
       <c r="AC11">
-        <v>-0.06179949882053973</v>
+        <v>0.003202689645481094</v>
       </c>
       <c r="AD11">
-        <v>28.5</v>
+        <v>242.3</v>
       </c>
       <c r="AE11">
-        <v>9.467357538706796</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>37.96735753870679</v>
+        <v>242.3</v>
       </c>
       <c r="AG11">
-        <v>-122.4326424612932</v>
+        <v>116</v>
       </c>
       <c r="AH11">
-        <v>0.2620835927690776</v>
+        <v>0.7164399763453577</v>
       </c>
       <c r="AI11">
-        <v>0.1238871175176023</v>
+        <v>0.69786866359447</v>
       </c>
       <c r="AJ11">
-        <v>7.88228035032616</v>
+        <v>0.5474280320906088</v>
       </c>
       <c r="AK11">
-        <v>-0.8381930400079254</v>
+        <v>0.5251244907197827</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AM11">
-        <v>-1.98</v>
+        <v>-0.9499999999999997</v>
       </c>
       <c r="AN11">
-        <v>7.960893854748603</v>
+        <v>10.67400881057269</v>
+      </c>
+      <c r="AO11">
+        <v>6.83848797250859</v>
       </c>
       <c r="AP11">
-        <v>-34.19906214002604</v>
+        <v>5.110132158590309</v>
       </c>
       <c r="AQ11">
-        <v>-0</v>
+        <v>-20.94736842105264</v>
       </c>
     </row>
     <row r="12">
@@ -1847,7 +1808,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Okasan Securities Group Inc. (TSE:8609)</t>
+          <t>Kobayashi Yoko Co., Ltd. (TSE:8742)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1856,118 +1817,112 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0295</v>
-      </c>
-      <c r="E12">
-        <v>0.0152</v>
+        <v>0.075</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.05228758169934641</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.05228758169934641</v>
       </c>
       <c r="I12">
-        <v>0.01683895030475693</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="J12">
-        <v>0.01275479504277308</v>
+        <v>0.05296148738379814</v>
       </c>
       <c r="K12">
-        <v>52.6</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>0.1102263202011735</v>
+        <v>0.06535947712418301</v>
       </c>
       <c r="M12">
-        <v>22.6582</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.03581757824849826</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.4307642585551331</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>22.6512</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.03580651280429972</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.4306311787072243</v>
+        <v>-0</v>
       </c>
       <c r="S12">
-        <v>0.00700000000000145</v>
-      </c>
-      <c r="T12">
-        <v>0.0003089389271875722</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>566.4</v>
+        <v>20.8</v>
       </c>
       <c r="V12">
-        <v>0.8953525134366107</v>
+        <v>0.9904761904761905</v>
       </c>
       <c r="W12">
-        <v>0.0345370978332239</v>
+        <v>0.03327787021630615</v>
       </c>
       <c r="X12">
-        <v>0.1276877684991462</v>
+        <v>0.06064429762064791</v>
       </c>
       <c r="Y12">
-        <v>-0.09315067066592231</v>
+        <v>-0.02736642740434175</v>
       </c>
       <c r="Z12">
-        <v>0.2265560251753657</v>
+        <v>0.7401136775910024</v>
       </c>
       <c r="AA12">
-        <v>0.002889675666817129</v>
+        <v>0.03919752119831232</v>
       </c>
       <c r="AB12">
-        <v>0.06899268664881975</v>
+        <v>0.0605757414366927</v>
       </c>
       <c r="AC12">
-        <v>-0.06610301098200262</v>
+        <v>-0.02137822023838038</v>
       </c>
       <c r="AD12">
-        <v>1381.1</v>
+        <v>0.06</v>
       </c>
       <c r="AE12">
-        <v>44.82226457284996</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1425.92226457285</v>
+        <v>0.06</v>
       </c>
       <c r="AG12">
-        <v>859.5222645728498</v>
+        <v>-20.74</v>
       </c>
       <c r="AH12">
-        <v>0.6926921749222534</v>
+        <v>0.002849002849002849</v>
       </c>
       <c r="AI12">
-        <v>0.5271388273759799</v>
+        <v>0.0009762447120078099</v>
       </c>
       <c r="AJ12">
-        <v>0.5760401040721053</v>
+        <v>-79.76923076923138</v>
       </c>
       <c r="AK12">
-        <v>0.4019046648915925</v>
+        <v>-0.5100836202656174</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-10.6</v>
+        <v>-0.308</v>
       </c>
       <c r="AN12">
-        <v>81.24117647058823</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="AP12">
-        <v>50.56013321016763</v>
+        <v>-9.096491228070176</v>
       </c>
       <c r="AQ12">
-        <v>-0</v>
+        <v>-6.623376623376624</v>
       </c>
     </row>
     <row r="13">
@@ -1978,7 +1933,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tokai Tokyo Financial Holdings, Inc. (TSE:8616)</t>
+          <t>Okasan Securities Group Inc. (TSE:8609)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1987,10 +1942,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.00229</v>
+        <v>-0.0144</v>
       </c>
       <c r="E13">
-        <v>-0.303</v>
+        <v>0.0706</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1999,103 +1954,103 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.02084632254999479</v>
+        <v>0.01749259809558059</v>
       </c>
       <c r="J13">
-        <v>0.01333445804491046</v>
+        <v>0.01142373753180773</v>
       </c>
       <c r="K13">
-        <v>28</v>
+        <v>56.9</v>
       </c>
       <c r="L13">
-        <v>0.05372217958557175</v>
+        <v>0.1174891596118109</v>
       </c>
       <c r="M13">
-        <v>37.7872</v>
+        <v>30.4216</v>
       </c>
       <c r="N13">
-        <v>0.0567801652892562</v>
+        <v>0.03056218605585695</v>
       </c>
       <c r="O13">
-        <v>1.349542857142857</v>
+        <v>0.5346502636203867</v>
       </c>
       <c r="P13">
-        <v>37.7872</v>
+        <v>13.7216</v>
       </c>
       <c r="Q13">
-        <v>0.0567801652892562</v>
+        <v>0.01378501105083384</v>
       </c>
       <c r="R13">
-        <v>1.349542857142857</v>
+        <v>0.2411528998242531</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.5489520603781524</v>
       </c>
       <c r="U13">
-        <v>554.3</v>
+        <v>550</v>
       </c>
       <c r="V13">
-        <v>0.8329075882794891</v>
+        <v>0.5525416917821981</v>
       </c>
       <c r="W13">
-        <v>0.01811711420252346</v>
+        <v>0.04911099602969101</v>
       </c>
       <c r="X13">
-        <v>0.2612923696305705</v>
+        <v>0.08908262124503359</v>
       </c>
       <c r="Y13">
-        <v>-0.243175255428047</v>
+        <v>-0.03997162521534258</v>
       </c>
       <c r="Z13">
-        <v>0.06406825174880808</v>
+        <v>0.2422176182318921</v>
       </c>
       <c r="AA13">
-        <v>0.0008543154149552424</v>
+        <v>0.002767030496260744</v>
       </c>
       <c r="AB13">
-        <v>0.06834366747012501</v>
+        <v>0.05479178833976736</v>
       </c>
       <c r="AC13">
-        <v>-0.06748935205516976</v>
+        <v>-0.05202475784350662</v>
       </c>
       <c r="AD13">
-        <v>5037.1</v>
+        <v>1848.2</v>
       </c>
       <c r="AE13">
-        <v>20.17448343471359</v>
+        <v>26.14167371155159</v>
       </c>
       <c r="AF13">
-        <v>5057.274483434714</v>
+        <v>1874.341673711552</v>
       </c>
       <c r="AG13">
-        <v>4502.974483434714</v>
+        <v>1324.341673711552</v>
       </c>
       <c r="AH13">
-        <v>0.8837102524437451</v>
+        <v>0.6531395110861635</v>
       </c>
       <c r="AI13">
-        <v>0.799130105789718</v>
+        <v>0.5853217416720143</v>
       </c>
       <c r="AJ13">
-        <v>0.8712386020027826</v>
+        <v>0.5709004966887649</v>
       </c>
       <c r="AK13">
-        <v>0.7798473178032822</v>
+        <v>0.4993291851335198</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-5.07</v>
+        <v>-10.4</v>
       </c>
       <c r="AN13">
-        <v>338.0604026845638</v>
+        <v>134.9051094890511</v>
       </c>
       <c r="AP13">
-        <v>302.213052579511</v>
+        <v>96.66727545339793</v>
       </c>
       <c r="AQ13">
         <v>-0</v>
@@ -2109,7 +2064,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GMO Financial Holdings, Inc. (TSE:7177)</t>
+          <t>Tokai Tokyo Financial Holdings, Inc. (TSE:8616)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2117,6 +2072,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D14">
+        <v>-0.009719999999999999</v>
+      </c>
+      <c r="E14">
+        <v>-0.127</v>
+      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2124,34 +2085,34 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>-0.000101862983304059</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>-6.022351962146701e-05</v>
       </c>
       <c r="K14">
-        <v>31.8</v>
+        <v>38.6</v>
       </c>
       <c r="L14">
-        <v>0.103515625</v>
+        <v>0.07669382078283331</v>
       </c>
       <c r="M14">
-        <v>25.014</v>
+        <v>33.40620000000001</v>
       </c>
       <c r="N14">
-        <v>0.05675970047651464</v>
+        <v>0.03590520206362855</v>
       </c>
       <c r="O14">
-        <v>0.7866037735849056</v>
+        <v>0.8654455958549224</v>
       </c>
       <c r="P14">
-        <v>25.014</v>
+        <v>33.40620000000001</v>
       </c>
       <c r="Q14">
-        <v>0.05675970047651464</v>
+        <v>0.03590520206362855</v>
       </c>
       <c r="R14">
-        <v>0.7866037735849056</v>
+        <v>0.8654455958549224</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2160,61 +2121,70 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>417.4</v>
+        <v>740.8</v>
       </c>
       <c r="V14">
-        <v>0.9471295665985932</v>
+        <v>0.7962166809974205</v>
       </c>
       <c r="W14">
-        <v>0.09031525134904857</v>
+        <v>0.03270077939681464</v>
       </c>
       <c r="X14">
-        <v>0.1507057023259479</v>
+        <v>0.1284070412204628</v>
       </c>
       <c r="Y14">
-        <v>-0.06039045097689931</v>
+        <v>-0.09570626182364821</v>
       </c>
       <c r="Z14">
-        <v>0.2571356825981418</v>
+        <v>0.08772180045175208</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>-5.282915570736505e-06</v>
       </c>
       <c r="AB14">
-        <v>0.06876237820743114</v>
+        <v>0.05332888806164252</v>
       </c>
       <c r="AC14">
-        <v>-0.06876237820743114</v>
+        <v>-0.05333417097721325</v>
       </c>
       <c r="AD14">
-        <v>1399.2</v>
+        <v>4096.6</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>74.25633819748467</v>
       </c>
       <c r="AF14">
-        <v>1399.2</v>
+        <v>4170.856338197485</v>
       </c>
       <c r="AG14">
-        <v>981.8000000000001</v>
+        <v>3430.056338197485</v>
       </c>
       <c r="AH14">
-        <v>0.7604761128322192</v>
+        <v>0.8176135566775392</v>
       </c>
       <c r="AI14">
-        <v>0.8252919664975816</v>
+        <v>0.7696788971702331</v>
       </c>
       <c r="AJ14">
-        <v>0.6901933216168717</v>
+        <v>0.7866278371257339</v>
       </c>
       <c r="AK14">
-        <v>0.7682316118935838</v>
+        <v>0.7332068640354806</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-7.18</v>
+      </c>
+      <c r="AN14">
+        <v>276.7972972972973</v>
+      </c>
+      <c r="AP14">
+        <v>231.760563391722</v>
+      </c>
+      <c r="AQ14">
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2225,7 +2195,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HS Holdings Co., Ltd. (TSE:8699)</t>
+          <t>Traders Holdings Co.,Ltd. (TSE:8704)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2234,109 +2204,112 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0775</v>
-      </c>
-      <c r="E15">
-        <v>0.165</v>
+        <v>0.358</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.001730103806228374</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.00774831687030115</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.00679467787087947</v>
       </c>
       <c r="K15">
-        <v>80.7</v>
+        <v>21.6</v>
       </c>
       <c r="L15">
-        <v>0.1840784671532847</v>
+        <v>0.3737024221453288</v>
       </c>
       <c r="M15">
-        <v>68.6528</v>
+        <v>7.4027</v>
       </c>
       <c r="N15">
-        <v>0.2400447552447552</v>
+        <v>0.06944371482176361</v>
       </c>
       <c r="O15">
-        <v>0.850716232961586</v>
+        <v>0.3427175925925926</v>
       </c>
       <c r="P15">
-        <v>2.1528</v>
+        <v>4.6927</v>
       </c>
       <c r="Q15">
-        <v>0.007527272727272727</v>
+        <v>0.04402157598499062</v>
       </c>
       <c r="R15">
-        <v>0.02667657992565056</v>
+        <v>0.2172546296296296</v>
       </c>
       <c r="S15">
-        <v>66.5</v>
+        <v>2.71</v>
       </c>
       <c r="T15">
-        <v>0.9686422112426587</v>
+        <v>0.3660826455212287</v>
       </c>
       <c r="U15">
-        <v>706.4</v>
+        <v>42.3</v>
       </c>
       <c r="V15">
-        <v>2.46993006993007</v>
+        <v>0.3968105065666041</v>
       </c>
       <c r="W15">
-        <v>0.1511802173098539</v>
+        <v>0.3042253521126761</v>
       </c>
       <c r="X15">
-        <v>0.1195193997199579</v>
+        <v>0.06321340115066808</v>
       </c>
       <c r="Y15">
-        <v>0.03166081758989603</v>
+        <v>0.241011950962008</v>
       </c>
       <c r="Z15">
-        <v>1.588981515041682</v>
+        <v>0.8959748904379872</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.006087860760922648</v>
       </c>
       <c r="AB15">
-        <v>0.06910925129187688</v>
+        <v>0.05988503199600906</v>
       </c>
       <c r="AC15">
-        <v>-0.06910925129187688</v>
+        <v>-0.05379717123508641</v>
       </c>
       <c r="AD15">
-        <v>551.2</v>
+        <v>14.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>4.110736424482968</v>
       </c>
       <c r="AF15">
-        <v>551.2</v>
+        <v>18.41073642448297</v>
       </c>
       <c r="AG15">
-        <v>-155.1999999999999</v>
+        <v>-23.88926357551703</v>
       </c>
       <c r="AH15">
-        <v>0.6583850931677019</v>
+        <v>0.1472732418915443</v>
       </c>
       <c r="AI15">
-        <v>0.4746404891070352</v>
+        <v>0.1771783846211402</v>
       </c>
       <c r="AJ15">
-        <v>-1.186544342507644</v>
+        <v>-0.2888290518042786</v>
       </c>
       <c r="AK15">
-        <v>-0.341173884370191</v>
+        <v>-0.387745139271276</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
         <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>11.25984251968504</v>
+      </c>
+      <c r="AP15">
+        <v>-18.81044376024963</v>
       </c>
     </row>
     <row r="16">
@@ -2347,7 +2320,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Matsui Securities Co., Ltd. (TSE:8628)</t>
+          <t>GMO Financial Holdings, Inc. (TSE:7177)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2356,10 +2329,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.00945</v>
+        <v>0.122</v>
       </c>
       <c r="E16">
-        <v>-0.0443</v>
+        <v>0.0895</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2374,28 +2347,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>61.5</v>
+        <v>34.9</v>
       </c>
       <c r="L16">
-        <v>0.3101361573373676</v>
+        <v>0.12301727176595</v>
       </c>
       <c r="M16">
-        <v>71</v>
+        <v>20.178</v>
       </c>
       <c r="N16">
-        <v>0.04638400731691383</v>
+        <v>0.03201332698714898</v>
       </c>
       <c r="O16">
-        <v>1.154471544715447</v>
+        <v>0.5781661891117479</v>
       </c>
       <c r="P16">
-        <v>71</v>
+        <v>20.178</v>
       </c>
       <c r="Q16">
-        <v>0.04638400731691383</v>
+        <v>0.03201332698714898</v>
       </c>
       <c r="R16">
-        <v>1.154471544715447</v>
+        <v>0.5781661891117479</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2404,64 +2377,61 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>429.4</v>
+        <v>513.8</v>
       </c>
       <c r="V16">
-        <v>0.2805252498856732</v>
+        <v>0.8151673806124068</v>
       </c>
       <c r="W16">
-        <v>0.08701188455008489</v>
+        <v>0.1233651466949452</v>
       </c>
       <c r="X16">
-        <v>0.1004535044074719</v>
+        <v>0.09857944027393334</v>
       </c>
       <c r="Y16">
-        <v>-0.01344161985738697</v>
+        <v>0.02478570642101188</v>
       </c>
       <c r="Z16">
-        <v>0.08830208843567708</v>
+        <v>0.2375251172136638</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.06951828350877937</v>
+        <v>0.0542400622476107</v>
       </c>
       <c r="AC16">
-        <v>-0.06951828350877937</v>
+        <v>-0.0542400622476107</v>
       </c>
       <c r="AD16">
-        <v>1782.5</v>
+        <v>1582.6</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1782.5</v>
+        <v>1582.6</v>
       </c>
       <c r="AG16">
-        <v>1353.1</v>
+        <v>1068.8</v>
       </c>
       <c r="AH16">
-        <v>0.5379995170831825</v>
+        <v>0.7151701387319808</v>
       </c>
       <c r="AI16">
-        <v>0.7689155379173497</v>
+        <v>0.8351891920417964</v>
       </c>
       <c r="AJ16">
-        <v>0.4692072959289825</v>
+        <v>0.6290389029486199</v>
       </c>
       <c r="AK16">
-        <v>0.7163807708598051</v>
+        <v>0.7738758960249077</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-0.131</v>
-      </c>
-      <c r="AQ16">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2472,7 +2442,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INV Inc. (TSE:7338)</t>
+          <t>Matsui Securities Co., Ltd. (TSE:8628)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2481,10 +2451,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0767</v>
+        <v>0.009990000000000001</v>
       </c>
       <c r="E17">
-        <v>0.291</v>
+        <v>-0.0741</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2499,28 +2469,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>3.27</v>
+        <v>58.3</v>
       </c>
       <c r="L17">
-        <v>0.08605263157894737</v>
+        <v>0.2793483469094394</v>
       </c>
       <c r="M17">
-        <v>1.74636</v>
+        <v>68.9564</v>
       </c>
       <c r="N17">
-        <v>0.05151504424778761</v>
+        <v>0.05161793547421214</v>
       </c>
       <c r="O17">
-        <v>0.5340550458715596</v>
+        <v>1.182785591766724</v>
       </c>
       <c r="P17">
-        <v>1.74636</v>
+        <v>68.9564</v>
       </c>
       <c r="Q17">
-        <v>0.05151504424778761</v>
+        <v>0.05161793547421214</v>
       </c>
       <c r="R17">
-        <v>0.5340550458715596</v>
+        <v>1.182785591766724</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2529,61 +2499,64 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>57.5</v>
+        <v>375.1</v>
       </c>
       <c r="V17">
-        <v>1.696165191740413</v>
+        <v>0.2807844898570252</v>
       </c>
       <c r="W17">
-        <v>0.032897384305835</v>
+        <v>0.108829568788501</v>
       </c>
       <c r="X17">
-        <v>0.09508828344053563</v>
+        <v>0.0806213444138589</v>
       </c>
       <c r="Y17">
-        <v>-0.06219089913470063</v>
+        <v>0.02820822437464211</v>
       </c>
       <c r="Z17">
-        <v>0.6608695652173912</v>
+        <v>0.1104934349851758</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06969108574180394</v>
+        <v>0.05553452351614676</v>
       </c>
       <c r="AC17">
-        <v>-0.06969108574180394</v>
+        <v>-0.05553452351614676</v>
       </c>
       <c r="AD17">
-        <v>32.2</v>
+        <v>1768.2</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>32.2</v>
+        <v>1768.2</v>
       </c>
       <c r="AG17">
-        <v>-25.3</v>
+        <v>1393.1</v>
       </c>
       <c r="AH17">
-        <v>0.48714069591528</v>
+        <v>0.5696337102541799</v>
       </c>
       <c r="AI17">
-        <v>0.2809773123909249</v>
+        <v>0.7763435194942044</v>
       </c>
       <c r="AJ17">
-        <v>-2.941860465116278</v>
+        <v>0.5104800293147673</v>
       </c>
       <c r="AK17">
-        <v>-0.4430823117338002</v>
+        <v>0.7322470433639947</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>-0.469</v>
+      </c>
+      <c r="AQ17">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2594,7 +2567,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kyokuto Securities Co., Ltd. (TSE:8706)</t>
+          <t>Mito Securities Co., Ltd. (TSE:8622)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2603,10 +2576,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.08119999999999999</v>
+        <v>-0.0358</v>
       </c>
       <c r="E18">
-        <v>-0.163</v>
+        <v>-0.0322</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2615,103 +2588,100 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0.005265779741080137</v>
+        <v>0.006820515755075476</v>
       </c>
       <c r="J18">
-        <v>0.003508879397560876</v>
+        <v>0.005219589140342482</v>
       </c>
       <c r="K18">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="L18">
-        <v>0.2005649717514124</v>
+        <v>0.1328502415458937</v>
       </c>
       <c r="M18">
-        <v>7.719799999999999</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.05549820273184759</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>1.087295774647887</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>7.719799999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.05549820273184759</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>1.087295774647887</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>153.7</v>
+        <v>182.9</v>
       </c>
       <c r="V18">
-        <v>1.104960460100647</v>
+        <v>0.9256072874493928</v>
       </c>
       <c r="W18">
-        <v>0.01701006229036895</v>
+        <v>0.0409683426443203</v>
       </c>
       <c r="X18">
-        <v>0.08496132374048139</v>
+        <v>0.06331666910928488</v>
       </c>
       <c r="Y18">
-        <v>-0.06795126145011243</v>
+        <v>-0.02234832646496458</v>
       </c>
       <c r="Z18">
-        <v>0.109135317584858</v>
+        <v>0.577098770054017</v>
       </c>
       <c r="AA18">
-        <v>0.0003829426674197716</v>
+        <v>0.00301221847307895</v>
       </c>
       <c r="AB18">
-        <v>0.07014812537755062</v>
+        <v>0.05924727195776503</v>
       </c>
       <c r="AC18">
-        <v>-0.06976518271013085</v>
+        <v>-0.05623505348468608</v>
       </c>
       <c r="AD18">
-        <v>75.3</v>
+        <v>28.6</v>
       </c>
       <c r="AE18">
-        <v>0.4679569858288159</v>
+        <v>6.876306477398752</v>
       </c>
       <c r="AF18">
-        <v>75.76795698582882</v>
+        <v>35.47630647739875</v>
       </c>
       <c r="AG18">
-        <v>-77.93204301417117</v>
+        <v>-147.4236935226012</v>
       </c>
       <c r="AH18">
-        <v>0.3526256685673516</v>
+        <v>0.1522089783108815</v>
       </c>
       <c r="AI18">
-        <v>0.1932028245453178</v>
+        <v>0.1167458789026625</v>
       </c>
       <c r="AJ18">
-        <v>-1.274066469675065</v>
+        <v>-2.938113700915915</v>
       </c>
       <c r="AK18">
-        <v>-0.3268029969276013</v>
+        <v>-1.218616254829564</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-3.54</v>
+        <v>-1.62</v>
       </c>
       <c r="AN18">
-        <v>268.9285714285714</v>
+        <v>14.74226804123711</v>
       </c>
       <c r="AP18">
-        <v>-278.3287250506113</v>
+        <v>-75.991594599279</v>
       </c>
       <c r="AQ18">
         <v>-0</v>
@@ -2725,7 +2695,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aizawa Securities Group Co., Ltd. (TSE:8708)</t>
+          <t>Nomura Holdings, Inc. (TSE:8604)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2734,10 +2704,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.0124</v>
+        <v>0.0118</v>
       </c>
       <c r="E19">
-        <v>0.199</v>
+        <v>0.049</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2746,100 +2716,103 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>0.009051777313706018</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>0.005882072662428245</v>
       </c>
       <c r="K19">
-        <v>-5.77</v>
+        <v>889.7</v>
       </c>
       <c r="L19">
-        <v>-0.06347634763476347</v>
+        <v>0.09278146247862178</v>
       </c>
       <c r="M19">
-        <v>13.1502</v>
+        <v>485.9</v>
       </c>
       <c r="N19">
-        <v>0.06601506024096385</v>
+        <v>0.03562760754639508</v>
       </c>
       <c r="O19">
-        <v>-2.279064124783362</v>
+        <v>0.5461391480274249</v>
       </c>
       <c r="P19">
-        <v>7.430199999999999</v>
+        <v>341.8</v>
       </c>
       <c r="Q19">
-        <v>0.03730020080321285</v>
+        <v>0.02506177456134562</v>
       </c>
       <c r="R19">
-        <v>-1.287729636048527</v>
+        <v>0.3841744408227492</v>
       </c>
       <c r="S19">
-        <v>5.719999999999999</v>
+        <v>144.1</v>
       </c>
       <c r="T19">
-        <v>0.4349743730133382</v>
+        <v>0.296563078822803</v>
       </c>
       <c r="U19">
-        <v>146.8</v>
+        <v>27483.9</v>
       </c>
       <c r="V19">
-        <v>0.7369477911646587</v>
+        <v>2.01519984162249</v>
       </c>
       <c r="W19">
-        <v>-0.01110469591993841</v>
+        <v>0.04069804674991995</v>
       </c>
       <c r="X19">
-        <v>0.08157281255806598</v>
+        <v>0.3208328194542764</v>
       </c>
       <c r="Y19">
-        <v>-0.09267750847800439</v>
+        <v>-0.2801347727043565</v>
       </c>
       <c r="Z19">
-        <v>0.2656574217494228</v>
+        <v>0.04923092631910004</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>0.0002895798858475976</v>
       </c>
       <c r="AB19">
-        <v>0.07035973352695506</v>
+        <v>0.05688079834407785</v>
       </c>
       <c r="AC19">
-        <v>-0.07035973352695506</v>
+        <v>-0.05659121845823025</v>
       </c>
       <c r="AD19">
-        <v>81.5</v>
+        <v>233405.3</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1238.003484917051</v>
       </c>
       <c r="AF19">
-        <v>81.5</v>
+        <v>234643.303484917</v>
       </c>
       <c r="AG19">
-        <v>-65.30000000000001</v>
+        <v>207159.403484917</v>
       </c>
       <c r="AH19">
-        <v>0.2903455646597791</v>
+        <v>0.9450692286155284</v>
       </c>
       <c r="AI19">
-        <v>0.1748176748176748</v>
+        <v>0.9122245085194844</v>
       </c>
       <c r="AJ19">
-        <v>-0.487677371172517</v>
+        <v>0.9382316945115707</v>
       </c>
       <c r="AK19">
-        <v>-0.204445835942392</v>
+        <v>0.9017237544240114</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-3.1</v>
-      </c>
-      <c r="AQ19">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>697.9823564593302</v>
+      </c>
+      <c r="AP19">
+        <v>619.4958238185319</v>
       </c>
     </row>
     <row r="20">
@@ -2850,7 +2823,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IwaiCosmo Holdings, Inc. (TSE:8707)</t>
+          <t>Daiwa Securities Group Inc. (TSE:8601)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2859,10 +2832,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0179</v>
+        <v>0.0866</v>
       </c>
       <c r="E20">
-        <v>-0.0471</v>
+        <v>-0.021</v>
+      </c>
+      <c r="F20">
+        <v>0.0721</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2871,97 +2847,106 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.005280693000228314</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>0.003816560708394438</v>
       </c>
       <c r="K20">
-        <v>26</v>
+        <v>575.3</v>
       </c>
       <c r="L20">
-        <v>0.1893663510560815</v>
+        <v>0.07833179020750504</v>
       </c>
       <c r="M20">
-        <v>9.7525</v>
+        <v>470.072</v>
       </c>
       <c r="N20">
-        <v>0.04218209342560553</v>
+        <v>0.04911625185463816</v>
       </c>
       <c r="O20">
-        <v>0.3750961538461538</v>
+        <v>0.8170902138014949</v>
       </c>
       <c r="P20">
-        <v>9.7525</v>
+        <v>295.672</v>
       </c>
       <c r="Q20">
-        <v>0.04218209342560553</v>
+        <v>0.03089377886443901</v>
       </c>
       <c r="R20">
-        <v>0.3750961538461538</v>
+        <v>0.5139440292021554</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>174.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>0.3710069946731565</v>
       </c>
       <c r="U20">
-        <v>84.59999999999999</v>
+        <v>29483.9</v>
       </c>
       <c r="V20">
-        <v>0.365916955017301</v>
+        <v>3.080674147911312</v>
       </c>
       <c r="W20">
-        <v>0.05165905026822968</v>
+        <v>0.05792388240032219</v>
       </c>
       <c r="X20">
-        <v>0.08075198581698241</v>
+        <v>0.2441554183407987</v>
       </c>
       <c r="Y20">
-        <v>-0.02909293554875273</v>
+        <v>-0.1862315359404765</v>
       </c>
       <c r="Z20">
-        <v>0.2994547437295529</v>
+        <v>0.07409815152916457</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>0.0002828000936908667</v>
       </c>
       <c r="AB20">
-        <v>0.07041726521824627</v>
+        <v>0.05696425125322613</v>
       </c>
       <c r="AC20">
-        <v>-0.07041726521824627</v>
+        <v>-0.05668145115953527</v>
       </c>
       <c r="AD20">
-        <v>87</v>
+        <v>115863.5</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>279.0823916456158</v>
       </c>
       <c r="AF20">
-        <v>87</v>
+        <v>116142.5823916456</v>
       </c>
       <c r="AG20">
-        <v>2.400000000000006</v>
+        <v>86658.68239164562</v>
       </c>
       <c r="AH20">
-        <v>0.2734129478315525</v>
+        <v>0.923869559119235</v>
       </c>
       <c r="AI20">
-        <v>0.1834668916069169</v>
+        <v>0.9072584391892954</v>
       </c>
       <c r="AJ20">
-        <v>0.01027397260273975</v>
+        <v>0.9005437870663068</v>
       </c>
       <c r="AK20">
-        <v>0.006160164271047242</v>
+        <v>0.8795069356681189</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>-23.7</v>
+      </c>
+      <c r="AN20">
+        <v>1224.772727272727</v>
+      </c>
+      <c r="AP20">
+        <v>916.0537250702497</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -2972,7 +2957,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Traders Holdings Co.,Ltd. (TSE:8704)</t>
+          <t>Monex Group, Inc. (TSE:8698)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2981,10 +2966,13 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.374</v>
+        <v>0.08810000000000001</v>
+      </c>
+      <c r="E21">
+        <v>-0.00183</v>
       </c>
       <c r="G21">
-        <v>0.007527675276752767</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2996,91 +2984,94 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>18.8</v>
+        <v>42.9</v>
       </c>
       <c r="L21">
-        <v>0.3468634686346864</v>
+        <v>0.07893284268629254</v>
       </c>
       <c r="M21">
-        <v>4.261200000000001</v>
+        <v>47.5892</v>
       </c>
       <c r="N21">
-        <v>0.0517764277035237</v>
+        <v>0.03639431018660141</v>
       </c>
       <c r="O21">
-        <v>0.2266595744680851</v>
+        <v>1.109305361305361</v>
       </c>
       <c r="P21">
-        <v>2.1812</v>
+        <v>13.5892</v>
       </c>
       <c r="Q21">
-        <v>0.02650303766707169</v>
+        <v>0.01039247476292444</v>
       </c>
       <c r="R21">
-        <v>0.1160212765957447</v>
+        <v>0.3167645687645687</v>
       </c>
       <c r="S21">
-        <v>2.080000000000001</v>
+        <v>34</v>
       </c>
       <c r="T21">
-        <v>0.4881254106824369</v>
+        <v>0.7144478158910005</v>
       </c>
       <c r="U21">
-        <v>25.3</v>
+        <v>1010.6</v>
       </c>
       <c r="V21">
-        <v>0.307411907654921</v>
+        <v>0.7728663199755278</v>
       </c>
       <c r="W21">
-        <v>0.2625698324022347</v>
+        <v>0.05833559967364699</v>
       </c>
       <c r="X21">
-        <v>0.07581080468316508</v>
+        <v>0.09052374711840872</v>
       </c>
       <c r="Y21">
-        <v>0.1867590277190696</v>
+        <v>-0.03218814744476172</v>
       </c>
       <c r="Z21">
-        <v>1.168103448275862</v>
+        <v>0.2379076384329175</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.07083132933805628</v>
+        <v>0.05737153481542129</v>
       </c>
       <c r="AC21">
-        <v>-0.07083132933805628</v>
+        <v>-0.05737153481542129</v>
       </c>
       <c r="AD21">
-        <v>14.7</v>
+        <v>2586.8</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>14.7</v>
+        <v>2586.8</v>
       </c>
       <c r="AG21">
-        <v>-10.6</v>
+        <v>1576.2</v>
       </c>
       <c r="AH21">
-        <v>0.1515463917525773</v>
+        <v>0.6642358258011504</v>
       </c>
       <c r="AI21">
-        <v>0.1715285880980163</v>
+        <v>0.7869311267948406</v>
       </c>
       <c r="AJ21">
-        <v>-0.1478382147838215</v>
+        <v>0.5465704972605591</v>
       </c>
       <c r="AK21">
-        <v>-0.1754966887417219</v>
+        <v>0.6923482386014231</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>-2.44</v>
+      </c>
+      <c r="AQ21">
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -3091,7 +3082,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kobayashi Yoko Co., Ltd. (TSE:8742)</t>
+          <t>Kyokuto Securities Co., Ltd. (TSE:8706)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3100,43 +3091,46 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0512</v>
+        <v>-0.0572</v>
+      </c>
+      <c r="E22">
+        <v>-0.0102</v>
       </c>
       <c r="G22">
-        <v>-0.03330882352941177</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>-0.03330882352941177</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0.001029411764705882</v>
+        <v>0.00505723525640442</v>
       </c>
       <c r="J22">
-        <v>0.0005494995200877555</v>
+        <v>0.00351539523920795</v>
       </c>
       <c r="K22">
-        <v>0.166</v>
+        <v>22.8</v>
       </c>
       <c r="L22">
-        <v>0.006102941176470589</v>
+        <v>0.5615763546798029</v>
       </c>
       <c r="M22">
-        <v>0.2125</v>
+        <v>9.601899999999999</v>
       </c>
       <c r="N22">
-        <v>0.01011904761904762</v>
+        <v>0.0440656264341441</v>
       </c>
       <c r="O22">
-        <v>1.280120481927711</v>
+        <v>0.4211359649122806</v>
       </c>
       <c r="P22">
-        <v>0.2125</v>
+        <v>9.601899999999999</v>
       </c>
       <c r="Q22">
-        <v>0.01011904761904762</v>
+        <v>0.0440656264341441</v>
       </c>
       <c r="R22">
-        <v>1.280120481927711</v>
+        <v>0.4211359649122806</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3145,73 +3139,70 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>18.9</v>
+        <v>131.4</v>
       </c>
       <c r="V22">
-        <v>0.8999999999999999</v>
+        <v>0.6030289123451125</v>
       </c>
       <c r="W22">
-        <v>0.002381635581061693</v>
+        <v>0.07206068268015171</v>
       </c>
       <c r="X22">
-        <v>0.0715842886485451</v>
+        <v>0.06618577597921564</v>
       </c>
       <c r="Y22">
-        <v>-0.06920265306748341</v>
+        <v>0.005874906700936072</v>
       </c>
       <c r="Z22">
-        <v>0.6188850967007963</v>
+        <v>0.1704068155851257</v>
       </c>
       <c r="AA22">
-        <v>0.0003400770636265517</v>
+        <v>0.000599047308236538</v>
       </c>
       <c r="AB22">
-        <v>0.07131418254999124</v>
+        <v>0.05820263156361767</v>
       </c>
       <c r="AC22">
-        <v>-0.07097410548636468</v>
+        <v>-0.05760358425538113</v>
       </c>
       <c r="AD22">
-        <v>0.2</v>
+        <v>80.2</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>0.2533812429499026</v>
       </c>
       <c r="AF22">
-        <v>0.2</v>
+        <v>80.4533812429499</v>
       </c>
       <c r="AG22">
-        <v>-18.7</v>
+        <v>-50.9466187570501</v>
       </c>
       <c r="AH22">
-        <v>0.009433962264150945</v>
+        <v>0.2696580173074576</v>
       </c>
       <c r="AI22">
-        <v>0.003316749585406302</v>
+        <v>0.1894119853914295</v>
       </c>
       <c r="AJ22">
-        <v>-8.130434782608694</v>
+        <v>-0.3051547586383578</v>
       </c>
       <c r="AK22">
-        <v>-0.4516908212560385</v>
+        <v>-0.1736697853666702</v>
       </c>
       <c r="AL22">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>-0.256</v>
+        <v>-6.03</v>
       </c>
       <c r="AN22">
-        <v>0.8264462809917356</v>
-      </c>
-      <c r="AO22">
-        <v>4</v>
+        <v>313.28125</v>
       </c>
       <c r="AP22">
-        <v>-77.27272727272727</v>
+        <v>-199.0102295197269</v>
       </c>
       <c r="AQ22">
-        <v>-0.109375</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -3222,7 +3213,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marusan Securities Co., Ltd. (TSE:8613)</t>
+          <t>INV Inc. (TSE:7338)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3231,10 +3222,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.00291</v>
+        <v>0.0664</v>
       </c>
       <c r="E23">
-        <v>0.0611</v>
+        <v>-0.128</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3249,85 +3240,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>0.1083916083916084</v>
+        <v>0.05154639175257732</v>
       </c>
       <c r="M23">
-        <v>10.7505</v>
+        <v>0.74676</v>
       </c>
       <c r="N23">
-        <v>0.05410417715148465</v>
+        <v>0.02249277108433735</v>
       </c>
       <c r="O23">
-        <v>0.8669758064516129</v>
+        <v>0.37338</v>
       </c>
       <c r="P23">
-        <v>7.2705</v>
+        <v>0.74676</v>
       </c>
       <c r="Q23">
-        <v>0.03659033719174636</v>
+        <v>0.02249277108433735</v>
       </c>
       <c r="R23">
-        <v>0.5863306451612903</v>
+        <v>0.37338</v>
       </c>
       <c r="S23">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>0.3237058741453886</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>241</v>
+        <v>59.7</v>
       </c>
       <c r="V23">
-        <v>1.212883744338198</v>
+        <v>1.798192771084337</v>
       </c>
       <c r="W23">
-        <v>0.02934216753431141</v>
+        <v>0.02427184466019417</v>
       </c>
       <c r="X23">
-        <v>0.07386214049475731</v>
+        <v>0.06820943587898354</v>
       </c>
       <c r="Y23">
-        <v>-0.04451997296044591</v>
+        <v>-0.04393759121878936</v>
       </c>
       <c r="Z23">
-        <v>1.345882352941177</v>
+        <v>0.6795096322241679</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.07103551970893907</v>
+        <v>0.05762439394703003</v>
       </c>
       <c r="AC23">
-        <v>-0.07103551970893907</v>
+        <v>-0.05762439394703003</v>
       </c>
       <c r="AD23">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="AG23">
-        <v>-221</v>
+        <v>-43</v>
       </c>
       <c r="AH23">
-        <v>0.09144947416552356</v>
+        <v>0.3346693386773547</v>
       </c>
       <c r="AI23">
-        <v>0.05986231667165519</v>
+        <v>0.1741397288842544</v>
       </c>
       <c r="AJ23">
-        <v>9.910313901345287</v>
+        <v>4.387755102040818</v>
       </c>
       <c r="AK23">
-        <v>-2.373791621911922</v>
+        <v>-1.187845303867403</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3344,7 +3335,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ichiyoshi Securities Co., Ltd. (TSE:8624)</t>
+          <t>Toyo Securities Co., Ltd. (TSE:8614)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3353,10 +3344,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.0369</v>
-      </c>
-      <c r="E24">
-        <v>-0.138</v>
+        <v>-0.0677</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3371,91 +3359,91 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>10.5</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L24">
-        <v>0.08454106280193237</v>
+        <v>-0.1446969696969697</v>
       </c>
       <c r="M24">
-        <v>13.2133</v>
+        <v>1.0374</v>
       </c>
       <c r="N24">
-        <v>0.08248002496878902</v>
+        <v>0.006066666666666666</v>
       </c>
       <c r="O24">
-        <v>1.258409523809524</v>
+        <v>-0.1086282722513089</v>
       </c>
       <c r="P24">
-        <v>4.4933</v>
+        <v>1.0374</v>
       </c>
       <c r="Q24">
-        <v>0.02804806491885144</v>
+        <v>0.006066666666666666</v>
       </c>
       <c r="R24">
-        <v>0.4279333333333333</v>
+        <v>-0.1086282722513089</v>
       </c>
       <c r="S24">
-        <v>8.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>0.6599411199321896</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>126.4</v>
+        <v>191.9</v>
       </c>
       <c r="V24">
-        <v>0.7890137328339576</v>
+        <v>1.122222222222222</v>
       </c>
       <c r="W24">
-        <v>0.03929640718562875</v>
+        <v>-0.03770232925384919</v>
       </c>
       <c r="X24">
-        <v>0.07184240172030965</v>
+        <v>0.06704051430622467</v>
       </c>
       <c r="Y24">
-        <v>-0.0325459945346809</v>
+        <v>-0.1047428435600739</v>
       </c>
       <c r="Z24">
-        <v>1.287980918801204</v>
+        <v>0.4385382059800664</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.07128010423427249</v>
+        <v>0.05794516142648402</v>
       </c>
       <c r="AC24">
-        <v>-0.07128010423427249</v>
+        <v>-0.05794516142648402</v>
       </c>
       <c r="AD24">
-        <v>3.18</v>
+        <v>72.8</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>3.18</v>
+        <v>72.8</v>
       </c>
       <c r="AG24">
-        <v>-123.22</v>
+        <v>-119.1</v>
       </c>
       <c r="AH24">
-        <v>0.01946382666177011</v>
+        <v>0.2986054142739951</v>
       </c>
       <c r="AI24">
-        <v>0.01578320428826683</v>
+        <v>0.232811000959386</v>
       </c>
       <c r="AJ24">
-        <v>-3.332071389940509</v>
+        <v>-2.294797687861272</v>
       </c>
       <c r="AK24">
-        <v>-1.64118273841236</v>
+        <v>-0.9859271523178809</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-0.104</v>
+        <v>-1.74</v>
       </c>
       <c r="AQ24">
         <v>-0</v>
@@ -3469,7 +3457,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Imamura Securities Co., Ltd. (TSE:7175)</t>
+          <t>Aizawa Securities Group Co., Ltd. (TSE:8708)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3478,10 +3466,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.04</v>
+        <v>-0.00722</v>
       </c>
       <c r="E25">
-        <v>0.0761</v>
+        <v>-0.6859999999999999</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3496,88 +3484,94 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>4.73</v>
+        <v>0.027</v>
       </c>
       <c r="L25">
-        <v>0.1701438848920863</v>
+        <v>0.0002581261950286807</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>11.3424</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.03643559267587536</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>420.0888888888889</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>6.5424</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.02101638291037584</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>242.3111111111111</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="T25">
+        <v>0.4231908590774439</v>
       </c>
       <c r="U25">
-        <v>54.2</v>
+        <v>130.4</v>
       </c>
       <c r="V25">
-        <v>1.812709030100335</v>
+        <v>0.4188885319627369</v>
       </c>
       <c r="W25">
-        <v>0.05124593716143012</v>
+        <v>7.32899022801303e-05</v>
       </c>
       <c r="X25">
-        <v>0.07134623617821302</v>
+        <v>0.06530930430887089</v>
       </c>
       <c r="Y25">
-        <v>-0.0201002990167829</v>
+        <v>-0.06523601440659076</v>
       </c>
       <c r="Z25">
-        <v>1.478723404255319</v>
+        <v>0.3460871636734207</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.07134623617821302</v>
+        <v>0.05848969328203323</v>
       </c>
       <c r="AC25">
-        <v>-0.07134623617821302</v>
+        <v>-0.05848969328203323</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AG25">
-        <v>-54.2</v>
+        <v>-33.5</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>0.2373836354728074</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>0.2038712392173365</v>
       </c>
       <c r="AJ25">
-        <v>2.230452674897119</v>
+        <v>-0.1205903527717783</v>
       </c>
       <c r="AK25">
-        <v>-2.683168316831683</v>
+        <v>-0.09712960278341549</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>-2.86</v>
+      </c>
+      <c r="AQ25">
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -3588,7 +3582,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maruhachi Securities Co., Ltd. (TSE:8700)</t>
+          <t>IwaiCosmo Holdings, Inc. (TSE:8707)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3597,10 +3591,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.00422</v>
+        <v>-0.00536</v>
       </c>
       <c r="E26">
-        <v>-0.149</v>
+        <v>-0.0267</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3615,91 +3609,91 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1.35</v>
+        <v>28.8</v>
       </c>
       <c r="L26">
-        <v>0.07031250000000001</v>
+        <v>0.2035335689045936</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>12.596</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.04112308194580477</v>
       </c>
       <c r="O26">
-        <v>-0</v>
+        <v>0.4373611111111111</v>
       </c>
       <c r="P26">
-        <v>-0</v>
+        <v>12.596</v>
       </c>
       <c r="Q26">
-        <v>-0</v>
+        <v>0.04112308194580477</v>
       </c>
       <c r="R26">
-        <v>-0</v>
+        <v>0.4373611111111111</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
       <c r="U26">
-        <v>29.3</v>
+        <v>57</v>
       </c>
       <c r="V26">
-        <v>0.6894117647058824</v>
+        <v>0.1860920666013712</v>
       </c>
       <c r="W26">
-        <v>0.02064220183486239</v>
+        <v>0.0743801652892562</v>
       </c>
       <c r="X26">
-        <v>0.07134623617821302</v>
+        <v>0.06425038342416892</v>
       </c>
       <c r="Y26">
-        <v>-0.05070403434335063</v>
+        <v>0.01012978186508728</v>
       </c>
       <c r="Z26">
-        <v>0.7868852459016391</v>
+        <v>0.3631930184804928</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.07134623617821302</v>
+        <v>0.0588722620646842</v>
       </c>
       <c r="AC26">
-        <v>-0.07134623617821302</v>
+        <v>-0.0588722620646842</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AG26">
-        <v>-29.3</v>
+        <v>16.90000000000001</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>0.1943713834823777</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>0.1542475474848675</v>
       </c>
       <c r="AJ26">
-        <v>-2.21969696969697</v>
+        <v>0.05228960396039605</v>
       </c>
       <c r="AK26">
-        <v>-1.362790697674419</v>
+        <v>0.04003790570954751</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-0.062</v>
-      </c>
-      <c r="AQ26">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3710,7 +3704,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Kosei Securities Co., Ltd. (TSE:8617)</t>
+          <t>HS Holdings Co., Ltd. (TSE:8699)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3719,7 +3713,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.268</v>
+        <v>0.0625</v>
+      </c>
+      <c r="E27">
+        <v>0.049</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3734,82 +3731,85 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>-3.32</v>
+        <v>43.7</v>
       </c>
       <c r="L27">
-        <v>-1.55868544600939</v>
+        <v>0.09297872340425532</v>
       </c>
       <c r="M27">
-        <v>-0</v>
+        <v>10.0367</v>
       </c>
       <c r="N27">
-        <v>-0</v>
+        <v>0.04659563602599814</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>0.2296727688787185</v>
       </c>
       <c r="P27">
-        <v>-0</v>
+        <v>2.0167</v>
       </c>
       <c r="Q27">
-        <v>-0</v>
+        <v>0.009362581244196843</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>0.0461487414187643</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>8.02</v>
+      </c>
+      <c r="T27">
+        <v>0.7990674225592077</v>
       </c>
       <c r="U27">
-        <v>40</v>
+        <v>109.6</v>
       </c>
       <c r="V27">
-        <v>1.556420233463035</v>
+        <v>0.5088207985143918</v>
       </c>
       <c r="W27">
-        <v>-0.02244759972954699</v>
+        <v>0.09866787085120796</v>
       </c>
       <c r="X27">
-        <v>0.07134623617821302</v>
+        <v>0.06112703648754469</v>
       </c>
       <c r="Y27">
-        <v>-0.09379383590776001</v>
+        <v>0.03754083436366326</v>
       </c>
       <c r="Z27">
-        <v>0.02613496932515337</v>
+        <v>1.633646159193604</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.07134623617821302</v>
+        <v>0.06030219357772607</v>
       </c>
       <c r="AC27">
-        <v>-0.07134623617821302</v>
+        <v>-0.06030219357772607</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="AG27">
-        <v>-40</v>
+        <v>-102.11</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>0.03360401992013998</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>0.01648363740399217</v>
       </c>
       <c r="AJ27">
-        <v>2.797202797202797</v>
+        <v>-0.9013152087562891</v>
       </c>
       <c r="AK27">
-        <v>-0.5997001499250375</v>
+        <v>-0.2961512804895734</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toyo Securities Co., Ltd. (TSE:8614)</t>
+          <t>Marusan Securities Co., Ltd. (TSE:8613)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.104</v>
+        <v>-0.0216</v>
       </c>
       <c r="E28">
-        <v>0.0282</v>
+        <v>-0.0428</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3853,28 +3853,28 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>-5.52</v>
+        <v>12</v>
       </c>
       <c r="L28">
-        <v>-0.08917609046849757</v>
+        <v>0.1088929219600726</v>
       </c>
       <c r="M28">
-        <v>3.2677</v>
+        <v>7.489800000000001</v>
       </c>
       <c r="N28">
-        <v>0.01851388101983003</v>
+        <v>0.01908229299363057</v>
       </c>
       <c r="O28">
-        <v>-0.5919746376811594</v>
+        <v>0.6241500000000001</v>
       </c>
       <c r="P28">
-        <v>3.2677</v>
+        <v>7.489800000000001</v>
       </c>
       <c r="Q28">
-        <v>0.01851388101983003</v>
+        <v>0.01908229299363057</v>
       </c>
       <c r="R28">
-        <v>-0.5919746376811594</v>
+        <v>0.6241500000000001</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3883,64 +3883,61 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>210.5</v>
+        <v>258.5</v>
       </c>
       <c r="V28">
-        <v>1.192634560906516</v>
+        <v>0.6585987261146496</v>
       </c>
       <c r="W28">
-        <v>-0.01583476764199656</v>
+        <v>0.0382043935052531</v>
       </c>
       <c r="X28">
-        <v>0.08659845351957417</v>
+        <v>0.06132942218158391</v>
       </c>
       <c r="Y28">
-        <v>-0.1024332211615707</v>
+        <v>-0.02312502867633081</v>
       </c>
       <c r="Z28">
-        <v>0.4110225763612217</v>
+        <v>1.183673469387755</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.07229966365708113</v>
+        <v>0.06037771578123831</v>
       </c>
       <c r="AC28">
-        <v>-0.07229966365708113</v>
+        <v>-0.06037771578123831</v>
       </c>
       <c r="AD28">
-        <v>107.7</v>
+        <v>18.9</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>107.7</v>
+        <v>18.9</v>
       </c>
       <c r="AG28">
-        <v>-102.8</v>
+        <v>-239.6</v>
       </c>
       <c r="AH28">
-        <v>0.3789584799437016</v>
+        <v>0.04594069032571706</v>
       </c>
       <c r="AI28">
-        <v>0.2983379501385042</v>
+        <v>0.05459272097053726</v>
       </c>
       <c r="AJ28">
-        <v>-1.394843962008141</v>
+        <v>-1.567037279267495</v>
       </c>
       <c r="AK28">
-        <v>-0.6830564784053156</v>
+        <v>-2.732041049030786</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-2.22</v>
-      </c>
-      <c r="AQ28">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3951,7 +3948,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Monex Group, Inc. (TSE:8698)</t>
+          <t>Ichiyoshi Securities Co., Ltd. (TSE:8624)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3960,10 +3957,10 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.105</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="E29">
-        <v>-0.0151</v>
+        <v>-0.237</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3978,91 +3975,91 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>15.5</v>
+        <v>7.42</v>
       </c>
       <c r="L29">
-        <v>0.0293282876064333</v>
+        <v>0.06418685121107266</v>
       </c>
       <c r="M29">
-        <v>28.3657</v>
+        <v>6.2932</v>
       </c>
       <c r="N29">
-        <v>0.03383313454198474</v>
+        <v>0.03712802359882006</v>
       </c>
       <c r="O29">
-        <v>1.830045161290323</v>
+        <v>0.8481401617250673</v>
       </c>
       <c r="P29">
-        <v>28.3657</v>
+        <v>3.8532</v>
       </c>
       <c r="Q29">
-        <v>0.03383313454198474</v>
+        <v>0.02273274336283186</v>
       </c>
       <c r="R29">
-        <v>1.830045161290323</v>
+        <v>0.5192991913746631</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>0.3877200788152291</v>
       </c>
       <c r="U29">
-        <v>7485.5</v>
+        <v>134.8</v>
       </c>
       <c r="V29">
-        <v>8.928315839694656</v>
+        <v>0.7952802359882006</v>
       </c>
       <c r="W29">
-        <v>0.0173203709911722</v>
+        <v>0.03741805345436208</v>
       </c>
       <c r="X29">
-        <v>0.1458080494411488</v>
+        <v>0.06086968357859902</v>
       </c>
       <c r="Y29">
-        <v>-0.1284876784499766</v>
+        <v>-0.02345163012423695</v>
       </c>
       <c r="Z29">
-        <v>0.1977771124915799</v>
+        <v>1.539690996270644</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.07322985438092383</v>
+        <v>0.06044588956292483</v>
       </c>
       <c r="AC29">
-        <v>-0.07322985438092383</v>
+        <v>-0.06044588956292483</v>
       </c>
       <c r="AD29">
-        <v>2497.6</v>
+        <v>3.01</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>2497.6</v>
+        <v>3.01</v>
       </c>
       <c r="AG29">
-        <v>-4987.9</v>
+        <v>-131.79</v>
       </c>
       <c r="AH29">
-        <v>0.7486810551558752</v>
+        <v>0.01744826386876123</v>
       </c>
       <c r="AI29">
-        <v>0.7705312519281793</v>
+        <v>0.01571719492454702</v>
       </c>
       <c r="AJ29">
-        <v>1.202048439571032</v>
+        <v>-3.49482895783612</v>
       </c>
       <c r="AK29">
-        <v>1.175255059965599</v>
+        <v>-2.323928760359726</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-16.6</v>
+        <v>-0.094</v>
       </c>
       <c r="AQ29">
         <v>-0</v>
@@ -4076,7 +4073,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nomura Holdings, Inc. (TSE:8604)</t>
+          <t>The Imamura Securities Co., Ltd. (TSE:7175)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4085,13 +4082,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>-0.0178</v>
+        <v>0.0339</v>
       </c>
       <c r="E30">
-        <v>-0.145</v>
-      </c>
-      <c r="F30">
-        <v>0.04</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4100,103 +4094,94 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0.01083112369246625</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>0.006780105723444051</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>758.6</v>
+        <v>5.81</v>
       </c>
       <c r="L30">
-        <v>0.08431793173204104</v>
+        <v>0.1976190476190476</v>
       </c>
       <c r="M30">
-        <v>827.662</v>
+        <v>-0</v>
       </c>
       <c r="N30">
-        <v>0.07441196831704532</v>
+        <v>-0</v>
       </c>
       <c r="O30">
-        <v>1.091038755602425</v>
+        <v>-0</v>
       </c>
       <c r="P30">
-        <v>393.262</v>
+        <v>-0</v>
       </c>
       <c r="Q30">
-        <v>0.03535670295881396</v>
+        <v>-0</v>
       </c>
       <c r="R30">
-        <v>0.5184049564988136</v>
+        <v>-0</v>
       </c>
       <c r="S30">
-        <v>434.4</v>
-      </c>
-      <c r="T30">
-        <v>0.5248519323105326</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>27799.4</v>
+        <v>57.1</v>
       </c>
       <c r="V30">
-        <v>2.499339189225638</v>
+        <v>1.441919191919192</v>
       </c>
       <c r="W30">
-        <v>0.03094873834730637</v>
+        <v>0.07809139784946235</v>
       </c>
       <c r="X30">
-        <v>0.5286010362330021</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="Y30">
-        <v>-0.4976522978856958</v>
+        <v>0.01749031620152114</v>
       </c>
       <c r="Z30">
-        <v>0.04190171394887759</v>
+        <v>1.455445544554455</v>
       </c>
       <c r="AA30">
-        <v>0.0002840980505669003</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.07511531743274975</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="AC30">
-        <v>-0.07483121938218286</v>
+        <v>-0.06060108164794122</v>
       </c>
       <c r="AD30">
-        <v>202128.1</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1344.767316256252</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>203472.8673162562</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>175673.4673162563</v>
+        <v>-57.1</v>
       </c>
       <c r="AH30">
-        <v>0.9481690132787872</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>0.9012066118447265</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>0.940455416404938</v>
+        <v>3.262857142857143</v>
       </c>
       <c r="AK30">
-        <v>0.8873344397694285</v>
+        <v>-2.785365853658538</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
         <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>551.6596615720524</v>
-      </c>
-      <c r="AP30">
-        <v>479.4581531557212</v>
       </c>
     </row>
     <row r="31">
@@ -4207,7 +4192,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Daiwa Securities Group Inc. (TSE:8601)</t>
+          <t>Maruhachi Securities Co., Ltd. (TSE:8700)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4216,13 +4201,10 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.00049</v>
+        <v>-0.0101</v>
       </c>
       <c r="E31">
-        <v>-0.0537</v>
-      </c>
-      <c r="F31">
-        <v>-0.05860000000000001</v>
+        <v>-0.104</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4231,103 +4213,94 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0.00708934583830262</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>0.005471828860854173</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>526.3</v>
+        <v>1.91</v>
       </c>
       <c r="L31">
-        <v>0.1164200234476961</v>
+        <v>0.1005263157894737</v>
       </c>
       <c r="M31">
-        <v>470.8736</v>
+        <v>-0</v>
       </c>
       <c r="N31">
-        <v>0.0733151060318251</v>
+        <v>-0</v>
       </c>
       <c r="O31">
-        <v>0.894686680600418</v>
+        <v>-0</v>
       </c>
       <c r="P31">
-        <v>271.6736</v>
+        <v>-0</v>
       </c>
       <c r="Q31">
-        <v>0.04229962943356273</v>
+        <v>-0</v>
       </c>
       <c r="R31">
-        <v>0.5161953258597758</v>
+        <v>-0</v>
       </c>
       <c r="S31">
-        <v>199.2</v>
-      </c>
-      <c r="T31">
-        <v>0.4230434664419496</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>27401.5</v>
+        <v>23.8</v>
       </c>
       <c r="V31">
-        <v>4.26641858437393</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="W31">
-        <v>0.04336326934168246</v>
+        <v>0.03759842519685039</v>
       </c>
       <c r="X31">
-        <v>0.5257801172035315</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="Y31">
-        <v>-0.482416847861849</v>
+        <v>-0.02300265645109082</v>
       </c>
       <c r="Z31">
-        <v>0.04923144624961927</v>
+        <v>0.8837209302325583</v>
       </c>
       <c r="AA31">
-        <v>0.0002693860484502577</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.07511410514648356</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="AC31">
-        <v>-0.07484471909803331</v>
+        <v>-0.06060108164794122</v>
       </c>
       <c r="AD31">
-        <v>116444.1</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>322.7559713439267</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>116766.8559713439</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>89365.35597134393</v>
+        <v>-23.8</v>
       </c>
       <c r="AH31">
-        <v>0.9478640444560936</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>0.908701697763699</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>0.9329498167606646</v>
+        <v>-1.619047619047619</v>
       </c>
       <c r="AK31">
-        <v>0.8839560668974835</v>
+        <v>-0.8981132075471699</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-32.4</v>
-      </c>
-      <c r="AN31">
-        <v>1205.425465838509</v>
-      </c>
-      <c r="AP31">
-        <v>925.1072046722975</v>
+        <v>-0.194</v>
       </c>
       <c r="AQ31">
         <v>-0</v>
@@ -4341,7 +4314,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Daiichi Commodities Co.,Ltd. (TSE:8746)</t>
+          <t>The Kosei Securities Co., Ltd. (TSE:8617)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4350,25 +4323,25 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.0344</v>
+        <v>0.035</v>
       </c>
       <c r="G32">
-        <v>-0.1112412177985948</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>-0.1112412177985948</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>-0.0611661743557906</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>-0.0611661743557906</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>-12</v>
+        <v>-0.281</v>
       </c>
       <c r="L32">
-        <v>-0.2810304449648712</v>
+        <v>-0.05017857142857143</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4392,70 +4365,61 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>20.5</v>
+        <v>40</v>
       </c>
       <c r="V32">
-        <v>0.7945736434108527</v>
+        <v>1.24223602484472</v>
       </c>
       <c r="W32">
-        <v>-0.25</v>
+        <v>-0.002633552014995314</v>
       </c>
       <c r="X32">
-        <v>0.07184903172443635</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="Y32">
-        <v>-0.3218490317244364</v>
+        <v>-0.06323463366293652</v>
       </c>
       <c r="Z32">
-        <v>1.244209536778776</v>
+        <v>0.08395802098950524</v>
       </c>
       <c r="AA32">
-        <v>-0.07610353746174808</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.07139584696863543</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="AC32">
-        <v>-0.1474993844303835</v>
+        <v>-0.06060108164794122</v>
       </c>
       <c r="AD32">
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>0.5189782249612932</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>0.5189782249612932</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>-19.98102177503871</v>
+        <v>-40</v>
       </c>
       <c r="AH32">
-        <v>0.01971878317331813</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>0.01595924144267638</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>-3.433768095114604</v>
+        <v>5.12820512820513</v>
       </c>
       <c r="AK32">
-        <v>-1.662455942680856</v>
+        <v>-0.603318250377074</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-0.007</v>
-      </c>
-      <c r="AN32">
-        <v>-0</v>
-      </c>
-      <c r="AP32">
-        <v>8.063366333752505</v>
-      </c>
-      <c r="AQ32">
-        <v>437.1428571428572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4466,7 +4430,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oak Capital Corporation (TSE:3113)</t>
+          <t>Daiichi Commodities Co.,Ltd. (TSE:8746)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4475,25 +4439,25 @@
         </is>
       </c>
       <c r="D33">
-        <v>-0.257</v>
+        <v>0.008020000000000001</v>
       </c>
       <c r="G33">
-        <v>-0.5333333333333333</v>
+        <v>-0.06315789473684211</v>
       </c>
       <c r="H33">
-        <v>-0.5333333333333333</v>
+        <v>-0.06315789473684211</v>
       </c>
       <c r="I33">
-        <v>-0.3986111111111111</v>
+        <v>-0.006792776269366353</v>
       </c>
       <c r="J33">
-        <v>-0.3986111111111111</v>
+        <v>-0.006792776269366353</v>
       </c>
       <c r="K33">
-        <v>-4.51</v>
+        <v>-0.094</v>
       </c>
       <c r="L33">
-        <v>-0.3131944444444444</v>
+        <v>-0.003298245614035088</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4517,73 +4481,439 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>12.1</v>
+        <v>13.6</v>
       </c>
       <c r="V33">
-        <v>0.2415169660678643</v>
+        <v>0.7431693989071038</v>
       </c>
       <c r="W33">
-        <v>-0.1288571428571429</v>
+        <v>-0.0029375</v>
       </c>
       <c r="X33">
-        <v>0.0769340546434928</v>
+        <v>0.06092505908187992</v>
       </c>
       <c r="Y33">
-        <v>-0.2057911975006357</v>
+        <v>-0.06386255908187992</v>
       </c>
       <c r="Z33">
-        <v>0.4578696343402226</v>
+        <v>2.42388766947908</v>
       </c>
       <c r="AA33">
-        <v>-0.1825119236883943</v>
+        <v>-0.01646492664084721</v>
       </c>
       <c r="AB33">
-        <v>0.07072545204403818</v>
+        <v>0.06049912449131096</v>
       </c>
       <c r="AC33">
-        <v>-0.2532373757324324</v>
+        <v>-0.07696405113215816</v>
       </c>
       <c r="AD33">
-        <v>11.2</v>
+        <v>0.134</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>0.2579706183847053</v>
       </c>
       <c r="AF33">
-        <v>11.2</v>
+        <v>0.3919706183847053</v>
       </c>
       <c r="AG33">
-        <v>-0.9000000000000004</v>
+        <v>-13.20802938161529</v>
       </c>
       <c r="AH33">
-        <v>0.1827079934747145</v>
+        <v>0.02096999970667502</v>
       </c>
       <c r="AI33">
-        <v>0.2338204592901879</v>
+        <v>0.01166858065094228</v>
       </c>
       <c r="AJ33">
-        <v>-0.01829268292682927</v>
+        <v>-2.59389347886795</v>
       </c>
       <c r="AK33">
-        <v>-0.02513966480446928</v>
+        <v>-0.6606667063360492</v>
       </c>
       <c r="AL33">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>-0.132</v>
+        <v>-0.121</v>
       </c>
       <c r="AN33">
-        <v>-2.125237191650854</v>
-      </c>
-      <c r="AO33">
-        <v>-46.29032258064516</v>
+        <v>-1.165217391304348</v>
       </c>
       <c r="AP33">
-        <v>0.1707779886148008</v>
+        <v>114.8524294053504</v>
       </c>
       <c r="AQ33">
-        <v>43.48484848484848</v>
+        <v>3.099173553719008</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>UNIVA Oak Holdings Limited (TSE:3113)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.0558</v>
+      </c>
+      <c r="G34">
+        <v>-0.1459770114942529</v>
+      </c>
+      <c r="H34">
+        <v>-0.1459770114942529</v>
+      </c>
+      <c r="I34">
+        <v>-0.2842911877394636</v>
+      </c>
+      <c r="J34">
+        <v>-0.2842911877394636</v>
+      </c>
+      <c r="K34">
+        <v>-6.51</v>
+      </c>
+      <c r="L34">
+        <v>-0.2494252873563218</v>
+      </c>
+      <c r="M34">
+        <v>-0</v>
+      </c>
+      <c r="N34">
+        <v>-0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>5.58</v>
+      </c>
+      <c r="V34">
+        <v>0.11625</v>
+      </c>
+      <c r="W34">
+        <v>-0.188150289017341</v>
+      </c>
+      <c r="X34">
+        <v>0.06297075748469141</v>
+      </c>
+      <c r="Y34">
+        <v>-0.2511210465020324</v>
+      </c>
+      <c r="Z34">
+        <v>0.9863945578231296</v>
+      </c>
+      <c r="AA34">
+        <v>-0.2804232804232805</v>
+      </c>
+      <c r="AB34">
+        <v>0.0593963627287283</v>
+      </c>
+      <c r="AC34">
+        <v>-0.3398196431520087</v>
+      </c>
+      <c r="AD34">
+        <v>7.52</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>7.52</v>
+      </c>
+      <c r="AG34">
+        <v>1.94</v>
+      </c>
+      <c r="AH34">
+        <v>0.1354466858789625</v>
+      </c>
+      <c r="AI34">
+        <v>0.2165898617511521</v>
+      </c>
+      <c r="AJ34">
+        <v>0.03884661593912694</v>
+      </c>
+      <c r="AK34">
+        <v>0.06657515442690458</v>
+      </c>
+      <c r="AL34">
+        <v>0.114</v>
+      </c>
+      <c r="AM34">
+        <v>-0.194</v>
+      </c>
+      <c r="AN34">
+        <v>-1.372262773722628</v>
+      </c>
+      <c r="AO34">
+        <v>-65.08771929824562</v>
+      </c>
+      <c r="AP34">
+        <v>-0.3540145985401459</v>
+      </c>
+      <c r="AQ34">
+        <v>38.24742268041237</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AI Partners Financial Inc. (TSE:7345)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>-0.03073913043478261</v>
+      </c>
+      <c r="H35">
+        <v>-0.03073913043478261</v>
+      </c>
+      <c r="I35">
+        <v>-0.01543478260869565</v>
+      </c>
+      <c r="J35">
+        <v>-0.01543478260869565</v>
+      </c>
+      <c r="K35">
+        <v>-0.395</v>
+      </c>
+      <c r="L35">
+        <v>-0.01717391304347826</v>
+      </c>
+      <c r="M35">
+        <v>0.4014</v>
+      </c>
+      <c r="N35">
+        <v>0.03935294117647059</v>
+      </c>
+      <c r="O35">
+        <v>-1.01620253164557</v>
+      </c>
+      <c r="P35">
+        <v>0.0864</v>
+      </c>
+      <c r="Q35">
+        <v>0.008470588235294119</v>
+      </c>
+      <c r="R35">
+        <v>-0.2187341772151899</v>
+      </c>
+      <c r="S35">
+        <v>0.3149999999999999</v>
+      </c>
+      <c r="T35">
+        <v>0.7847533632286995</v>
+      </c>
+      <c r="U35">
+        <v>3.58</v>
+      </c>
+      <c r="V35">
+        <v>0.3509803921568628</v>
+      </c>
+      <c r="W35">
+        <v>-0.079</v>
+      </c>
+      <c r="X35">
+        <v>0.06060108164794122</v>
+      </c>
+      <c r="Y35">
+        <v>-0.1396010816479412</v>
+      </c>
+      <c r="Z35">
+        <v>26.13636363636364</v>
+      </c>
+      <c r="AA35">
+        <v>-0.4034090909090909</v>
+      </c>
+      <c r="AB35">
+        <v>0.06060108164794122</v>
+      </c>
+      <c r="AC35">
+        <v>-0.4640101725570321</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>-3.58</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>-0.540785498489426</v>
+      </c>
+      <c r="AK35">
+        <v>-6.280701754385962</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>-0</v>
+      </c>
+      <c r="AP35">
+        <v>20.57471264367816</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ONDECK Co., Ltd. (TSE:7360)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0.2252124645892352</v>
+      </c>
+      <c r="H36">
+        <v>0.2252124645892352</v>
+      </c>
+      <c r="I36">
+        <v>-0.1303116147308782</v>
+      </c>
+      <c r="J36">
+        <v>-0.1303116147308782</v>
+      </c>
+      <c r="K36">
+        <v>-0.597</v>
+      </c>
+      <c r="L36">
+        <v>-0.08456090651558074</v>
+      </c>
+      <c r="M36">
+        <v>-0</v>
+      </c>
+      <c r="N36">
+        <v>-0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>-0</v>
+      </c>
+      <c r="Q36">
+        <v>-0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>4.15</v>
+      </c>
+      <c r="V36">
+        <v>0.2712418300653595</v>
+      </c>
+      <c r="W36">
+        <v>-0.06869965477560415</v>
+      </c>
+      <c r="X36">
+        <v>0.06060108164794122</v>
+      </c>
+      <c r="Y36">
+        <v>-0.1293007364235454</v>
+      </c>
+      <c r="Z36">
+        <v>12.40773286467485</v>
+      </c>
+      <c r="AA36">
+        <v>-1.616871704745165</v>
+      </c>
+      <c r="AB36">
+        <v>0.06060108164794122</v>
+      </c>
+      <c r="AC36">
+        <v>-1.677472786393106</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>-4.15</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>-0.3721973094170404</v>
+      </c>
+      <c r="AK36">
+        <v>-2.331460674157305</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>-0</v>
+      </c>
+      <c r="AP36">
+        <v>4.732041049030787</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1071</v>
+        <v>0.0702</v>
       </c>
       <c r="E2">
-        <v>0.2075</v>
+        <v>0.152</v>
       </c>
       <c r="F2">
-        <v>0.044</v>
+        <v>0.148</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.04798410964808166</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.04757962141585562</v>
       </c>
       <c r="I2">
-        <v>0.004328267002331959</v>
+        <v>0.04472396769253684</v>
       </c>
       <c r="J2">
-        <v>0.003131386220626475</v>
+        <v>0.03178155090609253</v>
       </c>
       <c r="K2">
-        <v>2934.9</v>
+        <v>4564.014</v>
       </c>
       <c r="L2">
-        <v>0.1322158051698817</v>
+        <v>0.1264185410336872</v>
       </c>
       <c r="M2">
-        <v>1875.3575</v>
+        <v>2718.53197</v>
       </c>
       <c r="N2">
-        <v>0.06979009281243255</v>
+        <v>0.06035535576716006</v>
       </c>
       <c r="O2">
-        <v>0.6389851442979317</v>
+        <v>0.5956449673467259</v>
       </c>
       <c r="P2">
-        <v>725.2574999999999</v>
+        <v>1393.94397</v>
       </c>
       <c r="Q2">
-        <v>0.02698994097814033</v>
+        <v>0.03094757948674684</v>
       </c>
       <c r="R2">
-        <v>0.2471148931820505</v>
+        <v>0.3054206165888185</v>
       </c>
       <c r="S2">
-        <v>1150.1</v>
+        <v>1324.588</v>
       </c>
       <c r="T2">
-        <v>0.6132697365702273</v>
+        <v>0.487243856102233</v>
       </c>
       <c r="U2">
-        <v>60658.5</v>
+        <v>100458.05</v>
       </c>
       <c r="V2">
-        <v>2.257362846744122</v>
+        <v>2.230314527963838</v>
       </c>
       <c r="W2">
-        <v>0.09375106077889937</v>
+        <v>0.09267867518884369</v>
       </c>
       <c r="X2">
-        <v>0.276386128523866</v>
+        <v>0.06808714631058553</v>
       </c>
       <c r="Y2">
-        <v>-0.1826350677449666</v>
+        <v>0.02459152887825816</v>
       </c>
       <c r="Z2">
-        <v>0.06811928353688347</v>
+        <v>0.1028969412691034</v>
       </c>
       <c r="AA2">
-        <v>0.0001441090751898461</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05865156071272346</v>
+        <v>0.06517311834697351</v>
       </c>
       <c r="AC2">
-        <v>-0.05850745163753361</v>
+        <v>-0.05934876068162222</v>
       </c>
       <c r="AD2">
-        <v>395314</v>
+        <v>443862.238</v>
       </c>
       <c r="AE2">
-        <v>1526.609973678178</v>
+        <v>1658.609907686405</v>
       </c>
       <c r="AF2">
-        <v>396840.6099736782</v>
+        <v>445520.8479076864</v>
       </c>
       <c r="AG2">
-        <v>336182.1099736782</v>
+        <v>345062.7979076864</v>
       </c>
       <c r="AH2">
-        <v>0.9365809810260763</v>
+        <v>0.9081828332284159</v>
       </c>
       <c r="AI2">
-        <v>0.9159667996885849</v>
+        <v>0.884368326871022</v>
       </c>
       <c r="AJ2">
-        <v>0.9259850152613915</v>
+        <v>0.8845384914632406</v>
       </c>
       <c r="AK2">
-        <v>0.9022859780851683</v>
+        <v>0.8555666828627789</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>297.954</v>
       </c>
       <c r="AM2">
-        <v>-46.8</v>
+        <v>162.638</v>
       </c>
       <c r="AN2">
-        <v>984.838066766318</v>
+        <v>188.8427528034196</v>
+      </c>
+      <c r="AO2">
+        <v>5.050262792243098</v>
       </c>
       <c r="AP2">
-        <v>837.5239411402048</v>
+        <v>146.8081829636014</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>9.252118201158401</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nomura Holdings, Inc. (TSE:8604)</t>
+          <t>M&amp;A Capital Partners Co.,Ltd. (TSE:6080)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,115 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0702</v>
+        <v>0.0877</v>
       </c>
       <c r="E3">
-        <v>0.224</v>
+        <v>0.0261</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.3639760837070254</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3639760837070254</v>
       </c>
       <c r="I3">
-        <v>0.007816194175667424</v>
+        <v>0.361644935651021</v>
       </c>
       <c r="J3">
-        <v>0.005474446873415756</v>
+        <v>0.2493826496396176</v>
       </c>
       <c r="K3">
-        <v>1916.9</v>
+        <v>31.2</v>
       </c>
       <c r="L3">
-        <v>0.1540148800437081</v>
+        <v>0.2331838565022421</v>
       </c>
       <c r="M3">
-        <v>1321.2</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.07547299149986289</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.6892378319161144</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>479.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02738552234713463</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2500912932338671</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>841.7999999999998</v>
-      </c>
-      <c r="T3">
-        <v>0.637148047229791</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>33694</v>
+        <v>273.2</v>
       </c>
       <c r="V3">
-        <v>1.92475550680925</v>
+        <v>0.5089418777943369</v>
       </c>
       <c r="W3">
-        <v>0.08698670853621458</v>
+        <v>0.1254019292604502</v>
       </c>
       <c r="X3">
-        <v>0.2731823725371763</v>
+        <v>0.06676508896603396</v>
       </c>
       <c r="Y3">
-        <v>-0.1861956640009617</v>
+        <v>0.0586368402944162</v>
       </c>
       <c r="Z3">
-        <v>0.05434329125104976</v>
+        <v>41.43007388381282</v>
       </c>
       <c r="AA3">
-        <v>0.0002974994608804312</v>
+        <v>5</v>
       </c>
       <c r="AB3">
-        <v>0.05865884477000599</v>
+        <v>0.06587394520989535</v>
       </c>
       <c r="AC3">
-        <v>-0.05836134530912556</v>
+        <v>4.934126054790105</v>
       </c>
       <c r="AD3">
-        <v>254694.2</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1071.090420254041</v>
+        <v>21.10953804946694</v>
       </c>
       <c r="AF3">
-        <v>255765.2904202541</v>
+        <v>21.10953804946694</v>
       </c>
       <c r="AG3">
-        <v>222071.2904202541</v>
+        <v>-252.090461950533</v>
       </c>
       <c r="AH3">
-        <v>0.9359404875759774</v>
+        <v>0.03783684739154839</v>
       </c>
       <c r="AI3">
-        <v>0.9151716150510895</v>
+        <v>0.06962029685894325</v>
       </c>
       <c r="AJ3">
-        <v>0.9269311828478426</v>
+        <v>-0.8854303360456212</v>
       </c>
       <c r="AK3">
-        <v>0.9035424134981734</v>
+        <v>-8.400344634928846</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.028</v>
       </c>
       <c r="AN3">
-        <v>817.6378812199038</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>712.9094395513773</v>
+        <v>-4.437431120410721</v>
+      </c>
+      <c r="AQ3">
+        <v>-1589.285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -841,130 +844,4017 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Strike Company,Limited (TSE:6196)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.382306477093207</v>
+      </c>
+      <c r="H4">
+        <v>0.382306477093207</v>
+      </c>
+      <c r="I4">
+        <v>0.3736176935229068</v>
+      </c>
+      <c r="J4">
+        <v>0.2750462169338846</v>
+      </c>
+      <c r="K4">
+        <v>34.6</v>
+      </c>
+      <c r="L4">
+        <v>0.2733017377567141</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>128.1</v>
+      </c>
+      <c r="V4">
+        <v>0.2868980963045912</v>
+      </c>
+      <c r="W4">
+        <v>0.3563336766220392</v>
+      </c>
+      <c r="X4">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="Y4">
+        <v>0.2901253974982996</v>
+      </c>
+      <c r="Z4">
+        <v>46.88888888888908</v>
+      </c>
+      <c r="AA4">
+        <v>5</v>
+      </c>
+      <c r="AB4">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="AC4">
+        <v>4.93379172087626</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-128.1</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.4023241206030151</v>
+      </c>
+      <c r="AK4">
+        <v>-160.1249999999977</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-0.035</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-2.646694214876033</v>
+      </c>
+      <c r="AQ4">
+        <v>-1351.428571428571</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>meinan M&amp;A co.,ltd. (NSE:7076)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.192</v>
+      </c>
+      <c r="E5">
+        <v>0.204</v>
+      </c>
+      <c r="G5">
+        <v>0.2999999999999999</v>
+      </c>
+      <c r="H5">
+        <v>0.2999999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0.2998818466558008</v>
+      </c>
+      <c r="J5">
+        <v>0.2161382458609628</v>
+      </c>
+      <c r="K5">
+        <v>2.72</v>
+      </c>
+      <c r="L5">
+        <v>0.2029850746268657</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>12.5</v>
+      </c>
+      <c r="V5">
+        <v>0.8278145695364238</v>
+      </c>
+      <c r="W5">
+        <v>0.2640776699029126</v>
+      </c>
+      <c r="X5">
+        <v>0.06646419260649636</v>
+      </c>
+      <c r="Y5">
+        <v>0.1976134772964163</v>
+      </c>
+      <c r="Z5">
+        <v>8.857066468079127</v>
+      </c>
+      <c r="AA5">
+        <v>1.914350809884576</v>
+      </c>
+      <c r="AB5">
+        <v>0.06608220224922119</v>
+      </c>
+      <c r="AC5">
+        <v>1.848268607635354</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0.2729162740613504</v>
+      </c>
+      <c r="AF5">
+        <v>0.2729162740613504</v>
+      </c>
+      <c r="AG5">
+        <v>-12.22708372593865</v>
+      </c>
+      <c r="AH5">
+        <v>0.01775305798821273</v>
+      </c>
+      <c r="AI5">
+        <v>0.01996035582980165</v>
+      </c>
+      <c r="AJ5">
+        <v>-4.255983314353124</v>
+      </c>
+      <c r="AK5">
+        <v>-10.42451536937163</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>-2.94415692895224</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nihon M&amp;A Center Holdings Inc. (TSE:2127)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.06509999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.0112</v>
+      </c>
+      <c r="G6">
+        <v>0.3532894736842105</v>
+      </c>
+      <c r="H6">
+        <v>0.3532894736842105</v>
+      </c>
+      <c r="I6">
+        <v>0.3692615211741883</v>
+      </c>
+      <c r="J6">
+        <v>0.2438093537185033</v>
+      </c>
+      <c r="K6">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="L6">
+        <v>0.2470394736842105</v>
+      </c>
+      <c r="M6">
+        <v>99.9692</v>
+      </c>
+      <c r="N6">
+        <v>0.07492819667216309</v>
+      </c>
+      <c r="O6">
+        <v>1.331147802929427</v>
+      </c>
+      <c r="P6">
+        <v>51.0692</v>
+      </c>
+      <c r="Q6">
+        <v>0.03827701993704093</v>
+      </c>
+      <c r="R6">
+        <v>0.6800159786950734</v>
+      </c>
+      <c r="S6">
+        <v>48.9</v>
+      </c>
+      <c r="T6">
+        <v>0.489150658402788</v>
+      </c>
+      <c r="U6">
+        <v>247.5</v>
+      </c>
+      <c r="V6">
+        <v>0.1855044221256184</v>
+      </c>
+      <c r="W6">
+        <v>0.2375830433407149</v>
+      </c>
+      <c r="X6">
+        <v>0.06664946922450618</v>
+      </c>
+      <c r="Y6">
+        <v>0.1709335741162087</v>
+      </c>
+      <c r="Z6">
+        <v>3.959751841462113</v>
+      </c>
+      <c r="AA6">
+        <v>0.965424537352531</v>
+      </c>
+      <c r="AB6">
+        <v>0.0659412707489183</v>
+      </c>
+      <c r="AC6">
+        <v>0.8994832666036127</v>
+      </c>
+      <c r="AD6">
+        <v>39.1</v>
+      </c>
+      <c r="AE6">
+        <v>2.472487815233876</v>
+      </c>
+      <c r="AF6">
+        <v>41.57248781523388</v>
+      </c>
+      <c r="AG6">
+        <v>-205.9275121847661</v>
+      </c>
+      <c r="AH6">
+        <v>0.03021756008600824</v>
+      </c>
+      <c r="AI6">
+        <v>0.1188557970208177</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1825157614039853</v>
+      </c>
+      <c r="AK6">
+        <v>-2.013518166848509</v>
+      </c>
+      <c r="AL6">
+        <v>0.105</v>
+      </c>
+      <c r="AM6">
+        <v>-0.754</v>
+      </c>
+      <c r="AN6">
+        <v>0.3434343434343435</v>
+      </c>
+      <c r="AO6">
+        <v>1056.190476190476</v>
+      </c>
+      <c r="AP6">
+        <v>-1.808761635351481</v>
+      </c>
+      <c r="AQ6">
+        <v>-147.0822281167109</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FinTech Global Incorporated (TSE:8789)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0852</v>
+      </c>
+      <c r="G7">
+        <v>0.2199170124481327</v>
+      </c>
+      <c r="H7">
+        <v>0.2199170124481327</v>
+      </c>
+      <c r="I7">
+        <v>0.1942974420826354</v>
+      </c>
+      <c r="J7">
+        <v>0.1508391976404838</v>
+      </c>
+      <c r="K7">
+        <v>11.7</v>
+      </c>
+      <c r="L7">
+        <v>0.1213692946058091</v>
+      </c>
+      <c r="M7">
+        <v>3.13</v>
+      </c>
+      <c r="N7">
+        <v>0.02041748206131767</v>
+      </c>
+      <c r="O7">
+        <v>0.2675213675213675</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>3.13</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>40.4</v>
+      </c>
+      <c r="V7">
+        <v>0.2635355512067841</v>
+      </c>
+      <c r="W7">
+        <v>0.2089285714285714</v>
+      </c>
+      <c r="X7">
+        <v>0.07141743199954063</v>
+      </c>
+      <c r="Y7">
+        <v>0.1375111394290308</v>
+      </c>
+      <c r="Z7">
+        <v>1.055910309406773</v>
+      </c>
+      <c r="AA7">
+        <v>0.1592726638512327</v>
+      </c>
+      <c r="AB7">
+        <v>0.06383177557682783</v>
+      </c>
+      <c r="AC7">
+        <v>0.09544088827440488</v>
+      </c>
+      <c r="AD7">
+        <v>52.1</v>
+      </c>
+      <c r="AE7">
+        <v>4.298632916169741</v>
+      </c>
+      <c r="AF7">
+        <v>56.39863291616975</v>
+      </c>
+      <c r="AG7">
+        <v>15.99863291616975</v>
+      </c>
+      <c r="AH7">
+        <v>0.2689508850480488</v>
+      </c>
+      <c r="AI7">
+        <v>0.4292178058819774</v>
+      </c>
+      <c r="AJ7">
+        <v>0.09449948083214388</v>
+      </c>
+      <c r="AK7">
+        <v>0.1758117941278095</v>
+      </c>
+      <c r="AL7">
+        <v>1.12</v>
+      </c>
+      <c r="AM7">
+        <v>0.9590000000000001</v>
+      </c>
+      <c r="AN7">
+        <v>2.276103101791175</v>
+      </c>
+      <c r="AO7">
+        <v>15.98214285714285</v>
+      </c>
+      <c r="AP7">
+        <v>0.6989354703438072</v>
+      </c>
+      <c r="AQ7">
+        <v>18.6652763295099</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SBI Holdings, Inc. (TSE:8473)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.29</v>
+      </c>
+      <c r="E8">
+        <v>0.152</v>
+      </c>
+      <c r="F8">
+        <v>0.252</v>
+      </c>
+      <c r="G8">
+        <v>0.1620266713266855</v>
+      </c>
+      <c r="H8">
+        <v>0.160519446477135</v>
+      </c>
+      <c r="I8">
+        <v>0.1376161819154862</v>
+      </c>
+      <c r="J8">
+        <v>0.1148682953016425</v>
+      </c>
+      <c r="K8">
+        <v>662.3</v>
+      </c>
+      <c r="L8">
+        <v>0.07233587085922738</v>
+      </c>
+      <c r="M8">
+        <v>381.5</v>
+      </c>
+      <c r="N8">
+        <v>0.04975611028510317</v>
+      </c>
+      <c r="O8">
+        <v>0.5760229503246264</v>
+      </c>
+      <c r="P8">
+        <v>381.402</v>
+      </c>
+      <c r="Q8">
+        <v>0.04974332889897488</v>
+      </c>
+      <c r="R8">
+        <v>0.5758749811263778</v>
+      </c>
+      <c r="S8">
+        <v>0.09800000000001319</v>
+      </c>
+      <c r="T8">
+        <v>0.0002568807339449887</v>
+      </c>
+      <c r="U8">
+        <v>34022.2</v>
+      </c>
+      <c r="V8">
+        <v>4.437253827894723</v>
+      </c>
+      <c r="W8">
+        <v>0.09039540311463551</v>
+      </c>
+      <c r="X8">
+        <v>0.1321347093184075</v>
+      </c>
+      <c r="Y8">
+        <v>-0.04173930620377198</v>
+      </c>
+      <c r="Z8">
+        <v>0.9164606376057254</v>
+      </c>
+      <c r="AA8">
+        <v>0.105272271152826</v>
+      </c>
+      <c r="AB8">
+        <v>0.05693535946844583</v>
+      </c>
+      <c r="AC8">
+        <v>0.04833691168438019</v>
+      </c>
+      <c r="AD8">
+        <v>35699.9</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>35699.9</v>
+      </c>
+      <c r="AG8">
+        <v>1677.700000000004</v>
+      </c>
+      <c r="AH8">
+        <v>0.8231985851090569</v>
+      </c>
+      <c r="AI8">
+        <v>0.7351421587705588</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1795272388738487</v>
+      </c>
+      <c r="AK8">
+        <v>0.1153875251896534</v>
+      </c>
+      <c r="AL8">
+        <v>293</v>
+      </c>
+      <c r="AM8">
+        <v>252.4</v>
+      </c>
+      <c r="AN8">
+        <v>21.63630303030303</v>
+      </c>
+      <c r="AO8">
+        <v>4.300341296928328</v>
+      </c>
+      <c r="AP8">
+        <v>1.016787878787881</v>
+      </c>
+      <c r="AQ8">
+        <v>4.992076069730587</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ONDECK Co., Ltd. (TSE:7360)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>-0.155</v>
+      </c>
+      <c r="H9">
+        <v>-0.155</v>
+      </c>
+      <c r="I9">
+        <v>0.042</v>
+      </c>
+      <c r="J9">
+        <v>0.021</v>
+      </c>
+      <c r="K9">
+        <v>0.13</v>
+      </c>
+      <c r="L9">
+        <v>0.01625</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>4.91</v>
+      </c>
+      <c r="V9">
+        <v>0.2888235294117647</v>
+      </c>
+      <c r="W9">
+        <v>0.02192242833052277</v>
+      </c>
+      <c r="X9">
+        <v>0.0664823025281184</v>
+      </c>
+      <c r="Y9">
+        <v>-0.04455987419759563</v>
+      </c>
+      <c r="Z9">
+        <v>4.494382022471911</v>
+      </c>
+      <c r="AA9">
+        <v>0.09438202247191015</v>
+      </c>
+      <c r="AB9">
+        <v>0.06604051932931362</v>
+      </c>
+      <c r="AC9">
+        <v>0.02834150314259652</v>
+      </c>
+      <c r="AD9">
+        <v>0.329</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0.329</v>
+      </c>
+      <c r="AG9">
+        <v>-4.581</v>
+      </c>
+      <c r="AH9">
+        <v>0.01898551560967165</v>
+      </c>
+      <c r="AI9">
+        <v>0.05149475661292848</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.3688702794105806</v>
+      </c>
+      <c r="AK9">
+        <v>-3.097363083164302</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0.6375968992248062</v>
+      </c>
+      <c r="AP9">
+        <v>-8.877906976744187</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Akatsuki Corp. (TSE:8737)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0696</v>
+      </c>
+      <c r="E10">
+        <v>0.156</v>
+      </c>
+      <c r="G10">
+        <v>0.07076663858466722</v>
+      </c>
+      <c r="H10">
+        <v>0.07076663858466722</v>
+      </c>
+      <c r="I10">
+        <v>0.06655433866891322</v>
+      </c>
+      <c r="J10">
+        <v>0.04505001663681479</v>
+      </c>
+      <c r="K10">
+        <v>16</v>
+      </c>
+      <c r="L10">
+        <v>0.04493119910137602</v>
+      </c>
+      <c r="M10">
+        <v>6.357100000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.0736628041714948</v>
+      </c>
+      <c r="O10">
+        <v>0.3973187500000001</v>
+      </c>
+      <c r="P10">
+        <v>4.7571</v>
+      </c>
+      <c r="Q10">
+        <v>0.05512282734646582</v>
+      </c>
+      <c r="R10">
+        <v>0.29731875</v>
+      </c>
+      <c r="S10">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="T10">
+        <v>0.2516870900253261</v>
+      </c>
+      <c r="U10">
+        <v>142.7</v>
+      </c>
+      <c r="V10">
+        <v>1.653534183082271</v>
+      </c>
+      <c r="W10">
+        <v>0.1584158415841584</v>
+      </c>
+      <c r="X10">
+        <v>0.1121971750091504</v>
+      </c>
+      <c r="Y10">
+        <v>0.04621866657500806</v>
+      </c>
+      <c r="Z10">
+        <v>1.694423296535973</v>
+      </c>
+      <c r="AA10">
+        <v>0.07633379769875213</v>
+      </c>
+      <c r="AB10">
+        <v>0.05759551568858153</v>
+      </c>
+      <c r="AC10">
+        <v>0.01873828201017061</v>
+      </c>
+      <c r="AD10">
+        <v>280.3</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>280.3</v>
+      </c>
+      <c r="AG10">
+        <v>137.6</v>
+      </c>
+      <c r="AH10">
+        <v>0.7645935624659028</v>
+      </c>
+      <c r="AI10">
+        <v>0.695188492063492</v>
+      </c>
+      <c r="AJ10">
+        <v>0.6145600714604734</v>
+      </c>
+      <c r="AK10">
+        <v>0.5282149712092131</v>
+      </c>
+      <c r="AL10">
+        <v>3.31</v>
+      </c>
+      <c r="AM10">
+        <v>-0.6200000000000001</v>
+      </c>
+      <c r="AN10">
+        <v>10.53759398496241</v>
+      </c>
+      <c r="AO10">
+        <v>7.16012084592145</v>
+      </c>
+      <c r="AP10">
+        <v>5.172932330827068</v>
+      </c>
+      <c r="AQ10">
+        <v>-38.2258064516129</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AI Partners Financial Inc. (TSE:7345)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.115</v>
+      </c>
+      <c r="E11">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0.009315589353612166</v>
+      </c>
+      <c r="H11">
+        <v>0.009315589353612166</v>
+      </c>
+      <c r="I11">
+        <v>0.002129277566539924</v>
+      </c>
+      <c r="J11">
+        <v>0.001064638783269962</v>
+      </c>
+      <c r="K11">
+        <v>0.007</v>
+      </c>
+      <c r="L11">
+        <v>0.0002661596958174905</v>
+      </c>
+      <c r="M11">
+        <v>0.09072000000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.007436065573770493</v>
+      </c>
+      <c r="O11">
+        <v>12.96</v>
+      </c>
+      <c r="P11">
+        <v>0.09072000000000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.007436065573770493</v>
+      </c>
+      <c r="R11">
+        <v>12.96</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>3.34</v>
+      </c>
+      <c r="V11">
+        <v>0.2737704918032787</v>
+      </c>
+      <c r="W11">
+        <v>0.001686746987951807</v>
+      </c>
+      <c r="X11">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="Y11">
+        <v>-0.06452153213578773</v>
+      </c>
+      <c r="Z11">
+        <v>46.14035087719296</v>
+      </c>
+      <c r="AA11">
+        <v>0.04912280701754384</v>
+      </c>
+      <c r="AB11">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0170854721061957</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>-3.34</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.3769751693002257</v>
+      </c>
+      <c r="AK11">
+        <v>-3.306930693069308</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>-15.98086124401914</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kobayashi Yoko Co., Ltd. (TSE:8742)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0462</v>
+      </c>
+      <c r="G12">
+        <v>0.0720125786163522</v>
+      </c>
+      <c r="H12">
+        <v>0.0720125786163522</v>
+      </c>
+      <c r="I12">
+        <v>0.05723270440251572</v>
+      </c>
+      <c r="J12">
+        <v>0.05445283018867925</v>
+      </c>
+      <c r="K12">
+        <v>2.33</v>
+      </c>
+      <c r="L12">
+        <v>0.07327044025157232</v>
+      </c>
+      <c r="M12">
+        <v>0.4340000000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.01990825688073395</v>
+      </c>
+      <c r="O12">
+        <v>0.1862660944206009</v>
+      </c>
+      <c r="P12">
+        <v>0.4340000000000001</v>
+      </c>
+      <c r="Q12">
+        <v>0.01990825688073395</v>
+      </c>
+      <c r="R12">
+        <v>0.1862660944206009</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>20.9</v>
+      </c>
+      <c r="V12">
+        <v>0.9587155963302751</v>
+      </c>
+      <c r="W12">
+        <v>0.03794788273615635</v>
+      </c>
+      <c r="X12">
+        <v>0.06643495725014145</v>
+      </c>
+      <c r="Y12">
+        <v>-0.0284870745139851</v>
+      </c>
+      <c r="Z12">
+        <v>0.7828655834564254</v>
+      </c>
+      <c r="AA12">
+        <v>0.04262924667651403</v>
+      </c>
+      <c r="AB12">
+        <v>0.06606904785108576</v>
+      </c>
+      <c r="AC12">
+        <v>-0.02343980117457173</v>
+      </c>
+      <c r="AD12">
+        <v>0.349</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0.349</v>
+      </c>
+      <c r="AG12">
+        <v>-20.551</v>
+      </c>
+      <c r="AH12">
+        <v>0.01575691904826403</v>
+      </c>
+      <c r="AI12">
+        <v>0.005174279826239084</v>
+      </c>
+      <c r="AJ12">
+        <v>-16.4539631705364</v>
+      </c>
+      <c r="AK12">
+        <v>-0.4414917613697394</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-0.356</v>
+      </c>
+      <c r="AN12">
+        <v>0.1608294930875576</v>
+      </c>
+      <c r="AP12">
+        <v>-9.470506912442396</v>
+      </c>
+      <c r="AQ12">
+        <v>-5.112359550561798</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tokai Tokyo Financial Holdings, Inc. (TSE:8616)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="E13">
+        <v>-0.245</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.003468768568615626</v>
+      </c>
+      <c r="J13">
+        <v>0.002148000584930938</v>
+      </c>
+      <c r="K13">
+        <v>73.8</v>
+      </c>
+      <c r="L13">
+        <v>0.1218827415359207</v>
+      </c>
+      <c r="M13">
+        <v>28.0672</v>
+      </c>
+      <c r="N13">
+        <v>0.03556862248130781</v>
+      </c>
+      <c r="O13">
+        <v>0.3803143631436314</v>
+      </c>
+      <c r="P13">
+        <v>28.0672</v>
+      </c>
+      <c r="Q13">
+        <v>0.03556862248130781</v>
+      </c>
+      <c r="R13">
+        <v>0.3803143631436314</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>921.5</v>
+      </c>
+      <c r="V13">
+        <v>1.167786085413762</v>
+      </c>
+      <c r="W13">
+        <v>0.06334220238606128</v>
+      </c>
+      <c r="X13">
+        <v>0.1527572212374479</v>
+      </c>
+      <c r="Y13">
+        <v>-0.08941501885138667</v>
+      </c>
+      <c r="Z13">
+        <v>0.1323382053059747</v>
+      </c>
+      <c r="AA13">
+        <v>0.0002842625424059441</v>
+      </c>
+      <c r="AB13">
+        <v>0.05652753402154208</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05624327147913613</v>
+      </c>
+      <c r="AD13">
+        <v>4768.9</v>
+      </c>
+      <c r="AE13">
+        <v>54.49830315851619</v>
+      </c>
+      <c r="AF13">
+        <v>4823.398303158516</v>
+      </c>
+      <c r="AG13">
+        <v>3901.898303158516</v>
+      </c>
+      <c r="AH13">
+        <v>0.8594030755330612</v>
+      </c>
+      <c r="AI13">
+        <v>0.7813197960498847</v>
+      </c>
+      <c r="AJ13">
+        <v>0.8317842068992675</v>
+      </c>
+      <c r="AK13">
+        <v>0.7429500873640101</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-8.91</v>
+      </c>
+      <c r="AN13">
+        <v>366.8384615384615</v>
+      </c>
+      <c r="AP13">
+        <v>300.1460233198858</v>
+      </c>
+      <c r="AQ13">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GMO Financial Holdings, Inc. (TSE:7177)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0583</v>
+      </c>
+      <c r="E14">
+        <v>-0.055</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>32.2</v>
+      </c>
+      <c r="L14">
+        <v>0.1095610751956448</v>
+      </c>
+      <c r="M14">
+        <v>24.19</v>
+      </c>
+      <c r="N14">
+        <v>0.04691621411947245</v>
+      </c>
+      <c r="O14">
+        <v>0.7512422360248446</v>
+      </c>
+      <c r="P14">
+        <v>24.19</v>
+      </c>
+      <c r="Q14">
+        <v>0.04691621411947245</v>
+      </c>
+      <c r="R14">
+        <v>0.7512422360248446</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>699.2</v>
+      </c>
+      <c r="V14">
+        <v>1.356089992242048</v>
+      </c>
+      <c r="W14">
+        <v>0.1031059878322126</v>
+      </c>
+      <c r="X14">
+        <v>0.1072937619675276</v>
+      </c>
+      <c r="Y14">
+        <v>-0.004187774135315001</v>
+      </c>
+      <c r="Z14">
+        <v>0.2227865372953305</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05783087842585</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05783087842585</v>
+      </c>
+      <c r="AD14">
+        <v>1496.1</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1496.1</v>
+      </c>
+      <c r="AG14">
+        <v>796.8999999999999</v>
+      </c>
+      <c r="AH14">
+        <v>0.7436993587513049</v>
+      </c>
+      <c r="AI14">
+        <v>0.8161138991926686</v>
+      </c>
+      <c r="AJ14">
+        <v>0.6071619047619047</v>
+      </c>
+      <c r="AK14">
+        <v>0.7027336860670192</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Okasan Securities Group Inc. (TSE:8609)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.0614</v>
+      </c>
+      <c r="E15">
+        <v>-0.405</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.007497451286264235</v>
+      </c>
+      <c r="J15">
+        <v>0.00525896065541305</v>
+      </c>
+      <c r="K15">
+        <v>82.7</v>
+      </c>
+      <c r="L15">
+        <v>0.142832469775475</v>
+      </c>
+      <c r="M15">
+        <v>65.03440000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.07925225444796491</v>
+      </c>
+      <c r="O15">
+        <v>0.7863893591293833</v>
+      </c>
+      <c r="P15">
+        <v>42.1344</v>
+      </c>
+      <c r="Q15">
+        <v>0.05134584450402144</v>
+      </c>
+      <c r="R15">
+        <v>0.5094848851269649</v>
+      </c>
+      <c r="S15">
+        <v>22.90000000000001</v>
+      </c>
+      <c r="T15">
+        <v>0.3521213388606645</v>
+      </c>
+      <c r="U15">
+        <v>482.9</v>
+      </c>
+      <c r="V15">
+        <v>0.5884718498659517</v>
+      </c>
+      <c r="W15">
+        <v>0.06658615136876006</v>
+      </c>
+      <c r="X15">
+        <v>0.1177119529777563</v>
+      </c>
+      <c r="Y15">
+        <v>-0.05112580160899624</v>
+      </c>
+      <c r="Z15">
+        <v>0.2240716515391169</v>
+      </c>
+      <c r="AA15">
+        <v>0.001178383999437639</v>
+      </c>
+      <c r="AB15">
+        <v>0.05927747878302402</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05809909478358638</v>
+      </c>
+      <c r="AD15">
+        <v>2941.1</v>
+      </c>
+      <c r="AE15">
+        <v>43.79487852626504</v>
+      </c>
+      <c r="AF15">
+        <v>2984.894878526265</v>
+      </c>
+      <c r="AG15">
+        <v>2501.994878526265</v>
+      </c>
+      <c r="AH15">
+        <v>0.7843644450474758</v>
+      </c>
+      <c r="AI15">
+        <v>0.6778775805097289</v>
+      </c>
+      <c r="AJ15">
+        <v>0.7530243589721126</v>
+      </c>
+      <c r="AK15">
+        <v>0.6381997110114587</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-13.7</v>
+      </c>
+      <c r="AN15">
+        <v>224.5114503816794</v>
+      </c>
+      <c r="AP15">
+        <v>190.9919754600202</v>
+      </c>
+      <c r="AQ15">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nomura Holdings, Inc. (TSE:8604)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0702</v>
+      </c>
+      <c r="E16">
+        <v>0.224</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0.007816194175667424</v>
+      </c>
+      <c r="J16">
+        <v>0.005474446873415756</v>
+      </c>
+      <c r="K16">
+        <v>1916.9</v>
+      </c>
+      <c r="L16">
+        <v>0.1540148800437081</v>
+      </c>
+      <c r="M16">
+        <v>1321.2</v>
+      </c>
+      <c r="N16">
+        <v>0.07547299149986289</v>
+      </c>
+      <c r="O16">
+        <v>0.6892378319161144</v>
+      </c>
+      <c r="P16">
+        <v>479.4</v>
+      </c>
+      <c r="Q16">
+        <v>0.02738552234713463</v>
+      </c>
+      <c r="R16">
+        <v>0.2500912932338671</v>
+      </c>
+      <c r="S16">
+        <v>841.7999999999998</v>
+      </c>
+      <c r="T16">
+        <v>0.637148047229791</v>
+      </c>
+      <c r="U16">
+        <v>33694</v>
+      </c>
+      <c r="V16">
+        <v>1.92475550680925</v>
+      </c>
+      <c r="W16">
+        <v>0.08698670853621458</v>
+      </c>
+      <c r="X16">
+        <v>0.2730819814494421</v>
+      </c>
+      <c r="Y16">
+        <v>-0.1860952729132275</v>
+      </c>
+      <c r="Z16">
+        <v>0.05434329125104976</v>
+      </c>
+      <c r="AA16">
+        <v>0.0002974994608804312</v>
+      </c>
+      <c r="AB16">
+        <v>0.05865241376587403</v>
+      </c>
+      <c r="AC16">
+        <v>-0.0583549143049936</v>
+      </c>
+      <c r="AD16">
+        <v>254694.2</v>
+      </c>
+      <c r="AE16">
+        <v>1071.090420254041</v>
+      </c>
+      <c r="AF16">
+        <v>255765.2904202541</v>
+      </c>
+      <c r="AG16">
+        <v>222071.2904202541</v>
+      </c>
+      <c r="AH16">
+        <v>0.9359404875759774</v>
+      </c>
+      <c r="AI16">
+        <v>0.9151716150510895</v>
+      </c>
+      <c r="AJ16">
+        <v>0.9269311828478426</v>
+      </c>
+      <c r="AK16">
+        <v>0.9035424134981734</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>817.6378812199038</v>
+      </c>
+      <c r="AP16">
+        <v>712.9094395513773</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Daiwa Securities Group Inc. (TSE:8601)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D17">
         <v>0.144</v>
       </c>
-      <c r="E4">
+      <c r="E17">
         <v>0.191</v>
       </c>
-      <c r="F4">
+      <c r="F17">
         <v>0.044</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>-0.0001234577592218235</v>
       </c>
-      <c r="J4">
+      <c r="J17">
         <v>-9.216725039641377E-05</v>
       </c>
-      <c r="K4">
+      <c r="K17">
         <v>1018</v>
       </c>
-      <c r="L4">
+      <c r="L17">
         <v>0.1043931252307314</v>
       </c>
-      <c r="M4">
+      <c r="M17">
         <v>554.1575</v>
       </c>
-      <c r="N4">
+      <c r="N17">
         <v>0.05916819705737898</v>
       </c>
-      <c r="O4">
+      <c r="O17">
         <v>0.5443590373280943</v>
       </c>
-      <c r="P4">
+      <c r="P17">
         <v>245.8575</v>
       </c>
-      <c r="Q4">
+      <c r="Q17">
         <v>0.02625056055008649</v>
       </c>
-      <c r="R4">
+      <c r="R17">
         <v>0.2415103143418467</v>
       </c>
-      <c r="S4">
+      <c r="S17">
         <v>308.3000000000001</v>
       </c>
-      <c r="T4">
+      <c r="T17">
         <v>0.5563400296847016</v>
       </c>
-      <c r="U4">
+      <c r="U17">
         <v>26964.5</v>
       </c>
-      <c r="V4">
+      <c r="V17">
         <v>2.879038629908818</v>
       </c>
-      <c r="W4">
+      <c r="W17">
         <v>0.1005154130215842</v>
       </c>
-      <c r="X4">
-        <v>0.2795898845105558</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1790744714889716</v>
-      </c>
-      <c r="Z4">
+      <c r="X17">
+        <v>0.2794866644564004</v>
+      </c>
+      <c r="Y17">
+        <v>-0.1789712514348162</v>
+      </c>
+      <c r="Z17">
         <v>0.1007007419752666</v>
       </c>
-      <c r="AA4">
+      <c r="AA17">
         <v>-9.281310500739051E-06</v>
       </c>
-      <c r="AB4">
-        <v>0.05864427665544092</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05865355796594166</v>
-      </c>
-      <c r="AD4">
+      <c r="AB17">
+        <v>0.05863785063052115</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05864713194102189</v>
+      </c>
+      <c r="AD17">
         <v>140619.8</v>
       </c>
-      <c r="AE4">
+      <c r="AE17">
         <v>455.5195534241377</v>
       </c>
-      <c r="AF4">
+      <c r="AF17">
         <v>141075.3195534241</v>
       </c>
-      <c r="AG4">
+      <c r="AG17">
         <v>114110.8195534241</v>
       </c>
-      <c r="AH4">
+      <c r="AH17">
         <v>0.9377444143741962</v>
       </c>
-      <c r="AI4">
+      <c r="AI17">
         <v>0.9174119745816051</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ17">
         <v>0.9241492030323382</v>
       </c>
-      <c r="AK4">
+      <c r="AK17">
         <v>0.8998508167936757</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
         <v>-46.8</v>
       </c>
-      <c r="AN4">
+      <c r="AN17">
         <v>1564.180200222469</v>
       </c>
-      <c r="AP4">
+      <c r="AP17">
         <v>1269.308337635419</v>
       </c>
-      <c r="AQ4">
-        <v>-0</v>
+      <c r="AQ17">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mito Securities Co., Ltd. (TSE:8622)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0745</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0.01039790705360605</v>
+      </c>
+      <c r="J18">
+        <v>0.00752503704439852</v>
+      </c>
+      <c r="K18">
+        <v>16.7</v>
+      </c>
+      <c r="L18">
+        <v>0.1624513618677043</v>
+      </c>
+      <c r="M18">
+        <v>5.62</v>
+      </c>
+      <c r="N18">
+        <v>0.02481236203090508</v>
+      </c>
+      <c r="O18">
+        <v>0.3365269461077844</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>-0</v>
+      </c>
+      <c r="S18">
+        <v>5.62</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>232.8</v>
+      </c>
+      <c r="V18">
+        <v>1.027814569536424</v>
+      </c>
+      <c r="W18">
+        <v>0.06222056631892698</v>
+      </c>
+      <c r="X18">
+        <v>0.06808714631058553</v>
+      </c>
+      <c r="Y18">
+        <v>-0.005866579991658551</v>
+      </c>
+      <c r="Z18">
+        <v>0.8649159774101181</v>
+      </c>
+      <c r="AA18">
+        <v>0.006508524770303292</v>
+      </c>
+      <c r="AB18">
+        <v>0.06517311834697351</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05866459357667021</v>
+      </c>
+      <c r="AD18">
+        <v>25.3</v>
+      </c>
+      <c r="AE18">
+        <v>4.755475774446488</v>
+      </c>
+      <c r="AF18">
+        <v>30.05547577444649</v>
+      </c>
+      <c r="AG18">
+        <v>-202.7445242255535</v>
+      </c>
+      <c r="AH18">
+        <v>0.1171500069671874</v>
+      </c>
+      <c r="AI18">
+        <v>0.09358543771352355</v>
+      </c>
+      <c r="AJ18">
+        <v>-8.534643808045463</v>
+      </c>
+      <c r="AK18">
+        <v>-2.294645832060471</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-2.12</v>
+      </c>
+      <c r="AN18">
+        <v>12.52475247524752</v>
+      </c>
+      <c r="AP18">
+        <v>-100.3685763492839</v>
+      </c>
+      <c r="AQ18">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Matsui Securities Co., Ltd. (TSE:8628)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.12</v>
+      </c>
+      <c r="E19">
+        <v>0.1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>77.8</v>
+      </c>
+      <c r="L19">
+        <v>0.2694838933148597</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>-0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>-0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>672.4</v>
+      </c>
+      <c r="V19">
+        <v>0.5032557443305142</v>
+      </c>
+      <c r="W19">
+        <v>0.1527287004318806</v>
+      </c>
+      <c r="X19">
+        <v>0.08825735089607592</v>
+      </c>
+      <c r="Y19">
+        <v>0.06447134953580472</v>
+      </c>
+      <c r="Z19">
+        <v>0.154071939374533</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05934876068162222</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05934876068162222</v>
+      </c>
+      <c r="AD19">
+        <v>2080.6</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>2080.6</v>
+      </c>
+      <c r="AG19">
+        <v>1408.2</v>
+      </c>
+      <c r="AH19">
+        <v>0.6089501565838382</v>
+      </c>
+      <c r="AI19">
+        <v>0.7938797313797313</v>
+      </c>
+      <c r="AJ19">
+        <v>0.5131363189155704</v>
+      </c>
+      <c r="AK19">
+        <v>0.7227468692260316</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-0.056</v>
+      </c>
+      <c r="AQ19">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Monex Group, Inc. (TSE:8698)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.0578</v>
+      </c>
+      <c r="E20">
+        <v>0.946</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>217</v>
+      </c>
+      <c r="L20">
+        <v>0.4694937256598875</v>
+      </c>
+      <c r="M20">
+        <v>73.81959999999999</v>
+      </c>
+      <c r="N20">
+        <v>0.0471389527458493</v>
+      </c>
+      <c r="O20">
+        <v>0.3401824884792626</v>
+      </c>
+      <c r="P20">
+        <v>67.9896</v>
+      </c>
+      <c r="Q20">
+        <v>0.04341609195402298</v>
+      </c>
+      <c r="R20">
+        <v>0.313316129032258</v>
+      </c>
+      <c r="S20">
+        <v>5.829999999999998</v>
+      </c>
+      <c r="T20">
+        <v>0.07897631523335265</v>
+      </c>
+      <c r="U20">
+        <v>411.9</v>
+      </c>
+      <c r="V20">
+        <v>0.2630268199233716</v>
+      </c>
+      <c r="W20">
+        <v>0.3099557206113412</v>
+      </c>
+      <c r="X20">
+        <v>0.07236566023623658</v>
+      </c>
+      <c r="Y20">
+        <v>0.2375900603751047</v>
+      </c>
+      <c r="Z20">
+        <v>0.2156085273125904</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.0635302855622461</v>
+      </c>
+      <c r="AC20">
+        <v>-0.0635302855622461</v>
+      </c>
+      <c r="AD20">
+        <v>681</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>681</v>
+      </c>
+      <c r="AG20">
+        <v>269.1</v>
+      </c>
+      <c r="AH20">
+        <v>0.3030707610146863</v>
+      </c>
+      <c r="AI20">
+        <v>0.4479379069920411</v>
+      </c>
+      <c r="AJ20">
+        <v>0.146640510053948</v>
+      </c>
+      <c r="AK20">
+        <v>0.2427823890292313</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-5.7</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hirose Tusyo Inc. (TSE:7185)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>18.6</v>
+      </c>
+      <c r="L21">
+        <v>0.2506738544474393</v>
+      </c>
+      <c r="M21">
+        <v>2.0502</v>
+      </c>
+      <c r="N21">
+        <v>0.01320154539600773</v>
+      </c>
+      <c r="O21">
+        <v>0.1102258064516129</v>
+      </c>
+      <c r="P21">
+        <v>2.0502</v>
+      </c>
+      <c r="Q21">
+        <v>0.01320154539600773</v>
+      </c>
+      <c r="R21">
+        <v>0.1102258064516129</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>96.2</v>
+      </c>
+      <c r="V21">
+        <v>0.6194462330972311</v>
+      </c>
+      <c r="W21">
+        <v>0.1730232558139535</v>
+      </c>
+      <c r="X21">
+        <v>0.07060284787777453</v>
+      </c>
+      <c r="Y21">
+        <v>0.102420407936179</v>
+      </c>
+      <c r="Z21">
+        <v>1.087976539589443</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.06354022579318454</v>
+      </c>
+      <c r="AC21">
+        <v>-0.06354022579318454</v>
+      </c>
+      <c r="AD21">
+        <v>48.2</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>48.2</v>
+      </c>
+      <c r="AG21">
+        <v>-48</v>
+      </c>
+      <c r="AH21">
+        <v>0.2368550368550369</v>
+      </c>
+      <c r="AI21">
+        <v>0.2688232013385388</v>
+      </c>
+      <c r="AJ21">
+        <v>-0.4473438956197576</v>
+      </c>
+      <c r="AK21">
+        <v>-0.5776173285198556</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aizawa Securities Group Co., Ltd. (TSE:8708)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.079</v>
+      </c>
+      <c r="E22">
+        <v>0.326</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>25</v>
+      </c>
+      <c r="L22">
+        <v>0.1944012441679627</v>
+      </c>
+      <c r="M22">
+        <v>84.8291</v>
+      </c>
+      <c r="N22">
+        <v>0.2420921803652968</v>
+      </c>
+      <c r="O22">
+        <v>3.393164</v>
+      </c>
+      <c r="P22">
+        <v>5.6291</v>
+      </c>
+      <c r="Q22">
+        <v>0.01606478310502283</v>
+      </c>
+      <c r="R22">
+        <v>0.225164</v>
+      </c>
+      <c r="S22">
+        <v>79.2</v>
+      </c>
+      <c r="T22">
+        <v>0.933641875252714</v>
+      </c>
+      <c r="U22">
+        <v>156.1</v>
+      </c>
+      <c r="V22">
+        <v>0.4454908675799087</v>
+      </c>
+      <c r="W22">
+        <v>0.06965728615213151</v>
+      </c>
+      <c r="X22">
+        <v>0.07212413602387022</v>
+      </c>
+      <c r="Y22">
+        <v>-0.002466849871738702</v>
+      </c>
+      <c r="Z22">
+        <v>0.3953772224596399</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.06360437506468161</v>
+      </c>
+      <c r="AC22">
+        <v>-0.06360437506468161</v>
+      </c>
+      <c r="AD22">
+        <v>146.4</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>146.4</v>
+      </c>
+      <c r="AG22">
+        <v>-9.699999999999989</v>
+      </c>
+      <c r="AH22">
+        <v>0.2946859903381643</v>
+      </c>
+      <c r="AI22">
+        <v>0.3063402385436284</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.02847079542119163</v>
+      </c>
+      <c r="AK22">
+        <v>-0.0301429459291485</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-3.38</v>
+      </c>
+      <c r="AQ22">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IwaiCosmo Holdings, Inc. (TSE:8707)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.0534</v>
+      </c>
+      <c r="E23">
+        <v>0.129</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>43.6</v>
+      </c>
+      <c r="L23">
+        <v>0.2473057288712422</v>
+      </c>
+      <c r="M23">
+        <v>16.403</v>
+      </c>
+      <c r="N23">
+        <v>0.0472845200345921</v>
+      </c>
+      <c r="O23">
+        <v>0.3762155963302752</v>
+      </c>
+      <c r="P23">
+        <v>16.403</v>
+      </c>
+      <c r="Q23">
+        <v>0.0472845200345921</v>
+      </c>
+      <c r="R23">
+        <v>0.3762155963302752</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>56.5</v>
+      </c>
+      <c r="V23">
+        <v>0.1628711444220237</v>
+      </c>
+      <c r="W23">
+        <v>0.1076011846001974</v>
+      </c>
+      <c r="X23">
+        <v>0.06926135768065098</v>
+      </c>
+      <c r="Y23">
+        <v>0.03833982691954646</v>
+      </c>
+      <c r="Z23">
+        <v>0.4176735370765222</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.06421021289964156</v>
+      </c>
+      <c r="AC23">
+        <v>-0.06421021289964156</v>
+      </c>
+      <c r="AD23">
+        <v>74.8</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>74.8</v>
+      </c>
+      <c r="AG23">
+        <v>18.3</v>
+      </c>
+      <c r="AH23">
+        <v>0.1773772824282665</v>
+      </c>
+      <c r="AI23">
+        <v>0.1391886862672125</v>
+      </c>
+      <c r="AJ23">
+        <v>0.05010952902519167</v>
+      </c>
+      <c r="AK23">
+        <v>0.03805364940736119</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kyokuto Securities Co., Ltd. (TSE:8706)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="E24">
+        <v>0.523</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>31.9</v>
+      </c>
+      <c r="L24">
+        <v>0.5747747747747748</v>
+      </c>
+      <c r="M24">
+        <v>17.8002</v>
+      </c>
+      <c r="N24">
+        <v>0.05886309523809524</v>
+      </c>
+      <c r="O24">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="P24">
+        <v>17.8002</v>
+      </c>
+      <c r="Q24">
+        <v>0.05886309523809524</v>
+      </c>
+      <c r="R24">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.2410714285714286</v>
+      </c>
+      <c r="W24">
+        <v>0.09267867518884369</v>
+      </c>
+      <c r="X24">
+        <v>0.07008990276873486</v>
+      </c>
+      <c r="Y24">
+        <v>0.02258877242010883</v>
+      </c>
+      <c r="Z24">
+        <v>0.189419795221843</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.06430710887000275</v>
+      </c>
+      <c r="AC24">
+        <v>-0.06430710887000275</v>
+      </c>
+      <c r="AD24">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+      <c r="AH24">
+        <v>0.2151570205035038</v>
+      </c>
+      <c r="AI24">
+        <v>0.1858327729208698</v>
+      </c>
+      <c r="AJ24">
+        <v>0.03201024327784891</v>
+      </c>
+      <c r="AK24">
+        <v>0.02679528403001072</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-5.48</v>
+      </c>
+      <c r="AQ24">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Toyo Securities Co., Ltd. (TSE:8614)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.0591</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>15.7</v>
+      </c>
+      <c r="L25">
+        <v>0.1914634146341463</v>
+      </c>
+      <c r="M25">
+        <v>5.677</v>
+      </c>
+      <c r="N25">
+        <v>0.01954889807162535</v>
+      </c>
+      <c r="O25">
+        <v>0.3615923566878981</v>
+      </c>
+      <c r="P25">
+        <v>5.677</v>
+      </c>
+      <c r="Q25">
+        <v>0.01954889807162535</v>
+      </c>
+      <c r="R25">
+        <v>0.3615923566878981</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>218.4</v>
+      </c>
+      <c r="V25">
+        <v>0.7520661157024794</v>
+      </c>
+      <c r="W25">
+        <v>0.06544393497290538</v>
+      </c>
+      <c r="X25">
+        <v>0.06946042413936822</v>
+      </c>
+      <c r="Y25">
+        <v>-0.004016489166462842</v>
+      </c>
+      <c r="Z25">
+        <v>0.6788079470198677</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.06455783254115915</v>
+      </c>
+      <c r="AC25">
+        <v>-0.06455783254115915</v>
+      </c>
+      <c r="AD25">
+        <v>66.7</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>66.7</v>
+      </c>
+      <c r="AG25">
+        <v>-151.7</v>
+      </c>
+      <c r="AH25">
+        <v>0.1867824138896668</v>
+      </c>
+      <c r="AI25">
+        <v>0.1991639295312034</v>
+      </c>
+      <c r="AJ25">
+        <v>-1.093727469358327</v>
+      </c>
+      <c r="AK25">
+        <v>-1.302145922746781</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1.84</v>
+      </c>
+      <c r="AQ25">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Marusan Securities Co., Ltd. (TSE:8613)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.0482</v>
+      </c>
+      <c r="E26">
+        <v>0.7659999999999999</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0.0006388219086443145</v>
+      </c>
+      <c r="J26">
+        <v>0.0004451343714866614</v>
+      </c>
+      <c r="K26">
+        <v>21.8</v>
+      </c>
+      <c r="L26">
+        <v>0.1632958801498127</v>
+      </c>
+      <c r="M26">
+        <v>9.254</v>
+      </c>
+      <c r="N26">
+        <v>0.02195492289442467</v>
+      </c>
+      <c r="O26">
+        <v>0.4244954128440367</v>
+      </c>
+      <c r="P26">
+        <v>9.254</v>
+      </c>
+      <c r="Q26">
+        <v>0.02195492289442467</v>
+      </c>
+      <c r="R26">
+        <v>0.4244954128440367</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>332.3</v>
+      </c>
+      <c r="V26">
+        <v>0.7883748517200475</v>
+      </c>
+      <c r="W26">
+        <v>0.0666055606477238</v>
+      </c>
+      <c r="X26">
+        <v>0.06684766601681462</v>
+      </c>
+      <c r="Y26">
+        <v>-0.0002421053690908198</v>
+      </c>
+      <c r="Z26">
+        <v>1.518191233884066</v>
+      </c>
+      <c r="AA26">
+        <v>0.0006757991006915425</v>
+      </c>
+      <c r="AB26">
+        <v>0.06582650447026162</v>
+      </c>
+      <c r="AC26">
+        <v>-0.06515070536957007</v>
+      </c>
+      <c r="AD26">
+        <v>18.8</v>
+      </c>
+      <c r="AE26">
+        <v>0.23358637597992</v>
+      </c>
+      <c r="AF26">
+        <v>19.03358637597992</v>
+      </c>
+      <c r="AG26">
+        <v>-313.2664136240201</v>
+      </c>
+      <c r="AH26">
+        <v>0.04320575539440352</v>
+      </c>
+      <c r="AI26">
+        <v>0.05113344704138216</v>
+      </c>
+      <c r="AJ26">
+        <v>-2.894354923579827</v>
+      </c>
+      <c r="AK26">
+        <v>-7.84468518991948</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>142.4242424242424</v>
+      </c>
+      <c r="AP26">
+        <v>-2373.230406242576</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Yutaka Trusty Securities Co., Ltd. (TSE:8747)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>14.4</v>
+      </c>
+      <c r="L27">
+        <v>0.2384105960264901</v>
+      </c>
+      <c r="M27">
+        <v>2.67235</v>
+      </c>
+      <c r="N27">
+        <v>0.04713139329805996</v>
+      </c>
+      <c r="O27">
+        <v>0.1855798611111111</v>
+      </c>
+      <c r="P27">
+        <v>2.67235</v>
+      </c>
+      <c r="Q27">
+        <v>0.04713139329805996</v>
+      </c>
+      <c r="R27">
+        <v>0.1855798611111111</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>40.6</v>
+      </c>
+      <c r="V27">
+        <v>0.7160493827160493</v>
+      </c>
+      <c r="W27">
+        <v>0.1892247043363995</v>
+      </c>
+      <c r="X27">
+        <v>0.06742942200264759</v>
+      </c>
+      <c r="Y27">
+        <v>0.1217952823337519</v>
+      </c>
+      <c r="Z27">
+        <v>1.357608451337379</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.06531392289369894</v>
+      </c>
+      <c r="AC27">
+        <v>-0.06531392289369894</v>
+      </c>
+      <c r="AD27">
+        <v>4.89</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>4.89</v>
+      </c>
+      <c r="AG27">
+        <v>-35.71</v>
+      </c>
+      <c r="AH27">
+        <v>0.07939600584510471</v>
+      </c>
+      <c r="AI27">
+        <v>0.0508368853311155</v>
+      </c>
+      <c r="AJ27">
+        <v>-1.701286326822296</v>
+      </c>
+      <c r="AK27">
+        <v>-0.6423817233315345</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-0.342</v>
+      </c>
+      <c r="AQ27">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Traders Holdings Co.,Ltd. (TSE:8704)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.169</v>
+      </c>
+      <c r="E28">
+        <v>0.214</v>
+      </c>
+      <c r="G28">
+        <v>0.008795180722891567</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>32.9</v>
+      </c>
+      <c r="L28">
+        <v>0.3603504928806134</v>
+      </c>
+      <c r="M28">
+        <v>8.690000000000001</v>
+      </c>
+      <c r="N28">
+        <v>0.04934696195343555</v>
+      </c>
+      <c r="O28">
+        <v>0.2641337386018238</v>
+      </c>
+      <c r="P28">
+        <v>3.08</v>
+      </c>
+      <c r="Q28">
+        <v>0.0174900624645088</v>
+      </c>
+      <c r="R28">
+        <v>0.09361702127659575</v>
+      </c>
+      <c r="S28">
+        <v>5.610000000000001</v>
+      </c>
+      <c r="T28">
+        <v>0.6455696202531646</v>
+      </c>
+      <c r="U28">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="V28">
+        <v>0.46053378762067</v>
+      </c>
+      <c r="W28">
+        <v>0.3847953216374269</v>
+      </c>
+      <c r="X28">
+        <v>0.0675188753992286</v>
+      </c>
+      <c r="Y28">
+        <v>0.3172764462381983</v>
+      </c>
+      <c r="Z28">
+        <v>1.587826086956522</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.06545968222131059</v>
+      </c>
+      <c r="AC28">
+        <v>-0.06545968222131059</v>
+      </c>
+      <c r="AD28">
+        <v>16.3</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>16.3</v>
+      </c>
+      <c r="AG28">
+        <v>-64.8</v>
+      </c>
+      <c r="AH28">
+        <v>0.08471933471933472</v>
+      </c>
+      <c r="AI28">
+        <v>0.125674633770239</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.582210242587601</v>
+      </c>
+      <c r="AK28">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HS Holdings Co., Ltd. (TSE:8699)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>-0.09390000000000001</v>
+      </c>
+      <c r="E29">
+        <v>0.0732</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>73</v>
+      </c>
+      <c r="L29">
+        <v>0.2965069049553209</v>
+      </c>
+      <c r="M29">
+        <v>2.107</v>
+      </c>
+      <c r="N29">
+        <v>0.01263947210557889</v>
+      </c>
+      <c r="O29">
+        <v>0.02886301369863014</v>
+      </c>
+      <c r="P29">
+        <v>2.107</v>
+      </c>
+      <c r="Q29">
+        <v>0.01263947210557889</v>
+      </c>
+      <c r="R29">
+        <v>0.02886301369863014</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>129.3</v>
+      </c>
+      <c r="V29">
+        <v>0.7756448710257949</v>
+      </c>
+      <c r="W29">
+        <v>0.1645997745208568</v>
+      </c>
+      <c r="X29">
+        <v>0.06700415377404063</v>
+      </c>
+      <c r="Y29">
+        <v>0.0975956207468162</v>
+      </c>
+      <c r="Z29">
+        <v>0.7529282241047126</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.0656088109814202</v>
+      </c>
+      <c r="AC29">
+        <v>-0.0656088109814202</v>
+      </c>
+      <c r="AD29">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="AG29">
+        <v>-119.93</v>
+      </c>
+      <c r="AH29">
+        <v>0.05321747032430283</v>
+      </c>
+      <c r="AI29">
+        <v>0.01605084194117546</v>
+      </c>
+      <c r="AJ29">
+        <v>-2.564250587983751</v>
+      </c>
+      <c r="AK29">
+        <v>-0.2638898057077475</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ichiyoshi Securities Co., Ltd. (TSE:8624)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.00389</v>
+      </c>
+      <c r="E30">
+        <v>-0.0554</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>14.8</v>
+      </c>
+      <c r="L30">
+        <v>0.1095484826054774</v>
+      </c>
+      <c r="M30">
+        <v>3.8794</v>
+      </c>
+      <c r="N30">
+        <v>0.01947489959839357</v>
+      </c>
+      <c r="O30">
+        <v>0.2621216216216216</v>
+      </c>
+      <c r="P30">
+        <v>3.8794</v>
+      </c>
+      <c r="Q30">
+        <v>0.01947489959839357</v>
+      </c>
+      <c r="R30">
+        <v>0.2621216216216216</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>176.8</v>
+      </c>
+      <c r="V30">
+        <v>0.887550200803213</v>
+      </c>
+      <c r="W30">
+        <v>0.07851458885941645</v>
+      </c>
+      <c r="X30">
+        <v>0.06639308879515385</v>
+      </c>
+      <c r="Y30">
+        <v>0.0121215000642626</v>
+      </c>
+      <c r="Z30">
+        <v>2.382295891377183</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.0660631468271478</v>
+      </c>
+      <c r="AC30">
+        <v>-0.0660631468271478</v>
+      </c>
+      <c r="AD30">
+        <v>2.6</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>2.6</v>
+      </c>
+      <c r="AG30">
+        <v>-174.2</v>
+      </c>
+      <c r="AH30">
+        <v>0.01288404360753221</v>
+      </c>
+      <c r="AI30">
+        <v>0.01247600767754319</v>
+      </c>
+      <c r="AJ30">
+        <v>-6.968000000000009</v>
+      </c>
+      <c r="AK30">
+        <v>-5.512658227848103</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-0.147</v>
+      </c>
+      <c r="AQ30">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The Imamura Securities Co., Ltd. (TSE:7175)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.09789999999999999</v>
+      </c>
+      <c r="E31">
+        <v>0.496</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>5.8</v>
+      </c>
+      <c r="L31">
+        <v>0.1841269841269841</v>
+      </c>
+      <c r="M31">
+        <v>1.6</v>
+      </c>
+      <c r="N31">
+        <v>0.0431266846361186</v>
+      </c>
+      <c r="O31">
+        <v>0.2758620689655172</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>-0</v>
+      </c>
+      <c r="S31">
+        <v>1.6</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>54.3</v>
+      </c>
+      <c r="V31">
+        <v>1.463611859838275</v>
+      </c>
+      <c r="W31">
+        <v>0.07474226804123711</v>
+      </c>
+      <c r="X31">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="Y31">
+        <v>0.00853398891749757</v>
+      </c>
+      <c r="Z31">
+        <v>1.536585365853659</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="AC31">
+        <v>-0.06620827912373954</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>-54.3</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>3.156976744186047</v>
+      </c>
+      <c r="AK31">
+        <v>-1.85958904109589</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Maruhachi Securities Co., Ltd. (TSE:8700)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0322</v>
+      </c>
+      <c r="E32">
+        <v>0.112</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>3.06</v>
+      </c>
+      <c r="L32">
+        <v>0.1403669724770642</v>
+      </c>
+      <c r="M32">
+        <v>-0</v>
+      </c>
+      <c r="N32">
+        <v>-0</v>
+      </c>
+      <c r="O32">
+        <v>-0</v>
+      </c>
+      <c r="P32">
+        <v>-0</v>
+      </c>
+      <c r="Q32">
+        <v>-0</v>
+      </c>
+      <c r="R32">
+        <v>-0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>28.2</v>
+      </c>
+      <c r="V32">
+        <v>0.7790055248618784</v>
+      </c>
+      <c r="W32">
+        <v>0.06083499005964215</v>
+      </c>
+      <c r="X32">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="Y32">
+        <v>-0.00537328906409739</v>
+      </c>
+      <c r="Z32">
+        <v>0.8226415094339624</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="AC32">
+        <v>-0.06620827912373954</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>-28.2</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>-3.524999999999998</v>
+      </c>
+      <c r="AK32">
+        <v>-1.184873949579832</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-0.377</v>
+      </c>
+      <c r="AQ32">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The Kosei Securities Co., Ltd. (TSE:8617)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.214</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>-0.063</v>
+      </c>
+      <c r="L33">
+        <v>-0.007768187422934649</v>
+      </c>
+      <c r="M33">
+        <v>-0</v>
+      </c>
+      <c r="N33">
+        <v>-0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>-0</v>
+      </c>
+      <c r="Q33">
+        <v>-0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>15.4</v>
+      </c>
+      <c r="V33">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="W33">
+        <v>-0.0005926622765757291</v>
+      </c>
+      <c r="X33">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="Y33">
+        <v>-0.06680094140031527</v>
+      </c>
+      <c r="Z33">
+        <v>0.1223227752639517</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.06620827912373954</v>
+      </c>
+      <c r="AC33">
+        <v>-0.06620827912373954</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>-15.4</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>-1.4</v>
+      </c>
+      <c r="AK33">
+        <v>-0.1568228105906314</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unbanked,Inc. (TSE:8746)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.0682</v>
+      </c>
+      <c r="E34">
+        <v>0.311</v>
+      </c>
+      <c r="G34">
+        <v>-0.01830578512396694</v>
+      </c>
+      <c r="H34">
+        <v>-0.01830578512396694</v>
+      </c>
+      <c r="I34">
+        <v>-0.001132707099532108</v>
+      </c>
+      <c r="J34">
+        <v>-0.001120200869726549</v>
+      </c>
+      <c r="K34">
+        <v>3.13</v>
+      </c>
+      <c r="L34">
+        <v>0.06466942148760331</v>
+      </c>
+      <c r="M34">
+        <v>-0</v>
+      </c>
+      <c r="N34">
+        <v>-0</v>
+      </c>
+      <c r="O34">
+        <v>-0</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>-0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>18.4</v>
+      </c>
+      <c r="V34">
+        <v>0.8803827751196173</v>
+      </c>
+      <c r="W34">
+        <v>0.09427710843373494</v>
+      </c>
+      <c r="X34">
+        <v>0.06659045400005537</v>
+      </c>
+      <c r="Y34">
+        <v>0.02768665443367957</v>
+      </c>
+      <c r="Z34">
+        <v>2.436677213632436</v>
+      </c>
+      <c r="AA34">
+        <v>-0.002729567933953918</v>
+      </c>
+      <c r="AB34">
+        <v>0.06597604809878332</v>
+      </c>
+      <c r="AC34">
+        <v>-0.06870561603273724</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0.5641151180867702</v>
+      </c>
+      <c r="AF34">
+        <v>0.5641151180867702</v>
+      </c>
+      <c r="AG34">
+        <v>-17.83588488191323</v>
+      </c>
+      <c r="AH34">
+        <v>0.02628177844664175</v>
+      </c>
+      <c r="AI34">
+        <v>0.01418653769640108</v>
+      </c>
+      <c r="AJ34">
+        <v>-5.820892556102763</v>
+      </c>
+      <c r="AK34">
+        <v>-0.8348524983753451</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-0.181</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>-109.4226066375045</v>
+      </c>
+      <c r="AQ34">
+        <v>0.6961325966850829</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UNIVA Oak Holdings Limited (TSE:3113)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.229</v>
+      </c>
+      <c r="G35">
+        <v>-0.267032967032967</v>
+      </c>
+      <c r="H35">
+        <v>-0.267032967032967</v>
+      </c>
+      <c r="I35">
+        <v>-0.2043956043956044</v>
+      </c>
+      <c r="J35">
+        <v>-0.2043956043956044</v>
+      </c>
+      <c r="K35">
+        <v>-10.8</v>
+      </c>
+      <c r="L35">
+        <v>-0.3956043956043956</v>
+      </c>
+      <c r="M35">
+        <v>-0</v>
+      </c>
+      <c r="N35">
+        <v>-0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>6.6</v>
+      </c>
+      <c r="V35">
+        <v>0.165</v>
+      </c>
+      <c r="W35">
+        <v>-0.4090909090909091</v>
+      </c>
+      <c r="X35">
+        <v>0.07052685466083494</v>
+      </c>
+      <c r="Y35">
+        <v>-0.479617763751744</v>
+      </c>
+      <c r="Z35">
+        <v>1.184381778741865</v>
+      </c>
+      <c r="AA35">
+        <v>-0.2420824295010846</v>
+      </c>
+      <c r="AB35">
+        <v>0.06454849506157483</v>
+      </c>
+      <c r="AC35">
+        <v>-0.3066309245626594</v>
+      </c>
+      <c r="AD35">
+        <v>12.2</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>12.2</v>
+      </c>
+      <c r="AG35">
+        <v>5.6</v>
+      </c>
+      <c r="AH35">
+        <v>0.2337164750957854</v>
+      </c>
+      <c r="AI35">
+        <v>0.4357142857142857</v>
+      </c>
+      <c r="AJ35">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="AK35">
+        <v>0.2616822429906542</v>
+      </c>
+      <c r="AL35">
+        <v>0.419</v>
+      </c>
+      <c r="AM35">
+        <v>0.105</v>
+      </c>
+      <c r="AN35">
+        <v>-2.449799196787148</v>
+      </c>
+      <c r="AO35">
+        <v>-13.31742243436754</v>
+      </c>
+      <c r="AP35">
+        <v>-1.124497991967871</v>
+      </c>
+      <c r="AQ35">
+        <v>-53.14285714285715</v>
       </c>
     </row>
   </sheetData>
